--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER GLOBAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEYENDA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESTAURANTES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIVIENDA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOTELES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEYENDA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESTAURANTES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIVIENDA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOTELES" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -156,62 +155,8 @@
       <color rgb="009C9088"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="003D6491"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="003D6491"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00B86328"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004A4A4A"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00B35D30"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00B35D30"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00436B3A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00436B3A"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E5C1E"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="30">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -338,28 +283,8 @@
         <fgColor rgb="00888888"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAE5D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3EDE0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005C5248"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDEB"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -396,38 +321,11 @@
         <color rgb="001A3A5C"/>
       </top>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="008B3A00"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="005C1831"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="001A3A5C"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -679,102 +577,6 @@
     <xf numFmtId="0" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1140,3975 +942,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PM ESTUDIO — MASTER GLOBAL  ·  1 septiembre 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="97" t="inlineStr">
-        <is>
-          <t>PROYECTO</t>
-        </is>
-      </c>
-      <c r="B3" s="97" t="inlineStr">
-        <is>
-          <t>DPTO</t>
-        </is>
-      </c>
-      <c r="C3" s="97" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D3" s="97" t="inlineStr">
-        <is>
-          <t>ESTADO</t>
-        </is>
-      </c>
-      <c r="E3" s="97" t="inlineStr">
-        <is>
-          <t>HITO PRÓXIMO</t>
-        </is>
-      </c>
-      <c r="F3" s="97" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="G3" s="97" t="inlineStr">
-        <is>
-          <t>BLOQUEADOR</t>
-        </is>
-      </c>
-      <c r="H3" s="97" t="inlineStr">
-        <is>
-          <t>CONSTRUCTORA</t>
-        </is>
-      </c>
-      <c r="I3" s="97" t="inlineStr">
-        <is>
-          <t>FASE</t>
-        </is>
-      </c>
-      <c r="J3" s="97" t="inlineStr">
-        <is>
-          <t>ATENCIÓN</t>
-        </is>
-      </c>
-      <c r="K3" s="97" t="inlineStr">
-        <is>
-          <t>NIVEL</t>
-        </is>
-      </c>
-      <c r="L3" s="97" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▸  PROYECTOS ACTIVOS  —  1 septiembre 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="99" t="inlineStr">
-        <is>
-          <t>PEDRAZA</t>
-        </is>
-      </c>
-      <c r="B5" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C5" s="101" t="inlineStr">
-        <is>
-          <t>Olatz/Paula</t>
-        </is>
-      </c>
-      <c r="D5" s="101" t="inlineStr">
-        <is>
-          <t>Remates finales</t>
-        </is>
-      </c>
-      <c r="E5" s="101" t="inlineStr">
-        <is>
-          <t>Reunión 1 sep con clientes y constructora</t>
-        </is>
-      </c>
-      <c r="F5" s="101" t="inlineStr">
-        <is>
-          <t>1 sep</t>
-        </is>
-      </c>
-      <c r="G5" s="101" t="inlineStr">
-        <is>
-          <t>2ª fase caballerías pendiente de definir</t>
-        </is>
-      </c>
-      <c r="H5" s="101" t="inlineStr">
-        <is>
-          <t>Amarco</t>
-        </is>
-      </c>
-      <c r="I5" s="101" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J5" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K5" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L5" s="101" t="inlineStr">
-        <is>
-          <t>Lista repasos pendiente. 2ª fase caballerías por definir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="103" t="inlineStr">
-        <is>
-          <t>ZAHARA</t>
-        </is>
-      </c>
-      <c r="B6" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C6" s="51" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D6" s="51" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E6" s="51" t="inlineStr">
-        <is>
-          <t>Dormitorio de abajo pendiente</t>
-        </is>
-      </c>
-      <c r="F6" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G6" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="51" t="inlineStr">
-        <is>
-          <t>Raúl</t>
-        </is>
-      </c>
-      <c r="I6" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J6" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K6" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L6" s="51" t="inlineStr">
-        <is>
-          <t>Pedidos hechos. Ale con listas de deco faltante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="103" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
-      <c r="B7" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C7" s="51" t="inlineStr">
-        <is>
-          <t>Sara/Andrea</t>
-        </is>
-      </c>
-      <c r="D7" s="51" t="inlineStr">
-        <is>
-          <t>Entregado 29 ago</t>
-        </is>
-      </c>
-      <c r="E7" s="51" t="inlineStr">
-        <is>
-          <t>Mobiliario exterior mediados sep</t>
-        </is>
-      </c>
-      <c r="F7" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G7" s="51" t="inlineStr">
-        <is>
-          <t>Problemas de obra asumidos</t>
-        </is>
-      </c>
-      <c r="H7" s="51" t="inlineStr">
-        <is>
-          <t>Raúl</t>
-        </is>
-      </c>
-      <c r="I7" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J7" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K7" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L7" s="51" t="inlineStr">
-        <is>
-          <t>Entregado. Mob. exterior mediados sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="99" t="inlineStr">
-        <is>
-          <t>ALCALÁ 58</t>
-        </is>
-      </c>
-      <c r="B8" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C8" s="101" t="inlineStr">
-        <is>
-          <t>Alicia/Javi</t>
-        </is>
-      </c>
-      <c r="D8" s="101" t="inlineStr">
-        <is>
-          <t>Fin de obra</t>
-        </is>
-      </c>
-      <c r="E8" s="101" t="inlineStr">
-        <is>
-          <t>Comunicar fecha nueva al cliente</t>
-        </is>
-      </c>
-      <c r="F8" s="101" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G8" s="101" t="inlineStr">
-        <is>
-          <t>Va retrasado — cliente sin informar</t>
-        </is>
-      </c>
-      <c r="H8" s="101" t="inlineStr">
-        <is>
-          <t>Consultores Proy.</t>
-        </is>
-      </c>
-      <c r="I8" s="101" t="inlineStr">
-        <is>
-          <t>FIN OBRA</t>
-        </is>
-      </c>
-      <c r="J8" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K8" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L8" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Va retrasado. Comunicar nueva fecha al cliente hoy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="99" t="inlineStr">
-        <is>
-          <t>LA FLORIDA</t>
-        </is>
-      </c>
-      <c r="B9" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C9" s="101" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D9" s="101" t="inlineStr">
-        <is>
-          <t>Obra en ejecución</t>
-        </is>
-      </c>
-      <c r="E9" s="101" t="inlineStr">
-        <is>
-          <t>Montaje última semana sep</t>
-        </is>
-      </c>
-      <c r="F9" s="101" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G9" s="101" t="inlineStr">
-        <is>
-          <t>Paula debe visitar obra para confirmar fecha</t>
-        </is>
-      </c>
-      <c r="H9" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="101" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J9" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K9" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L9" s="101" t="inlineStr">
-        <is>
-          <t>Deco organizada 2ª sem sep. Montaje última sem sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="99" t="inlineStr">
-        <is>
-          <t>LA RINCONADA</t>
-        </is>
-      </c>
-      <c r="B10" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C10" s="101" t="inlineStr">
-        <is>
-          <t>Cristina/Nela</t>
-        </is>
-      </c>
-      <c r="D10" s="101" t="inlineStr">
-        <is>
-          <t>Obra en ejecución</t>
-        </is>
-      </c>
-      <c r="E10" s="101" t="inlineStr">
-        <is>
-          <t>FIN OBRA fin oct · Entrega deco nov</t>
-        </is>
-      </c>
-      <c r="F10" s="101" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G10" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Presu deco sin enviar — Ale revisar URGENTE</t>
-        </is>
-      </c>
-      <c r="H10" s="101" t="inlineStr">
-        <is>
-          <t>Raúl</t>
-        </is>
-      </c>
-      <c r="I10" s="101" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J10" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K10" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L10" s="101" t="inlineStr">
-        <is>
-          <t>Presu deco pendiente revisión Ale. FIN OBRA fin oct (pdte aceptación). Entrega nov.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="99" t="inlineStr">
-        <is>
-          <t>VIUDA DE ALDAMA 3</t>
-        </is>
-      </c>
-      <c r="B11" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C11" s="101" t="inlineStr">
-        <is>
-          <t>Nela/Andrea</t>
-        </is>
-      </c>
-      <c r="D11" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E11" s="101" t="inlineStr">
-        <is>
-          <t>Reunión jue 3 sep (Natalia+Raúl+Ale+Nela)</t>
-        </is>
-      </c>
-      <c r="F11" s="101" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G11" s="101" t="inlineStr">
-        <is>
-          <t>Presupuestos obra+deco pendientes actualizar</t>
-        </is>
-      </c>
-      <c r="H11" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J11" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K11" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L11" s="101" t="inlineStr">
-        <is>
-          <t>Reunión 3 sep. Objetivo: arrancar obra septiembre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="103" t="inlineStr">
-        <is>
-          <t>VIUDA DE ALDAMA 2</t>
-        </is>
-      </c>
-      <c r="B12" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="D12" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto nuevo</t>
-        </is>
-      </c>
-      <c r="E12" s="51" t="inlineStr">
-        <is>
-          <t>Organizar con cliente en septiembre</t>
-        </is>
-      </c>
-      <c r="F12" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G12" s="51" t="inlineStr">
-        <is>
-          <t>Sin responsable asignado</t>
-        </is>
-      </c>
-      <c r="H12" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J12" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K12" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L12" s="51" t="inlineStr">
-        <is>
-          <t>Nuevo proyecto. Arranque septiembre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="99" t="inlineStr">
-        <is>
-          <t>SANTANDER VIV</t>
-        </is>
-      </c>
-      <c r="B13" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C13" s="101" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="D13" s="101" t="inlineStr">
-        <is>
-          <t>Obra en ejecución</t>
-        </is>
-      </c>
-      <c r="E13" s="101" t="inlineStr">
-        <is>
-          <t>Visita obra 14 sep · Deco sem 21 sep</t>
-        </is>
-      </c>
-      <c r="F13" s="101" t="inlineStr">
-        <is>
-          <t>Dic 2026</t>
-        </is>
-      </c>
-      <c r="G13" s="101" t="inlineStr">
-        <is>
-          <t>Muchas decisiones pendientes de cliente</t>
-        </is>
-      </c>
-      <c r="H13" s="101" t="inlineStr">
-        <is>
-          <t>Constructora cliente</t>
-        </is>
-      </c>
-      <c r="I13" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J13" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K13" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L13" s="101" t="inlineStr">
-        <is>
-          <t>Visita 14 sep. Reuniones deco sem 21 sep. Montaje dic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="103" t="inlineStr">
-        <is>
-          <t>IBIZA</t>
-        </is>
-      </c>
-      <c r="B14" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C14" s="51" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="inlineStr">
-        <is>
-          <t>Obra parada (municipio)</t>
-        </is>
-      </c>
-      <c r="E14" s="51" t="inlineStr">
-        <is>
-          <t>Reanudar sep · Preparar deco</t>
-        </is>
-      </c>
-      <c r="F14" s="51" t="inlineStr">
-        <is>
-          <t>Dic 2026</t>
-        </is>
-      </c>
-      <c r="G14" s="51" t="inlineStr">
-        <is>
-          <t>Obra parada por municipio. Pagos pendientes clientes.</t>
-        </is>
-      </c>
-      <c r="H14" s="51" t="inlineStr">
-        <is>
-          <t>Albañil local</t>
-        </is>
-      </c>
-      <c r="I14" s="51" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="J14" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K14" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L14" s="51" t="inlineStr">
-        <is>
-          <t>Parada hasta sep. Arrancar proy deco al reanudar. Montaje dic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="103" t="inlineStr">
-        <is>
-          <t>HERMOSILLA</t>
-        </is>
-      </c>
-      <c r="B15" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C15" s="51" t="inlineStr">
-        <is>
-          <t>Nela/Olatz</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="E15" s="51" t="inlineStr">
-        <is>
-          <t>Olatz contactar cliente al volver</t>
-        </is>
-      </c>
-      <c r="F15" s="51" t="inlineStr">
-        <is>
-          <t>Mar 2027</t>
-        </is>
-      </c>
-      <c r="G15" s="51" t="inlineStr">
-        <is>
-          <t>Sin info de cliente ni constructora</t>
-        </is>
-      </c>
-      <c r="H15" s="51" t="inlineStr">
-        <is>
-          <t>Raumplan</t>
-        </is>
-      </c>
-      <c r="I15" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J15" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K15" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L15" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias. Olatz contactar al volver.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="99" t="inlineStr">
-        <is>
-          <t>MONTESQUINZA</t>
-        </is>
-      </c>
-      <c r="B16" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C16" s="101" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="D16" s="101" t="inlineStr">
-        <is>
-          <t>Obra en ejecución</t>
-        </is>
-      </c>
-      <c r="E16" s="101" t="inlineStr">
-        <is>
-          <t>Revisar notificación licencia/DR</t>
-        </is>
-      </c>
-      <c r="F16" s="101" t="inlineStr">
-        <is>
-          <t>Mar 2027</t>
-        </is>
-      </c>
-      <c r="G16" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Notificación licencia/DR recibida pendiente revisar</t>
-        </is>
-      </c>
-      <c r="H16" s="101" t="inlineStr">
-        <is>
-          <t>Consultores Proy.</t>
-        </is>
-      </c>
-      <c r="I16" s="101" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J16" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K16" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L16" s="101" t="inlineStr">
-        <is>
-          <t>Obra avanzando. Notificación DR — revisar urgente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="103" t="inlineStr">
-        <is>
-          <t>GAMAL STO. DOMINGO</t>
-        </is>
-      </c>
-      <c r="B17" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C17" s="51" t="inlineStr">
-        <is>
-          <t>Sofía/Olatz</t>
-        </is>
-      </c>
-      <c r="D17" s="51" t="inlineStr">
-        <is>
-          <t>Montaje realizado</t>
-        </is>
-      </c>
-      <c r="E17" s="51" t="inlineStr">
-        <is>
-          <t>Confirmar remates o cierre</t>
-        </is>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J17" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K17" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L17" s="51" t="inlineStr">
-        <is>
-          <t>Montaje realizado. Confirmar si hay remates o se cierra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="99" t="inlineStr">
-        <is>
-          <t>CAMINO SUR 70</t>
-        </is>
-      </c>
-      <c r="B18" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C18" s="101" t="inlineStr">
-        <is>
-          <t>Cristina/Nela</t>
-        </is>
-      </c>
-      <c r="D18" s="101" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E18" s="101" t="inlineStr">
-        <is>
-          <t>Fallos Contraluz iluminación</t>
-        </is>
-      </c>
-      <c r="F18" s="101" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G18" s="101" t="inlineStr">
-        <is>
-          <t>Fallos grandes Contraluz. Remates papel pendientes.</t>
-        </is>
-      </c>
-      <c r="H18" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" s="101" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J18" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K18" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L18" s="101" t="inlineStr">
-        <is>
-          <t>Visita clientes 1 sep. Fallos Contraluz iluminación. Remates papel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="103" t="inlineStr">
-        <is>
-          <t>CAMINO SUR 35</t>
-        </is>
-      </c>
-      <c r="B19" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C19" s="51" t="inlineStr">
-        <is>
-          <t>Nela</t>
-        </is>
-      </c>
-      <c r="D19" s="51" t="inlineStr">
-        <is>
-          <t>Renders en curso</t>
-        </is>
-      </c>
-      <c r="E19" s="51" t="inlineStr">
-        <is>
-          <t>6 fases de renders — sin deco todavía</t>
-        </is>
-      </c>
-      <c r="F19" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G19" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="51" t="inlineStr">
-        <is>
-          <t>Project Work</t>
-        </is>
-      </c>
-      <c r="I19" s="51" t="inlineStr">
-        <is>
-          <t>RENDERS</t>
-        </is>
-      </c>
-      <c r="J19" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K19" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L19" s="51" t="inlineStr">
-        <is>
-          <t>Pancho con correcciones renders (6 fases). Sin deco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="103" t="inlineStr">
-        <is>
-          <t>TORRE VALENCIA</t>
-        </is>
-      </c>
-      <c r="B20" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C20" s="51" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D20" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E20" s="51" t="inlineStr">
-        <is>
-          <t>Paula visita próxima sem</t>
-        </is>
-      </c>
-      <c r="F20" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G20" s="51" t="inlineStr">
-        <is>
-          <t>Cliente sin decisiones domótica</t>
-        </is>
-      </c>
-      <c r="H20" s="51" t="inlineStr">
-        <is>
-          <t>Ecobuild</t>
-        </is>
-      </c>
-      <c r="I20" s="51" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J20" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K20" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L20" s="51" t="inlineStr">
-        <is>
-          <t>Replanteo iluminación realizado. Cliente sin decisiones domótica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="103" t="inlineStr">
-        <is>
-          <t>PASEO LAGOS 105</t>
-        </is>
-      </c>
-      <c r="B21" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="inlineStr">
-        <is>
-          <t>Sara/Andrea</t>
-        </is>
-      </c>
-      <c r="D21" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto básico</t>
-        </is>
-      </c>
-      <c r="E21" s="51" t="inlineStr">
-        <is>
-          <t>Reunión 15 sep · renders + presentación</t>
-        </is>
-      </c>
-      <c r="F21" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G21" s="51" t="inlineStr">
-        <is>
-          <t>Obra retrasa a ppios 2027 (humedades)</t>
-        </is>
-      </c>
-      <c r="H21" s="51" t="inlineStr">
-        <is>
-          <t>Raúl/Jamena</t>
-        </is>
-      </c>
-      <c r="I21" s="51" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="J21" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K21" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L21" s="51" t="inlineStr">
-        <is>
-          <t>Reunión 15 sep. Obra ppios 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="103" t="inlineStr">
-        <is>
-          <t>VALCARCE</t>
-        </is>
-      </c>
-      <c r="B22" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C22" s="51" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D22" s="51" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E22" s="51" t="inlineStr">
-        <is>
-          <t>Remates papel y Raúl pendientes</t>
-        </is>
-      </c>
-      <c r="F22" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="51" t="inlineStr">
-        <is>
-          <t>David (empapelador) da largas</t>
-        </is>
-      </c>
-      <c r="H22" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J22" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K22" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L22" s="51" t="inlineStr">
-        <is>
-          <t>Remates papel (David). Remates Raúl: cliente espere 2 semanas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="103" t="inlineStr">
-        <is>
-          <t>PESQUERA</t>
-        </is>
-      </c>
-      <c r="B23" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C23" s="51" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D23" s="51" t="inlineStr">
-        <is>
-          <t>Pedidos</t>
-        </is>
-      </c>
-      <c r="E23" s="51" t="inlineStr">
-        <is>
-          <t>Deco en oficina pendiente enviar</t>
-        </is>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
-        <is>
-          <t>Dic 2026</t>
-        </is>
-      </c>
-      <c r="G23" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="51" t="inlineStr">
-        <is>
-          <t>PEDIDOS</t>
-        </is>
-      </c>
-      <c r="J23" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K23" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L23" s="51" t="inlineStr">
-        <is>
-          <t>Deco en oficina pdte enviar. Constructora en marcha. Cliente: navidades.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="99" t="inlineStr">
-        <is>
-          <t>PASEO LAGOS 121</t>
-        </is>
-      </c>
-      <c r="B24" s="100" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C24" s="101" t="inlineStr">
-        <is>
-          <t>Olatz</t>
-        </is>
-      </c>
-      <c r="D24" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto deco</t>
-        </is>
-      </c>
-      <c r="E24" s="101" t="inlineStr">
-        <is>
-          <t>Reunión 2 sep · Presentación Nela</t>
-        </is>
-      </c>
-      <c r="F24" s="101" t="inlineStr">
-        <is>
-          <t>Feb 2027</t>
-        </is>
-      </c>
-      <c r="G24" s="101" t="inlineStr">
-        <is>
-          <t>Presentación pendiente revisión Ale — URGENTE</t>
-        </is>
-      </c>
-      <c r="H24" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="101" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="J24" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K24" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L24" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Reunión 2 sep. Presentación Nela — Ale revisar URGENTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="103" t="inlineStr">
-        <is>
-          <t>VIV PALOMA RD</t>
-        </is>
-      </c>
-      <c r="B25" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C25" s="51" t="inlineStr">
-        <is>
-          <t>Olatz/Andrea</t>
-        </is>
-      </c>
-      <c r="D25" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto deco</t>
-        </is>
-      </c>
-      <c r="E25" s="51" t="inlineStr">
-        <is>
-          <t>Reunión septiembre</t>
-        </is>
-      </c>
-      <c r="F25" s="51" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G25" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="51" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="J25" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K25" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L25" s="51" t="inlineStr">
-        <is>
-          <t>Reunión agosto con Ale. Siguiente sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="103" t="inlineStr">
-        <is>
-          <t>TEPEYAC</t>
-        </is>
-      </c>
-      <c r="B26" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C26" s="51" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D26" s="51" t="inlineStr">
-        <is>
-          <t>Parado</t>
-        </is>
-      </c>
-      <c r="E26" s="51" t="inlineStr">
-        <is>
-          <t>Reunión pendiente Raúl+Paula+cliente</t>
-        </is>
-      </c>
-      <c r="F26" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G26" s="51" t="inlineStr">
-        <is>
-          <t>Sin reunión programada</t>
-        </is>
-      </c>
-      <c r="H26" s="51" t="inlineStr">
-        <is>
-          <t>Raúl</t>
-        </is>
-      </c>
-      <c r="I26" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J26" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K26" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L26" s="51" t="inlineStr">
-        <is>
-          <t>Parado. Reunión pdte para presupuesto obra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="103" t="inlineStr">
-        <is>
-          <t>ABUBILLA</t>
-        </is>
-      </c>
-      <c r="B27" s="104" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C27" s="51" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D27" s="51" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E27" s="51" t="inlineStr">
-        <is>
-          <t>Semana del 7 sep</t>
-        </is>
-      </c>
-      <c r="F27" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G27" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J27" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K27" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L27" s="51" t="inlineStr">
-        <is>
-          <t>Remates sofá y cortinas. Semana del 7 sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="106" t="inlineStr">
-        <is>
-          <t>FOX + LA DESPENSA</t>
-        </is>
-      </c>
-      <c r="B28" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C28" s="51" t="inlineStr">
-        <is>
-          <t>Sofía/Naiara</t>
-        </is>
-      </c>
-      <c r="D28" s="51" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E28" s="51" t="inlineStr">
-        <is>
-          <t>Apertura 23 sep</t>
-        </is>
-      </c>
-      <c r="F28" s="51" t="inlineStr">
-        <is>
-          <t>23 sep</t>
-        </is>
-      </c>
-      <c r="G28" s="51" t="inlineStr">
-        <is>
-          <t>Amboage pendiente antes del 17 sep</t>
-        </is>
-      </c>
-      <c r="H28" s="51" t="inlineStr">
-        <is>
-          <t>Amboage</t>
-        </is>
-      </c>
-      <c r="I28" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J28" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K28" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L28" s="51" t="inlineStr">
-        <is>
-          <t>Amboage pdte antes 17 sep. Apertura 23 sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="108" t="inlineStr">
-        <is>
-          <t>PUERTO RICO</t>
-        </is>
-      </c>
-      <c r="B29" s="109" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C29" s="101" t="inlineStr">
-        <is>
-          <t>Sofía</t>
-        </is>
-      </c>
-      <c r="D29" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E29" s="101" t="inlineStr">
-        <is>
-          <t>Mediciones 2ª sem oct</t>
-        </is>
-      </c>
-      <c r="F29" s="101" t="inlineStr">
-        <is>
-          <t>Mar/Abr 2027</t>
-        </is>
-      </c>
-      <c r="G29" s="101" t="inlineStr">
-        <is>
-          <t>Decidir carpintero (Amboage descartado)</t>
-        </is>
-      </c>
-      <c r="H29" s="101" t="inlineStr">
-        <is>
-          <t>Amboage(pdte cambio)</t>
-        </is>
-      </c>
-      <c r="I29" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J29" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K29" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L29" s="101" t="inlineStr">
-        <is>
-          <t>Mediciones oct. Fab nov-ene. Instalación feb. Apertura mar/abr.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="106" t="inlineStr">
-        <is>
-          <t>RUBAIYAT MADRID</t>
-        </is>
-      </c>
-      <c r="B30" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C30" s="51" t="inlineStr">
-        <is>
-          <t>Naiara</t>
-        </is>
-      </c>
-      <c r="D30" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto deco</t>
-        </is>
-      </c>
-      <c r="E30" s="51" t="inlineStr">
-        <is>
-          <t>Cerrar deco terraza sem sep</t>
-        </is>
-      </c>
-      <c r="F30" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G30" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="51" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="J30" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K30" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L30" s="51" t="inlineStr">
-        <is>
-          <t>Cerrando deco terraza. Cortina, mueble, ampliación. Terminar sem sep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="108" t="inlineStr">
-        <is>
-          <t>RUBAIYAT SÃO PAULO</t>
-        </is>
-      </c>
-      <c r="B31" s="109" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C31" s="101" t="inlineStr">
-        <is>
-          <t>Naiara</t>
-        </is>
-      </c>
-      <c r="D31" s="101" t="inlineStr">
-        <is>
-          <t>Anteproyecto</t>
-        </is>
-      </c>
-      <c r="E31" s="101" t="inlineStr">
-        <is>
-          <t>Viaje 29 sep (2 noches)</t>
-        </is>
-      </c>
-      <c r="F31" s="101" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G31" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="101" t="inlineStr">
-        <is>
-          <t>Constructora local</t>
-        </is>
-      </c>
-      <c r="I31" s="101" t="inlineStr">
-        <is>
-          <t>ANT.PROY</t>
-        </is>
-      </c>
-      <c r="J31" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K31" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L31" s="101" t="inlineStr">
-        <is>
-          <t>Preparar anteproyecto. Revisión ~22 sep. Viaje 29 sep. Obra enero por fases.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="106" t="inlineStr">
-        <is>
-          <t>BERNABÉU</t>
-        </is>
-      </c>
-      <c r="B32" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C32" s="51" t="inlineStr">
-        <is>
-          <t>Naiara</t>
-        </is>
-      </c>
-      <c r="D32" s="51" t="inlineStr">
-        <is>
-          <t>Terminado — pendiente cierre</t>
-        </is>
-      </c>
-      <c r="E32" s="51" t="inlineStr">
-        <is>
-          <t>Cierre oficial: números + mesa + perchas</t>
-        </is>
-      </c>
-      <c r="F32" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G32" s="51" t="inlineStr">
-        <is>
-          <t>Mesas estropeadas: decisión cliente pendiente</t>
-        </is>
-      </c>
-      <c r="H32" s="51" t="inlineStr">
-        <is>
-          <t>Consultores Proy.</t>
-        </is>
-      </c>
-      <c r="I32" s="51" t="inlineStr">
-        <is>
-          <t>CIERRE</t>
-        </is>
-      </c>
-      <c r="J32" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K32" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L32" s="51" t="inlineStr">
-        <is>
-          <t>Terminado. Pendiente cierre oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="108" t="inlineStr">
-        <is>
-          <t>MALLORCA SEVILLA</t>
-        </is>
-      </c>
-      <c r="B33" s="109" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C33" s="101" t="inlineStr">
-        <is>
-          <t>Sofía/Naiara</t>
-        </is>
-      </c>
-      <c r="D33" s="101" t="inlineStr">
-        <is>
-          <t>Obra</t>
-        </is>
-      </c>
-      <c r="E33" s="101" t="inlineStr">
-        <is>
-          <t>Reunión 1 sep · A construir</t>
-        </is>
-      </c>
-      <c r="F33" s="101" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G33" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="101" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J33" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K33" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L33" s="101" t="inlineStr">
-        <is>
-          <t>Licencia concedida. Demolición hecha. A construir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="106" t="inlineStr">
-        <is>
-          <t>HIPÓDROMO</t>
-        </is>
-      </c>
-      <c r="B34" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C34" s="51" t="inlineStr">
-        <is>
-          <t>Sofía/Naiara</t>
-        </is>
-      </c>
-      <c r="D34" s="51" t="inlineStr">
-        <is>
-          <t>Pendiente licencia</t>
-        </is>
-      </c>
-      <c r="E34" s="51" t="inlineStr">
-        <is>
-          <t>Hablar con María PM</t>
-        </is>
-      </c>
-      <c r="F34" s="51" t="inlineStr">
-        <is>
-          <t>Pdte</t>
-        </is>
-      </c>
-      <c r="G34" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias</t>
-        </is>
-      </c>
-      <c r="H34" s="51" t="inlineStr">
-        <is>
-          <t>4 constructoras</t>
-        </is>
-      </c>
-      <c r="I34" s="51" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="J34" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K34" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L34" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias. Pendiente hablar con María PM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="106" t="inlineStr">
-        <is>
-          <t>VIV JOANN (Anteproy.)</t>
-        </is>
-      </c>
-      <c r="B35" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C35" s="51" t="inlineStr">
-        <is>
-          <t>Sofía</t>
-        </is>
-      </c>
-      <c r="D35" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto básico</t>
-        </is>
-      </c>
-      <c r="E35" s="51" t="inlineStr">
-        <is>
-          <t>Arrancando PB</t>
-        </is>
-      </c>
-      <c r="F35" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G35" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="51" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="J35" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K35" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L35" s="51" t="inlineStr">
-        <is>
-          <t>Arrancando PB. Planning enviado. Obra desde 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="108" t="inlineStr">
-        <is>
-          <t>COBUE</t>
-        </is>
-      </c>
-      <c r="B36" s="109" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C36" s="101" t="inlineStr">
-        <is>
-          <t>Sofía/Naiara</t>
-        </is>
-      </c>
-      <c r="D36" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto entregado · licitando</t>
-        </is>
-      </c>
-      <c r="E36" s="101" t="inlineStr">
-        <is>
-          <t>Apertura 21 enero</t>
-        </is>
-      </c>
-      <c r="F36" s="101" t="inlineStr">
-        <is>
-          <t>21 ene</t>
-        </is>
-      </c>
-      <c r="G36" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="101" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J36" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K36" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L36" s="101" t="inlineStr">
-        <is>
-          <t>Entrega valoración+renders esta sem. Licitando. Apertura 21 ene.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="106" t="inlineStr">
-        <is>
-          <t>PASEO LAGOS 132</t>
-        </is>
-      </c>
-      <c r="B37" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C37" s="51" t="inlineStr">
-        <is>
-          <t>Sofía/Naiara</t>
-        </is>
-      </c>
-      <c r="D37" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E37" s="51" t="inlineStr">
-        <is>
-          <t>Cerrar acabados y definiciones</t>
-        </is>
-      </c>
-      <c r="F37" s="51" t="inlineStr">
-        <is>
-          <t>May 2027</t>
-        </is>
-      </c>
-      <c r="G37" s="51" t="inlineStr">
-        <is>
-          <t>Pendiente cerrar acabados, techos, carpintería, iluminación</t>
-        </is>
-      </c>
-      <c r="H37" s="51" t="inlineStr">
-        <is>
-          <t>Ferbocar</t>
-        </is>
-      </c>
-      <c r="I37" s="51" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J37" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K37" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L37" s="51" t="inlineStr">
-        <is>
-          <t>Pendiente cerrar: acabados, techos, carpintería, iluminación, domótica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="106" t="inlineStr">
-        <is>
-          <t>CARBON</t>
-        </is>
-      </c>
-      <c r="B38" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C38" s="51" t="inlineStr">
-        <is>
-          <t>Sofía</t>
-        </is>
-      </c>
-      <c r="D38" s="51" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E38" s="51" t="inlineStr">
-        <is>
-          <t>Ejecutar aislamiento acústico</t>
-        </is>
-      </c>
-      <c r="F38" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G38" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="51" t="inlineStr">
-        <is>
-          <t>Empresa acústica</t>
-        </is>
-      </c>
-      <c r="I38" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J38" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K38" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L38" s="51" t="inlineStr">
-        <is>
-          <t>Remate aislamiento acústico pendiente de ejecutar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="106" t="inlineStr">
-        <is>
-          <t>CLÍNICA LONGEVIDAD</t>
-        </is>
-      </c>
-      <c r="B39" s="107" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C39" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="51" t="inlineStr">
-        <is>
-          <t>Sin novedades</t>
-        </is>
-      </c>
-      <c r="E39" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="51" t="inlineStr">
-        <is>
-          <t>Sin feedback clientes</t>
-        </is>
-      </c>
-      <c r="H39" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J39" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K39" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L39" s="51" t="inlineStr">
-        <is>
-          <t>Sin novedades.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="110" t="inlineStr">
-        <is>
-          <t>DON RAMÓN</t>
-        </is>
-      </c>
-      <c r="B40" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C40" s="51" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>Remates</t>
-        </is>
-      </c>
-      <c r="E40" s="51" t="inlineStr">
-        <is>
-          <t>Revisión remates montaje 1 sep</t>
-        </is>
-      </c>
-      <c r="F40" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G40" s="51" t="inlineStr">
-        <is>
-          <t>Problema mueble cocinas/carpintero (no resp. estudio)</t>
-        </is>
-      </c>
-      <c r="H40" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="51" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-      <c r="J40" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K40" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L40" s="51" t="inlineStr">
-        <is>
-          <t>Montaje 1 sep realizado. Marta y Ale. Revisión remates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="112" t="inlineStr">
-        <is>
-          <t>ONE SHOT BILBAO</t>
-        </is>
-      </c>
-      <c r="B41" s="113" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C41" s="101" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D41" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E41" s="101" t="inlineStr">
-        <is>
-          <t>Montaje fin oct</t>
-        </is>
-      </c>
-      <c r="F41" s="101" t="inlineStr">
-        <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="G41" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Cliente+MO cambiaron elementos unilateralmente</t>
-        </is>
-      </c>
-      <c r="H41" s="101" t="inlineStr">
-        <is>
-          <t>Martínez Otero</t>
-        </is>
-      </c>
-      <c r="I41" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J41" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K41" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L41" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Hablar con MO. Fin oct. Visita 1-2 días montaje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="110" t="inlineStr">
-        <is>
-          <t>ROCA MAYA</t>
-        </is>
-      </c>
-      <c r="B42" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C42" s="51" t="inlineStr">
-        <is>
-          <t>Marta/Jesús</t>
-        </is>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E42" s="51" t="inlineStr">
-        <is>
-          <t>Detalles listos sep → fabricar</t>
-        </is>
-      </c>
-      <c r="F42" s="51" t="inlineStr">
-        <is>
-          <t>Sem Santa</t>
-        </is>
-      </c>
-      <c r="G42" s="51" t="inlineStr">
-        <is>
-          <t>Sin detalle de climatización</t>
-        </is>
-      </c>
-      <c r="H42" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="51" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J42" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K42" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L42" s="51" t="inlineStr">
-        <is>
-          <t>Muestras OK. Detalles listos sep→fabricar. Entrega Sem Santa: hab→ZZCC→azotea.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="110" t="inlineStr">
-        <is>
-          <t>HOTEL ÚNICO BCN</t>
-        </is>
-      </c>
-      <c r="B43" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C43" s="51" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D43" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E43" s="51" t="inlineStr">
-        <is>
-          <t>Entregar todo sep y licitar</t>
-        </is>
-      </c>
-      <c r="F43" s="51" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G43" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="51" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J43" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K43" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L43" s="51" t="inlineStr">
-        <is>
-          <t>Fichas técnicas definidas. Auna propuesto proveedor. Entregar sep y licitar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="112" t="inlineStr">
-        <is>
-          <t>VÍA 66</t>
-        </is>
-      </c>
-      <c r="B44" s="113" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C44" s="101" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D44" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E44" s="101" t="inlineStr">
-        <is>
-          <t>Entregadas 2ª+3ª plantas. ZZCC fase 2 enero</t>
-        </is>
-      </c>
-      <c r="F44" s="101" t="inlineStr">
-        <is>
-          <t>Ene 2027</t>
-        </is>
-      </c>
-      <c r="G44" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Error interno muebles tipo. MO con retrasos.</t>
-        </is>
-      </c>
-      <c r="H44" s="101" t="inlineStr">
-        <is>
-          <t>Martínez Otero</t>
-        </is>
-      </c>
-      <c r="I44" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J44" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K44" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L44" s="101" t="inlineStr">
-        <is>
-          <t>⚠ Muebles necesitan adaptación por habitación. ZZCC fase 2 enero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="112" t="inlineStr">
-        <is>
-          <t>PSN PORTAL</t>
-        </is>
-      </c>
-      <c r="B45" s="113" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C45" s="101" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D45" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E45" s="101" t="inlineStr">
-        <is>
-          <t>Entrega sep · Obra 1 nov</t>
-        </is>
-      </c>
-      <c r="F45" s="101" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G45" s="101" t="inlineStr">
-        <is>
-          <t>Pendiente revisión Ale antes de entregar</t>
-        </is>
-      </c>
-      <c r="H45" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J45" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K45" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L45" s="101" t="inlineStr">
-        <is>
-          <t>Entrega sep. Valoración Raúl fin sep. Obra 1 nov.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="112" t="inlineStr">
-        <is>
-          <t>CASA ALMAGRO</t>
-        </is>
-      </c>
-      <c r="B46" s="113" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C46" s="101" t="inlineStr">
-        <is>
-          <t>Jesús/Marta</t>
-        </is>
-      </c>
-      <c r="D46" s="101" t="inlineStr">
-        <is>
-          <t>Proyecto ejecución</t>
-        </is>
-      </c>
-      <c r="E46" s="101" t="inlineStr">
-        <is>
-          <t>Obra mediados nov/ppios dic</t>
-        </is>
-      </c>
-      <c r="F46" s="101" t="inlineStr">
-        <is>
-          <t>Feb 2027</t>
-        </is>
-      </c>
-      <c r="G46" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="101" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J46" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="K46" s="102" t="inlineStr">
-        <is>
-          <t>ATENCIÓN ALTA</t>
-        </is>
-      </c>
-      <c r="L46" s="101" t="inlineStr">
-        <is>
-          <t>Kickoff realizado. Restaurante hotel Madrid. Obra nov/dic. ~2 meses. 200k€.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="110" t="inlineStr">
-        <is>
-          <t>HOTEL SEVILLA</t>
-        </is>
-      </c>
-      <c r="B47" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C47" s="51" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D47" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto actualizado</t>
-        </is>
-      </c>
-      <c r="E47" s="51" t="inlineStr">
-        <is>
-          <t>Sin planning realista</t>
-        </is>
-      </c>
-      <c r="F47" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="51" t="inlineStr">
-        <is>
-          <t>Ampliación no aceptada. Obra casi parada.</t>
-        </is>
-      </c>
-      <c r="H47" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="51" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J47" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K47" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L47" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto actualizado. Ampliación no aceptada. Obra casi parada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="110" t="inlineStr">
-        <is>
-          <t>HOTEL GIJÓN</t>
-        </is>
-      </c>
-      <c r="B48" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C48" s="51" t="inlineStr">
-        <is>
-          <t>Marta/Jesús</t>
-        </is>
-      </c>
-      <c r="D48" s="51" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E48" s="51" t="inlineStr">
-        <is>
-          <t>Pendiente últimos planos instalaciones</t>
-        </is>
-      </c>
-      <c r="F48" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="51" t="inlineStr">
-        <is>
-          <t>Problemas instalaciones condicionan techos</t>
-        </is>
-      </c>
-      <c r="H48" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J48" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K48" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L48" s="51" t="inlineStr">
-        <is>
-          <t>Problemas instalaciones. Pendiente últimos planos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="110" t="inlineStr">
-        <is>
-          <t>VINCCI VALENCIA</t>
-        </is>
-      </c>
-      <c r="B49" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C49" s="51" t="inlineStr">
-        <is>
-          <t>Marta/Jesús</t>
-        </is>
-      </c>
-      <c r="D49" s="51" t="inlineStr">
-        <is>
-          <t>Proyecto entregado</t>
-        </is>
-      </c>
-      <c r="E49" s="51" t="inlineStr">
-        <is>
-          <t>Piloto enero 2027</t>
-        </is>
-      </c>
-      <c r="F49" s="51" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G49" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="51" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J49" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K49" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L49" s="51" t="inlineStr">
-        <is>
-          <t>Piloto enero 2027. Montaje final jul/ago 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="110" t="inlineStr">
-        <is>
-          <t>MARTÍNEZ CAMPOS</t>
-        </is>
-      </c>
-      <c r="B50" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C50" s="51" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D50" s="51" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E50" s="51" t="inlineStr">
-        <is>
-          <t>Reunión cuando vuelva Jesús</t>
-        </is>
-      </c>
-      <c r="F50" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G50" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias</t>
-        </is>
-      </c>
-      <c r="H50" s="51" t="inlineStr">
-        <is>
-          <t>Raúl (previsto)</t>
-        </is>
-      </c>
-      <c r="I50" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J50" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K50" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L50" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="110" t="inlineStr">
-        <is>
-          <t>CASA KORREOS</t>
-        </is>
-      </c>
-      <c r="B51" s="111" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C51" s="51" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D51" s="51" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E51" s="51" t="inlineStr">
-        <is>
-          <t>Reunión cuando vuelva Jesús</t>
-        </is>
-      </c>
-      <c r="F51" s="51" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G51" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias</t>
-        </is>
-      </c>
-      <c r="H51" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="51" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J51" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="K51" s="105" t="inlineStr">
-        <is>
-          <t>SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="L51" s="51" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="114" t="inlineStr">
-        <is>
-          <t>GONZALO CÓRDOBA</t>
-        </is>
-      </c>
-      <c r="B52" s="115" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C52" s="116" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D52" s="116" t="inlineStr">
-        <is>
-          <t>Supervisión</t>
-        </is>
-      </c>
-      <c r="E52" s="116" t="inlineStr">
-        <is>
-          <t>Consultas puntuales</t>
-        </is>
-      </c>
-      <c r="F52" s="116" t="inlineStr">
-        <is>
-          <t>Continuo</t>
-        </is>
-      </c>
-      <c r="G52" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="116" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J52" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="K52" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="L52" s="116" t="inlineStr">
-        <is>
-          <t>Solo consultas puntuales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="114" t="inlineStr">
-        <is>
-          <t>AYALA OFICINAS</t>
-        </is>
-      </c>
-      <c r="B53" s="115" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C53" s="116" t="inlineStr">
-        <is>
-          <t>Ale/Jesús</t>
-        </is>
-      </c>
-      <c r="D53" s="116" t="inlineStr">
-        <is>
-          <t>Supervisión</t>
-        </is>
-      </c>
-      <c r="E53" s="116" t="inlineStr">
-        <is>
-          <t>Montaje diciembre</t>
-        </is>
-      </c>
-      <c r="F53" s="116" t="inlineStr">
-        <is>
-          <t>Dic 2026</t>
-        </is>
-      </c>
-      <c r="G53" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="116" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="J53" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="K53" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="L53" s="116" t="inlineStr">
-        <is>
-          <t>Presu deco entregado. Montaje diciembre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="114" t="inlineStr">
-        <is>
-          <t>KANDA SÁNCHEZ PACHECO</t>
-        </is>
-      </c>
-      <c r="B54" s="115" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C54" s="116" t="inlineStr">
-        <is>
-          <t>Jesús/Marta</t>
-        </is>
-      </c>
-      <c r="D54" s="116" t="inlineStr">
-        <is>
-          <t>Supervisión</t>
-        </is>
-      </c>
-      <c r="E54" s="116" t="inlineStr">
-        <is>
-          <t>Sin feedback</t>
-        </is>
-      </c>
-      <c r="F54" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="116" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J54" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="K54" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="L54" s="116" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="114" t="inlineStr">
-        <is>
-          <t>KANDA CATALINA SUÁREZ</t>
-        </is>
-      </c>
-      <c r="B55" s="115" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C55" s="116" t="inlineStr">
-        <is>
-          <t>Jesús/Marta</t>
-        </is>
-      </c>
-      <c r="D55" s="116" t="inlineStr">
-        <is>
-          <t>Supervisión</t>
-        </is>
-      </c>
-      <c r="E55" s="116" t="inlineStr">
-        <is>
-          <t>Sin feedback</t>
-        </is>
-      </c>
-      <c r="F55" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="116" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="116" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J55" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="K55" s="117" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="L55" s="116" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▸  LATENTES / EN ESPERA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="119" t="inlineStr">
-        <is>
-          <t>ANA HONTANAR</t>
-        </is>
-      </c>
-      <c r="B57" s="120" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C57" s="121" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D57" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E57" s="121" t="inlineStr">
-        <is>
-          <t>Después de verano</t>
-        </is>
-      </c>
-      <c r="F57" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J57" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K57" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L57" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="119" t="inlineStr">
-        <is>
-          <t>JAIME PESQUERA</t>
-        </is>
-      </c>
-      <c r="B58" s="120" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C58" s="121" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D58" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E58" s="121" t="inlineStr">
-        <is>
-          <t>Después de verano</t>
-        </is>
-      </c>
-      <c r="F58" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J58" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K58" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L58" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="119" t="inlineStr">
-        <is>
-          <t>HABITACIÓN ABI</t>
-        </is>
-      </c>
-      <c r="B59" s="120" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C59" s="121" t="inlineStr">
-        <is>
-          <t>Andrea</t>
-        </is>
-      </c>
-      <c r="D59" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E59" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J59" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K59" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L59" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="119" t="inlineStr">
-        <is>
-          <t>ANTIC COLONIAL</t>
-        </is>
-      </c>
-      <c r="B60" s="120" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C60" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E60" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J60" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K60" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L60" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="119" t="inlineStr">
-        <is>
-          <t>MONTALBÁN</t>
-        </is>
-      </c>
-      <c r="B61" s="120" t="inlineStr">
-        <is>
-          <t>VIVIENDA</t>
-        </is>
-      </c>
-      <c r="C61" s="121" t="inlineStr">
-        <is>
-          <t>Olatz</t>
-        </is>
-      </c>
-      <c r="D61" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E61" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J61" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K61" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L61" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="123" t="inlineStr">
-        <is>
-          <t>SANTANDER REST</t>
-        </is>
-      </c>
-      <c r="B62" s="124" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C62" s="121" t="inlineStr">
-        <is>
-          <t>Admón.</t>
-        </is>
-      </c>
-      <c r="D62" s="121" t="inlineStr">
-        <is>
-          <t>Gestión cobro</t>
-        </is>
-      </c>
-      <c r="E62" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="121" t="inlineStr">
-        <is>
-          <t>Disputa judicial</t>
-        </is>
-      </c>
-      <c r="H62" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J62" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K62" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L62" s="121" t="inlineStr">
-        <is>
-          <t>Gestión interna cobro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="123" t="inlineStr">
-        <is>
-          <t>JOANN DOMINICANA</t>
-        </is>
-      </c>
-      <c r="B63" s="124" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C63" s="121" t="inlineStr">
-        <is>
-          <t>Sofía</t>
-        </is>
-      </c>
-      <c r="D63" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E63" s="121" t="inlineStr">
-        <is>
-          <t>Pendiente entrar</t>
-        </is>
-      </c>
-      <c r="F63" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J63" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K63" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L63" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="123" t="inlineStr">
-        <is>
-          <t>SOPHIE</t>
-        </is>
-      </c>
-      <c r="B64" s="124" t="inlineStr">
-        <is>
-          <t>RESTAURANTES</t>
-        </is>
-      </c>
-      <c r="C64" s="121" t="inlineStr">
-        <is>
-          <t>Sofía</t>
-        </is>
-      </c>
-      <c r="D64" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E64" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J64" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K64" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L64" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="125" t="inlineStr">
-        <is>
-          <t>PANTANO RURAL</t>
-        </is>
-      </c>
-      <c r="B65" s="126" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C65" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E65" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J65" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K65" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L65" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="125" t="inlineStr">
-        <is>
-          <t>4 MASOS</t>
-        </is>
-      </c>
-      <c r="B66" s="126" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C66" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D66" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E66" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J66" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K66" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L66" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="125" t="inlineStr">
-        <is>
-          <t>BLESS</t>
-        </is>
-      </c>
-      <c r="B67" s="126" t="inlineStr">
-        <is>
-          <t>HOTELES</t>
-        </is>
-      </c>
-      <c r="C67" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D67" s="121" t="inlineStr">
-        <is>
-          <t>En espera</t>
-        </is>
-      </c>
-      <c r="E67" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="121" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J67" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="K67" s="122" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-      <c r="L67" s="121" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="127" t="inlineStr">
-        <is>
-          <t>Actualizado: 1 septiembre 2026  ·  51 proyectos activos  ·  11 latentes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="A69:L69"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A4:L4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5404,7 +1237,7 @@
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
         <is>
-          <t>Actualizado: 01/09/2026</t>
+          <t>Actualizado: 07/09/2026  ·  Sara de vacaciones 3-14 sep</t>
         </is>
       </c>
     </row>
@@ -5416,7 +1249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5454,20 +1287,15 @@
     <row r="2" ht="14" customHeight="1">
       <c r="G2" s="37" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="H2" s="37" t="inlineStr">
-        <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L2" s="37" t="inlineStr">
+      <c r="K2" s="37" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="P2" s="37" t="inlineStr">
+      <c r="O2" s="37" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
@@ -5506,57 +1334,57 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>1 SEP</t>
+          <t>7 SEP</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>8 SEP</t>
+          <t>14 SEP</t>
         </is>
       </c>
       <c r="I3" s="39" t="inlineStr">
         <is>
-          <t>15 SEP</t>
+          <t>21 SEP</t>
         </is>
       </c>
       <c r="J3" s="39" t="inlineStr">
         <is>
-          <t>22 SEP</t>
+          <t>28 SEP</t>
         </is>
       </c>
       <c r="K3" s="39" t="inlineStr">
         <is>
-          <t>29 SEP</t>
+          <t>5 OCT</t>
         </is>
       </c>
       <c r="L3" s="39" t="inlineStr">
         <is>
-          <t>6 OCT</t>
+          <t>12 OCT</t>
         </is>
       </c>
       <c r="M3" s="39" t="inlineStr">
         <is>
-          <t>13 OCT</t>
+          <t>19 OCT</t>
         </is>
       </c>
       <c r="N3" s="39" t="inlineStr">
         <is>
-          <t>20 OCT</t>
+          <t>26 OCT</t>
         </is>
       </c>
       <c r="O3" s="39" t="inlineStr">
         <is>
-          <t>27 OCT</t>
+          <t>2 NOV</t>
         </is>
       </c>
       <c r="P3" s="39" t="inlineStr">
         <is>
-          <t>3 NOV</t>
+          <t>9 NOV</t>
         </is>
       </c>
       <c r="Q3" s="39" t="inlineStr">
         <is>
-          <t>10 NOV</t>
+          <t>16 NOV</t>
         </is>
       </c>
     </row>
@@ -6429,22 +2257,6 @@
           <t xml:space="preserve">  LATENTES / PAUSADOS</t>
         </is>
       </c>
-      <c r="B17" s="128" t="n"/>
-      <c r="C17" s="128" t="n"/>
-      <c r="D17" s="128" t="n"/>
-      <c r="E17" s="128" t="n"/>
-      <c r="F17" s="128" t="n"/>
-      <c r="G17" s="128" t="n"/>
-      <c r="H17" s="128" t="n"/>
-      <c r="I17" s="128" t="n"/>
-      <c r="J17" s="128" t="n"/>
-      <c r="K17" s="128" t="n"/>
-      <c r="L17" s="128" t="n"/>
-      <c r="M17" s="128" t="n"/>
-      <c r="N17" s="128" t="n"/>
-      <c r="O17" s="128" t="n"/>
-      <c r="P17" s="128" t="n"/>
-      <c r="Q17" s="128" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="69" t="inlineStr"/>
@@ -6558,16 +2370,16 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A17:Q17"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6605,20 +2417,15 @@
     <row r="2" ht="14" customHeight="1">
       <c r="G2" s="37" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="H2" s="37" t="inlineStr">
-        <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L2" s="37" t="inlineStr">
+      <c r="K2" s="37" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="P2" s="37" t="inlineStr">
+      <c r="O2" s="37" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
@@ -6657,57 +2464,57 @@
       </c>
       <c r="G3" s="77" t="inlineStr">
         <is>
-          <t>1 SEP</t>
+          <t>7 SEP</t>
         </is>
       </c>
       <c r="H3" s="77" t="inlineStr">
         <is>
-          <t>8 SEP</t>
+          <t>14 SEP</t>
         </is>
       </c>
       <c r="I3" s="77" t="inlineStr">
         <is>
-          <t>15 SEP</t>
+          <t>21 SEP</t>
         </is>
       </c>
       <c r="J3" s="77" t="inlineStr">
         <is>
-          <t>22 SEP</t>
+          <t>28 SEP</t>
         </is>
       </c>
       <c r="K3" s="77" t="inlineStr">
         <is>
-          <t>29 SEP</t>
+          <t>5 OCT</t>
         </is>
       </c>
       <c r="L3" s="77" t="inlineStr">
         <is>
-          <t>6 OCT</t>
+          <t>12 OCT</t>
         </is>
       </c>
       <c r="M3" s="77" t="inlineStr">
         <is>
-          <t>13 OCT</t>
+          <t>19 OCT</t>
         </is>
       </c>
       <c r="N3" s="77" t="inlineStr">
         <is>
-          <t>20 OCT</t>
+          <t>26 OCT</t>
         </is>
       </c>
       <c r="O3" s="77" t="inlineStr">
         <is>
-          <t>27 OCT</t>
+          <t>2 NOV</t>
         </is>
       </c>
       <c r="P3" s="77" t="inlineStr">
         <is>
-          <t>3 NOV</t>
+          <t>9 NOV</t>
         </is>
       </c>
       <c r="Q3" s="77" t="inlineStr">
         <is>
-          <t>10 NOV</t>
+          <t>16 NOV</t>
         </is>
       </c>
     </row>
@@ -8413,22 +4220,6 @@
           <t xml:space="preserve">  LATENTES / PAUSADOS</t>
         </is>
       </c>
-      <c r="B28" s="129" t="n"/>
-      <c r="C28" s="129" t="n"/>
-      <c r="D28" s="129" t="n"/>
-      <c r="E28" s="129" t="n"/>
-      <c r="F28" s="129" t="n"/>
-      <c r="G28" s="129" t="n"/>
-      <c r="H28" s="129" t="n"/>
-      <c r="I28" s="129" t="n"/>
-      <c r="J28" s="129" t="n"/>
-      <c r="K28" s="129" t="n"/>
-      <c r="L28" s="129" t="n"/>
-      <c r="M28" s="129" t="n"/>
-      <c r="N28" s="129" t="n"/>
-      <c r="O28" s="129" t="n"/>
-      <c r="P28" s="129" t="n"/>
-      <c r="Q28" s="129" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="69" t="inlineStr">
@@ -8615,17 +4406,17 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8663,20 +4454,15 @@
     <row r="2" ht="14" customHeight="1">
       <c r="G2" s="37" t="inlineStr">
         <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="H2" s="37" t="inlineStr">
-        <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L2" s="37" t="inlineStr">
+      <c r="K2" s="37" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="P2" s="37" t="inlineStr">
+      <c r="O2" s="37" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
@@ -8715,57 +4501,57 @@
       </c>
       <c r="G3" s="90" t="inlineStr">
         <is>
-          <t>1 SEP</t>
+          <t>7 SEP</t>
         </is>
       </c>
       <c r="H3" s="90" t="inlineStr">
         <is>
-          <t>8 SEP</t>
+          <t>14 SEP</t>
         </is>
       </c>
       <c r="I3" s="90" t="inlineStr">
         <is>
-          <t>15 SEP</t>
+          <t>21 SEP</t>
         </is>
       </c>
       <c r="J3" s="90" t="inlineStr">
         <is>
-          <t>22 SEP</t>
+          <t>28 SEP</t>
         </is>
       </c>
       <c r="K3" s="90" t="inlineStr">
         <is>
-          <t>29 SEP</t>
+          <t>5 OCT</t>
         </is>
       </c>
       <c r="L3" s="90" t="inlineStr">
         <is>
-          <t>6 OCT</t>
+          <t>12 OCT</t>
         </is>
       </c>
       <c r="M3" s="90" t="inlineStr">
         <is>
-          <t>13 OCT</t>
+          <t>19 OCT</t>
         </is>
       </c>
       <c r="N3" s="90" t="inlineStr">
         <is>
-          <t>20 OCT</t>
+          <t>26 OCT</t>
         </is>
       </c>
       <c r="O3" s="90" t="inlineStr">
         <is>
-          <t>27 OCT</t>
+          <t>2 NOV</t>
         </is>
       </c>
       <c r="P3" s="90" t="inlineStr">
         <is>
-          <t>3 NOV</t>
+          <t>9 NOV</t>
         </is>
       </c>
       <c r="Q3" s="90" t="inlineStr">
         <is>
-          <t>10 NOV</t>
+          <t>16 NOV</t>
         </is>
       </c>
     </row>
@@ -9555,22 +5341,6 @@
           <t xml:space="preserve">  SUPERVISIÓN / SEGUIMIENTO PUNTUAL</t>
         </is>
       </c>
-      <c r="B16" s="130" t="n"/>
-      <c r="C16" s="130" t="n"/>
-      <c r="D16" s="130" t="n"/>
-      <c r="E16" s="130" t="n"/>
-      <c r="F16" s="130" t="n"/>
-      <c r="G16" s="130" t="n"/>
-      <c r="H16" s="130" t="n"/>
-      <c r="I16" s="130" t="n"/>
-      <c r="J16" s="130" t="n"/>
-      <c r="K16" s="130" t="n"/>
-      <c r="L16" s="130" t="n"/>
-      <c r="M16" s="130" t="n"/>
-      <c r="N16" s="130" t="n"/>
-      <c r="O16" s="130" t="n"/>
-      <c r="P16" s="130" t="n"/>
-      <c r="Q16" s="130" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="69" t="inlineStr">
@@ -9781,22 +5551,6 @@
           <t xml:space="preserve">  LATENTES / PAUSADOS</t>
         </is>
       </c>
-      <c r="B22" s="130" t="n"/>
-      <c r="C22" s="130" t="n"/>
-      <c r="D22" s="130" t="n"/>
-      <c r="E22" s="130" t="n"/>
-      <c r="F22" s="130" t="n"/>
-      <c r="G22" s="130" t="n"/>
-      <c r="H22" s="130" t="n"/>
-      <c r="I22" s="130" t="n"/>
-      <c r="J22" s="130" t="n"/>
-      <c r="K22" s="130" t="n"/>
-      <c r="L22" s="130" t="n"/>
-      <c r="M22" s="130" t="n"/>
-      <c r="N22" s="130" t="n"/>
-      <c r="O22" s="130" t="n"/>
-      <c r="P22" s="130" t="n"/>
-      <c r="Q22" s="130" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="69" t="inlineStr"/>
@@ -9910,10 +5664,10 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A22:Q22"/>
-    <mergeCell ref="H2:K2"/>
     <mergeCell ref="A16:Q16"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javo\APESTUDIO Dropbox\Carpeta del equipo APESTUDIO\999_PM\APDS ACTIVO\apds-pm-estudio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF5D48B-5176-4C2C-9AC6-7D033F12B39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF658DF2-B8E7-485E-9434-5345F9962066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER GLOBAL" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="543">
   <si>
     <t>PM ESTUDIO — MASTER GLOBAL  ·  19 octubre 2026</t>
   </si>
@@ -1650,18 +1650,6 @@
   </si>
   <si>
     <t>Dic'26</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>KANDA SÁNCHEZ PACHECO</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>KANDA CATALINA SUÁREZ</t>
   </si>
   <si>
     <t>06</t>
@@ -4404,8 +4392,8 @@
       <c r="B48" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="23" t="s">
-        <v>170</v>
+      <c r="C48" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>314</v>
@@ -4430,8 +4418,8 @@
       <c r="B49" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="23" t="s">
-        <v>170</v>
+      <c r="C49" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>317</v>
@@ -5212,6 +5200,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="28.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -7013,7 +7004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -7576,60 +7567,51 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>542</v>
+        <v>437</v>
       </c>
       <c r="B19" t="s">
-        <v>543</v>
-      </c>
-      <c r="C19" t="s">
-        <v>275</v>
-      </c>
-      <c r="D19" t="s">
-        <v>534</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>305</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>544</v>
-      </c>
-      <c r="B20" t="s">
-        <v>545</v>
-      </c>
-      <c r="C20" t="s">
-        <v>275</v>
-      </c>
-      <c r="D20" t="s">
-        <v>534</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>305</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>437</v>
-      </c>
       <c r="B21" t="s">
-        <v>438</v>
+        <v>343</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>439</v>
+        <v>542</v>
+      </c>
+      <c r="B22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -7638,37 +7620,6 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>546</v>
-      </c>
-      <c r="B24" t="s">
-        <v>344</v>
-      </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>345</v>
-      </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" t="s">
         <v>325</v>
       </c>
     </row>

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,6 +129,12 @@
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -185,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -302,6 +308,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -667,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,7 +698,6 @@
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -704,7 +713,6 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -757,37 +765,32 @@
           <t>ATENCIÓN</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="40" t="inlineStr">
         <is>
           <t>FIN OBRA PREVISTO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="40" t="inlineStr">
         <is>
           <t>MONTAJE PREVISTO</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="40" t="inlineStr">
         <is>
           <t>FINALIZACIÓN OFICIAL</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>OBSERVACIONES</t>
+          <t>DECO CERRADA</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>DECO CERRADA</t>
+          <t>PRESUPUESTO DECO ACEPTADO</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO DECO ACEPTADO</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>PEDIDOS CONFIRMADOS</t>
         </is>
@@ -811,7 +814,6 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -867,26 +869,6 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>Ampliación deco acordada. Montaje 23 oct. Olatz ejecutando pedidos.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -942,26 +924,6 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>Entregado. Mob. exterior mediados sep.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -976,7 +938,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Alicia/Javi</t>
+          <t>Javi</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1017,26 +979,6 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>Primera reunión cierre realizada. Listado remates elaborado.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1092,26 +1034,6 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>Deco organizada 2ª sem sep. Montaje última sem sep.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1175,26 +1097,6 @@
         </is>
       </c>
       <c r="M9" s="2" t="n"/>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>Todo pedido y en almacenes. CONTROLADO.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1250,26 +1152,6 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>Deco y presu listos. Standby hasta señal cliente.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1325,26 +1207,6 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>Primera reunión oct w4 pendiente. Definir responsable.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1404,26 +1266,6 @@
       </c>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>Reunión celebrada. Decisiones tomadas pero cliente no cierra. Pendiente calendario.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1489,26 +1331,6 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Feb 2027</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>Carpintería APROBADA por cliente. Planning deco activo semana a semana.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1566,26 +1388,6 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>Obra parada. Cliente sin respuesta — contactar urgente.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1641,26 +1443,6 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>Planos actualizados + baños enviados a constructora. PE por cerrar.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1716,26 +1498,6 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>Algunos remates fabricando en España. Sin fecha de entrega.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1791,26 +1553,6 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>Visita clientes 1 sep. Fallos Contraluz iluminación. Remates papel.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1870,26 +1612,6 @@
       </c>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>Reunión hoy. Renders retrasados — comunicar al cliente. Obra: ~2 años desde ahora (oct 2028).</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1945,26 +1667,6 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>Replanteo iluminación realizado. Cliente sin decisiones domótica.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -2020,26 +1722,6 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>Reunión renders pendiente. Mediciones sin actualizar para constructora.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -2095,26 +1777,6 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>Deco en oficina pdte enviar. Constructora en marcha. Cliente: navidades.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2180,26 +1842,6 @@
       <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Feb 2027</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>Avances en curso. Sin revisión Ale, reunión bloqueada.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2257,26 +1899,6 @@
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>Reunión agosto con Ale. Siguiente sep.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -2332,26 +1954,6 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>Parado. Reunión pdte para presupuesto obra.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
@@ -2407,11 +2009,6 @@
       <c r="K25" s="39" t="n"/>
       <c r="L25" s="39" t="n"/>
       <c r="M25" s="39" t="n"/>
-      <c r="N25" s="37" t="inlineStr">
-        <is>
-          <t>Nueva vivienda en Zahara. Honorarios aprobados. Reunión anteproy 14 oct. Constructora Raúl — solapar obra con Zahara Isabella.</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
@@ -2467,11 +2064,6 @@
       <c r="K26" s="39" t="n"/>
       <c r="L26" s="39" t="n"/>
       <c r="M26" s="39" t="n"/>
-      <c r="N26" s="37" t="inlineStr">
-        <is>
-          <t>Nueva vivienda en Zahara. Honorarios aprobados. Reunión anteproy 15 oct. Estrategia: solapar obra con Zahara Sergio.</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -2527,26 +2119,6 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="11" t="inlineStr">
-        <is>
-          <t>Queda mueble tocador. Amboage sin fecha. Posible proyecto nuevo de este cliente (pendiente confirmar).</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -2602,26 +2174,6 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>A la espera: confirmación pavimento + decisión techo (2 opciones enviadas ayer). Después: revisar capítulo completo carpintería. Luego: planificación.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -2677,26 +2229,6 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Reunión in situ realizada. Nueva distribución sacada y acordada. Tenemos una planta. Sin más material desarrollado por ahora.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
@@ -2756,26 +2288,6 @@
           <t>15 feb 2027</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>Distribución clara y cerrada. Compromiso entrega 1 mes (≈7 nov). Obra ene-feb, objetivo entrega 15 feb.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -2835,26 +2347,6 @@
       </c>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>Obra muy avanzada. Planos en planta actualizados. Alzados y detalles pendientes — urgente. Objetivo: terminar antes de fin de año.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -2910,26 +2402,6 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="11" t="inlineStr">
-        <is>
-          <t>Requerimiento Patrimonio. Respuesta preparándose. Plazo: ~17 oct.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
@@ -2985,26 +2457,6 @@
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>Reunión cocina+vestidor hoy. Mañana reunión clienta. PE parcial octubre: revestimientos, iluminación, techos, distribución. Carpintería, alzados y detalles: enero/febrero.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
@@ -3062,26 +2514,6 @@
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t>21 ene 2027</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>Obra arrancó el lunes 6 oct. Primera visita viernes 10 oct. Objetivo apertura 21 ene'27. 2 proyectos nuevos de revisión/asesoramiento implantaciones (por contrato).</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3119,7 +2551,6 @@
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
-      <c r="N35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
@@ -3175,26 +2606,6 @@
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="11" t="inlineStr">
-        <is>
-          <t>Reunión de obra todos los miércoles. Reunión con clienta: renders + cambios semana pasada. Acabados a cerrar a lo largo de octubre.</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
@@ -3258,26 +2669,6 @@
         </is>
       </c>
       <c r="M37" s="2" t="n"/>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>Fin obra 26 oct. Van Marta y Jesús. Montaje solapado ~1 mes sin fecha confirmada.</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -3337,26 +2728,6 @@
       </c>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
-      <c r="N38" s="11" t="inlineStr">
-        <is>
-          <t>Renders hab mandados. ZZ.CC./exterior pendientes. Marcar prioridades con renderista urgente.</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
@@ -3412,26 +2783,6 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>F1 cerrada. F2 ene'27: habitaciones + lobby (~3 meses). F3 verano'27: desayunador.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
@@ -3487,26 +2838,6 @@
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>Visita 6 oct (Jesús+Marta+Raúl). Presu esta semana — entrega 13 oct. Arrancar nov, duración 2-3 meses.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
@@ -3566,26 +2897,6 @@
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr">
-        <is>
-          <t>Adqua (hicieron Don Ramón) lo estudia. PE oct → valoración Adqua nov.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -3641,26 +2952,6 @@
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
-      <c r="N42" s="11" t="inlineStr">
-        <is>
-          <t>Sin planning actualizado. Originalmente marzo. Javier llama; sin respuesta → mail bomba.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -3716,26 +3007,6 @@
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
-      <c r="N43" s="11" t="inlineStr">
-        <is>
-          <t>Sin cambios. Temas estructurales condicionan proyecto.</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -3799,26 +3070,6 @@
         </is>
       </c>
       <c r="M44" s="2" t="n"/>
-      <c r="N44" s="11" t="inlineStr">
-        <is>
-          <t>En licitación mobiliario. San José ejecutando. Objetivo piloto ene'27. Fin jul'27.</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -3874,26 +3125,6 @@
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
-      <c r="N45" s="11" t="inlineStr">
-        <is>
-          <t>Textos enviados. Pendiente Patrimonio. Si cierra: PE 3 nov.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
@@ -3949,26 +3180,6 @@
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
-      <c r="N46" s="23" t="inlineStr">
-        <is>
-          <t>Alguna supervisión puntual. Actividad muy baja.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
@@ -3983,7 +3194,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Ale/Jesús</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -4024,24 +3235,9 @@
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
-      <c r="N47" s="23" t="inlineStr">
-        <is>
-          <t>Presupuesto aceptado. Pedidos iniciándose. Fin previsto ene'27.</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
           <t>SÍ</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -4079,7 +3275,6 @@
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
-      <c r="N48" s="23" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
@@ -4115,7 +3310,6 @@
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
-      <c r="N49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="25" t="inlineStr">
@@ -4135,151 +3329,122 @@
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="41" t="inlineStr">
         <is>
           <t>DON RAMÓN</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="41" t="inlineStr">
         <is>
           <t>HOTELES</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="41" t="inlineStr">
         <is>
           <t>Marta</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="41" t="inlineStr">
         <is>
           <t>Honorarios ampliación enviados</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="41" t="inlineStr">
         <is>
           <t>Pendiente confirmación cliente</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="41" t="inlineStr">
         <is>
           <t>No han contestado a honorarios. Ampliación para terraza.</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="H51" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="41" t="inlineStr">
         <is>
           <t>LATENTE</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="41" t="inlineStr">
         <is>
           <t>PARADO</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Ampliación para terraza. Sin respuesta honorarios. Sin avance.</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K51" s="41" t="n"/>
+      <c r="L51" s="41" t="n"/>
+      <c r="M51" s="41" t="n"/>
+      <c r="N51" s="41" t="n"/>
+      <c r="O51" s="41" t="n"/>
+      <c r="P51" s="41" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="41" t="inlineStr">
         <is>
           <t>HOTEL ÚNICO BCN</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>HOTELES</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="41" t="inlineStr">
         <is>
           <t>Marta</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="41" t="inlineStr">
         <is>
           <t>Pendiente licencia — sin previsión</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="41" t="inlineStr">
         <is>
           <t>Sin previsión de licencia · Valorando constructora y mobiliario</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="41" t="inlineStr">
         <is>
           <t>Sin señales. Parece que están sacando presu obra+mobiliario.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="H52" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="41" t="inlineStr">
         <is>
           <t>LATENTE</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="41" t="inlineStr">
         <is>
           <t>PARADO</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Sin señales de avance. Parece sacando presu obra+mobiliario internamente.</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="K52" s="41" t="n"/>
+      <c r="L52" s="41" t="n"/>
+      <c r="M52" s="41" t="n"/>
+      <c r="N52" s="41" t="n"/>
+      <c r="O52" s="41" t="n"/>
+      <c r="P52" s="41" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="26" t="inlineStr">
@@ -4335,26 +3500,6 @@
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
-      <c r="N53" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="26" t="inlineStr">
@@ -4410,26 +3555,6 @@
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
-      <c r="N54" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="26" t="inlineStr">
@@ -4485,26 +3610,6 @@
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
-      <c r="N55" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="26" t="inlineStr">
@@ -4560,26 +3665,6 @@
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
-      <c r="N56" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="30" t="inlineStr">
@@ -4635,26 +3720,6 @@
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
-      <c r="N57" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="30" t="inlineStr">
@@ -4710,26 +3775,6 @@
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
-      <c r="N58" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="32" t="inlineStr">
@@ -4785,26 +3830,6 @@
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
-      <c r="N59" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="32" t="inlineStr">
@@ -4860,26 +3885,6 @@
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
-      <c r="N60" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="32" t="inlineStr">
@@ -4935,26 +3940,6 @@
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
-      <c r="N61" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -4970,7 +3955,6 @@
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
-      <c r="N62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="34" t="inlineStr">
@@ -4990,7 +3974,6 @@
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5283,6 +4266,2811 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ALEJANDRA POMBO DESIGN STUDIO  ·  RESTAURANTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NOTAS / ESTADO ACTUAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FIN EST.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RIESGO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12 OCT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>19 OCT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>26 OCT</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2 NOV</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>9 NOV</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>16 NOV</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>23 NOV</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30 NOV</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7 DIC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>14 DIC</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21 DIC</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>28 DIC</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4 ENE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>11 ENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FOX + LA DESPENSA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Carpintero termina esta semana · Proyecto nuevo: japonés planta baja · Honorarios pdte aceptar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>REMATES</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>APERTURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PUERTO RICO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cambios de proyecto · Comunicado a cliente: fin proyecto jun/jul</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mar/Abr'27</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>VISITA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RUBAIYAT MADRID</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parado · Cliente centrado en Sao Paulo · En espera reactivación</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sep'26</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ENTREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RUBAIYAT SÃO PAULO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Básico esta semana · Ejecutivo en 2 semanas · Entrega anticipada al cliente</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>REVISIÓN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>VIAJE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ANT.PROY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MALLORCA SEVILLA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>⚠ Cerrar pedidos iluminación y cortinas ESTA SEMANA · Obra fin de año</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>REUNIÓN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HIPÓDROMO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Respuesta Patrimonio esta semana · Licitación constructora nov · Licencia ene/feb</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pdte</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VIV JOANN (Anteproy.)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PE parcial: ilum + suelos + revestimientos + techos · Entregar este mes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COBUE VALDEMARÍN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Obra iniciada · Apertura 21 ene · Terraza pdte · Mobiliario a encargar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>21 ene</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ENTREGA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COBUE AYALA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Seguimiento adaptación · Revisión completada · Cliente adapta nuestro proyecto a nuevos locales</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cont.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PASEO LAGOS 132</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Solados definidos · Revisar planos ya pasados</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>May'27</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAMINO SUR 35</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sofía/Naiara (Nela apoyo)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Reunión cliente esta semana · Renders cada 2 semanas · Avance parcial en 2 zonas</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>oct'28</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>🏖</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LATENTES / PAUSADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JOANN DOMINICANA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pendiente entrar.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PARADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SOPHIE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pendiente aceptación.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PARADO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ALEJANDRA POMBO DESIGN STUDIO  ·  VIVIENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROYECTO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NOTAS / ESTADO ACTUAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FIN EST.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RIESGO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12 OCT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>19 OCT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>26 OCT</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2 NOV</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>9 NOV</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>16 NOV</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>23 NOV</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30 NOV</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7 DIC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>14 DIC</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21 DIC</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>28 DIC</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4 ENE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>11 ENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PEDRAZA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Olatz/Paula</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Montaje jue 29 oct · Entrega vie 30 oct · Paisajismo + fases cuadras/jueces pdte (sin fechas)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>oct'26</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>REMATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sara/Andrea</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Exterior entregado hoy · Visita pdte cuando Raúl fabrique mueble barbacoa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sep'26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>REMATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ALCALÁ 58</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Javi</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Va retrasado. Comunicar nueva fecha al cliente hoy.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sep'26</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FIN OBRA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Corrección mueble pendiente · Paula informa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>oct'26</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>MONTAJE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MONTAJE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA RINCONADA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cristina/Nela</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Montaje 3 nov · Entrega 5 nov · Bancada cocina semana siguiente · Mesa salón pdte</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>nov'26</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>FIN OBRA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ENTREGA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VIUDA DE ALDAMA 3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nela/Andrea</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Reactiva: inicio en 3 semanas · Ampliación deco · Obra en curso</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>dic'26</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>REUNIÓN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VIUDA DE ALDAMA 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nuevo proyecto. Organizar con cliente en septiembre.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SANTANDER VIV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sara/Cristina/Andrea</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Proveedores casi todos con encargos · Suelo en 6 semanas mínimo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ene'27</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>VISITA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IBIZA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reunión 20 oct · Obra avanzando · Carpintero pendiente de cerrar</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ene'27</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>PDTE LIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nela/Olatz</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Actualización presu constructora · Reunión cliente semana 27 oct</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mar'27</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MONTE ESQUINZA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>⚠ Notificación licencia/DR — revisar. Obra avanzando.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mar'27</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GAMAL STO. DOMINGO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sofía/Olatz</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Montaje realizado. Confirmar remates o cierre.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>REMATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAMINO SUR 70</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cristina/Nela</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Interior termina esta semana · Mobiliario exterior en 3 semanas</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>oct'26</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>REMATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TORRE VALENCIA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Obra lenta · Irene contacta cliente para planificación</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pdte</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>REUNIÓN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASEO LAGOS 105</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nela/Andrea</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Reunión Raúl 20 oct · Valoración este mes · Obra nov · Renders semana que viene</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>mar'27</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>REUNIÓN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>PROY B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PESQUERA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Valoración constructora recibida · Pendiente aceptación cliente · Presu carpintería pdte</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ene'27</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PEDIDOS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>OBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASEO LAGOS 121</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nela/Olatz</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Terminando renders · Reunión vie 24 oct para ver renders y cambios</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>feb'27</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>🔴ALTA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>REUNIÓN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VIV PALOMA RD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Olatz/Andrea</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Reunión agosto con Ale. Siguiente sep.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Jul'27</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>REUNIÓN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TEPEYAC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pendiente saber inicio · Raúl visita pendiente</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>pdte</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ZAHARA SERGIO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Anteproyecto enviado la semana pasada · Sin feedback · Montaje principios mayo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>may'27</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ZAHARA ISABELLA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Proyecto ampliado (2 casas) · Visita pendiente · Avanzar distribución · Fin antes de verano</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>jun'27</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEGUIM.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ANTEPROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ANA Y JOSÉ ÁNGEL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Anteproyecto · Distribución iniciada · Reunión jue 22 oct</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>pdte</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SAN MARTÍN DE VALDEIGLESIAS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Anteproyecto · Unifamiliar cerca del pantano (ampliación)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>pdte</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>🏖</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VACACIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LATENTES / PAUSADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ANA HONTANAR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Después de verano.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PARADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HABITACIÓN ABI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pdte feedback presupuesto.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PARADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ANTIC COLONIAL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PARADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MONTALBÁN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PARADO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5310,7 +7098,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ALEJANDRA POMBO DESIGN STUDIO  ·  RESTAURANTES</t>
+          <t>ALEJANDRA POMBO DESIGN STUDIO  ·  HOTELES</t>
         </is>
       </c>
     </row>
@@ -5441,27 +7229,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FOX + LA DESPENSA</t>
+          <t>DON RAMÓN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sofía/Naiara</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Carpintero termina esta semana · Proyecto nuevo: japonés planta baja · Honorarios pdte aceptar</t>
+          <t>Honorarios ampliación enviados · Pendiente confirmación cliente</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5472,38 +7260,33 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>REMATES</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>APERTURA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PUERTO RICO</t>
+          <t>ONE SHOT BILBAO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cambios de proyecto · Comunicado a cliente: fin proyecto jun/jul</t>
+          <t>Fin obra lun 26 oct · Montaje ~1 mes · Organizar visita equipo semana que viene</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mar/Abr'27</t>
+          <t>Oct'26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5538,17 +7321,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>VISITA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PROY E</t>
+          <t>MONTAJE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PROY E</t>
+          <t>MONTAJE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -5570,27 +7353,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RUBAIYAT MADRID</t>
+          <t>ROCA MAYA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sofía/Naiara</t>
+          <t>Marta/Jesús</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Parado · Cliente centrado en Sao Paulo · En espera reactivación</t>
+          <t>Renders hab. listos · ZZ.CC. en curso · Ale revisa mobiliario ZZ.CC. · Challán termina renders · Entrega este mes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sep'26</t>
+          <t>Sem Santa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5600,158 +7383,258 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ENTREGA</t>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>PROY E</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RUBAIYAT SÃO PAULO</t>
+          <t>HOTEL ÚNICO BCN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Naiara</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Básico esta semana · Ejecutivo en 2 semanas · Entrega anticipada al cliente</t>
+          <t>Pendiente licencia · Sin previsión · Valorando constructora y mobiliario</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>Sep'26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🔴ALTA</t>
+          <t>SEGUIM.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>REVISIÓN</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>VIAJE</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ANT.PROY</t>
+          <t>PROY E</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BERNABÉU</t>
+          <t>VÍA 66</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Naiara</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Terminado. Cierre oficial: números, 1 mesa+perchas. Mesas estrope</t>
+          <t>Lobby y desayunador entregados · Reunión mié 21 oct: suite ático · F2 ene-SS · F3 verano</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sep'26</t>
+          <t>Ene'27</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SEGUIM.</t>
+          <t>🔴ALTA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CIERRE</t>
+          <t>ENTREGA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>PROY E</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MALLORCA SEVILLA</t>
+          <t>PSN PORTAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Naiara</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>⚠ Cerrar pedidos iluminación y cortinas ESTA SEMANA · Obra fin de año</t>
+          <t>⚠ Inicio obra 1 nov · Buscar 2 presupuestos más · Mobiliario a proveedores · Preguntar Raúl fecha fin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>Nov'26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5761,17 +7644,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>REUNIÓN</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>ENTREGA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -5786,315 +7669,205 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>OBRA</t>
+          <t>PROY E</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HIPÓDROMO</t>
+          <t>CASA ALMAGRO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sofía/Naiara</t>
+          <t>Jesús/Marta</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Respuesta Patrimonio esta semana · Licitación constructora nov · Licencia ene/feb</t>
+          <t>PE antes 28 oct · Solo desayunador/bar · Obra enero 2 meses</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pdte</t>
+          <t>Feb'27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEGUIM.</t>
+          <t>🔴ALTA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>OBRA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>OBRA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>OBRA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>OBRA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>PDTE LIC</t>
+          <t>PROY E</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VIV JOANN (Anteproy.)</t>
+          <t>HOTEL SEVILLA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PE parcial: ilum + suelos + revestimientos + techos · Entregar este mes</t>
+          <t>Cliente confirma · Fin obra mayo 2027 · Honorarios ampliación pdte aceptar · Mobiliario: cliente</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>PROY B</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COBUE VALDEMARÍN</t>
+          <t>HOTEL GIJÓN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sofía/Naiara</t>
+          <t>Marta/Jesús</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Obra iniciada · Apertura 21 ene · Terraza pdte · Mobiliario a encargar</t>
+          <t>Bloqueado · Pendiente planos instalaciones de ingeniería</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21 ene</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ENTREGA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
+          <t>SEGUIM.</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COBUE AYALA</t>
+          <t>VINCCI VALENCIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sofía/Naiara</t>
+          <t>Marta/Jesús</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Seguimiento adaptación · Revisión completada · Cliente adapta nuestro proyecto a nuevos locales</t>
+          <t>Obra en marcha · Licitación mobiliario · Piloto ene · Fin jul/ago · Visita próximas semanas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cont.</t>
+          <t>Jul'27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6106,27 +7879,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PASEO LAGOS 132</t>
+          <t>CASA CORREOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sofía/Naiara</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Solados definidos · Revisar planos ya pasados</t>
+          <t>Anteproyecto enviado Patrimonio · Comunicar al cliente: a la espera de su confirmación</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>May'27</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6134,150 +7907,80 @@
           <t>SEGUIM.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CARBON</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sofía</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Remate aislamiento acústico pendiente de ejecutar.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sep'26</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>REMATES</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUPERVISIÓN / SEGUIMIENTO PUNTUAL</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLÍNICA LONGEVIDAD</t>
+          <t>GONZALO CÓRDOBA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin novedades.</t>
+          <t>Sin noticias.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Continuo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEGUIM.</t>
+          <t>ESTABLE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAMINO SUR 35</t>
+          <t>AYALA OFICINAS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sofía/Naiara (Nela apoyo)</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reunión cliente esta semana · Renders cada 2 semanas · Avance parcial en 2 zonas</t>
+          <t>Aceptado · Pendiente pago para iniciar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>oct'28</t>
+          <t>Dic'26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ACTIVO</t>
+          <t>ESTABLE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PROY DECO</t>
         </is>
       </c>
     </row>
@@ -6303,17 +8006,17 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANTANDER REST</t>
+          <t>PANTANO RURAL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Admón.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gestión interna cobro.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6325,22 +8028,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JOANN DOMINICANA</t>
+          <t>4 MASOS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pendiente entrar.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6352,3018 +8055,20 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOPHIE</t>
+          <t>BLESS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pendiente aceptación.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ALEJANDRA POMBO DESIGN STUDIO  ·  VIVIENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PROYECTO</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EQUIPO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NOTAS / ESTADO ACTUAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FIN EST.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RIESGO</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>12 OCT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>19 OCT</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>26 OCT</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2 NOV</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>9 NOV</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>16 NOV</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>23 NOV</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>30 NOV</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>7 DIC</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>14 DIC</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21 DIC</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>28 DIC</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>4 ENE</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>11 ENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PEDRAZA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Olatz/Paula</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Montaje jue 29 oct · Entrega vie 30 oct · Paisajismo + fases cuadras/jueces pdte (sin fechas)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>oct'26</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>VALENCIA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sara/Andrea</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Exterior entregado hoy · Visita pdte cuando Raúl fabrique mueble barbacoa</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sep'26</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ALCALÁ 58</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Alicia/Javi</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Va retrasado. Comunicar nueva fecha al cliente hoy.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sep'26</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FIN OBRA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LA FLORIDA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Corrección mueble pendiente · Paula informa</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>oct'26</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>MONTAJE</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>MONTAJE</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LA RINCONADA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cristina/Nela</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Montaje 3 nov · Entrega 5 nov · Bancada cocina semana siguiente · Mesa salón pdte</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>nov'26</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>FIN OBRA</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ENTREGA</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VIUDA DE ALDAMA 3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nela/Andrea</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Reactiva: inicio en 3 semanas · Ampliación deco · Obra en curso</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>dic'26</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>REUNIÓN</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VIUDA DE ALDAMA 2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Por asignar</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nuevo proyecto. Organizar con cliente en septiembre.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SANTANDER VIV</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sara/Cristina/Andrea</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Proveedores casi todos con encargos · Suelo en 6 semanas mínimo</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ene'27</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>VISITA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IBIZA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Reunión 20 oct · Obra avanzando · Carpintero pendiente de cerrar</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ene'27</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>PDTE LIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>HERMOSILLA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nela/Olatz</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Actualización presu constructora · Reunión cliente semana 27 oct</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>mar'27</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MONTE ESQUINZA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sara</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>⚠ Notificación licencia/DR — revisar. Obra avanzando.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Mar'27</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GAMAL STO. DOMINGO</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sofía/Olatz</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Montaje realizado. Confirmar remates o cierre.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CAMINO SUR 70</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cristina/Nela</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Interior termina esta semana · Mobiliario exterior en 3 semanas</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>oct'26</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TORRE VALENCIA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Obra lenta · Irene contacta cliente para planificación</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pdte</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>REUNIÓN</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PASEO LAGOS 105</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nela/Andrea</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Reunión Raúl 20 oct · Valoración este mes · Obra nov · Renders semana que viene</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>mar'27</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>REUNIÓN</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>PROY B</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>VALCARCE</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Remates papel (David da largas). Remates Raúl: cliente espere 2 s</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PESQUERA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Valoración constructora recibida · Pendiente aceptación cliente · Presu carpintería pdte</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ene'27</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>PEDIDOS</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PASEO LAGOS 121</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nela/Olatz</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Terminando renders · Reunión vie 24 oct para ver renders y cambios</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>feb'27</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>REUNIÓN</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>VIV PALOMA RD</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Olatz/Andrea</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Reunión agosto con Ale. Siguiente sep.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Jul'27</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>REUNIÓN</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TEPEYAC</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Pendiente saber inicio · Raúl visita pendiente</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>pdte</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ABUBILLA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Remates sofá y cortinas. Semana del 7 sep.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Sep'26</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ZAHARA SERGIO</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Por asignar</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Anteproyecto enviado la semana pasada · Sin feedback · Montaje principios mayo</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>may'27</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ZAHARA ISABELLA</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Por asignar</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Proyecto ampliado (2 casas) · Visita pendiente · Avanzar distribución · Fin antes de verano</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>jun'27</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>ANTEPROYECTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ANA Y JOSÉ ÁNGEL</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Por asignar</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Anteproyecto · Distribución iniciada · Reunión jue 22 oct</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>pdte</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SAN MARTÍN DE VALDEIGLESIAS</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Por asignar</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Anteproyecto · Unifamiliar cerca del pantano (ampliación)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>pdte</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>🏖</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>VACACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LATENTES / PAUSADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ANA HONTANAR</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Después de verano.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>HABITACIÓN ABI</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Andrea</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Pdte feedback presupuesto.</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ANTIC COLONIAL</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>MONTALBÁN</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Olatz</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ALEJANDRA POMBO DESIGN STUDIO  ·  HOTELES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PROYECTO</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EQUIPO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NOTAS / ESTADO ACTUAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FIN EST.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RIESGO</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>12 OCT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>19 OCT</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>26 OCT</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2 NOV</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>9 NOV</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>16 NOV</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>23 NOV</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>30 NOV</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>7 DIC</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>14 DIC</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21 DIC</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>28 DIC</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>4 ENE</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>11 ENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DON RAMÓN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Honorarios ampliación enviados · Pendiente confirmación cliente</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1 sep</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>REMATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ONE SHOT BILBAO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fin obra lun 26 oct · Montaje ~1 mes · Organizar visita equipo semana que viene</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Oct'26</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>MONTAJE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MONTAJE</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ROCA MAYA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Marta/Jesús</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Renders hab. listos · ZZ.CC. en curso · Ale revisa mobiliario ZZ.CC. · Challán termina renders · Entrega este mes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sem Santa</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HOTEL ÚNICO BCN</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Pendiente licencia · Sin previsión · Valorando constructora y mobiliario</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Sep'26</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VÍA 66</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Lobby y desayunador entregados · Reunión mié 21 oct: suite ático · F2 ene-SS · F3 verano</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ene'27</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ENTREGA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PSN PORTAL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>⚠ Inicio obra 1 nov · Buscar 2 presupuestos más · Mobiliario a proveedores · Preguntar Raúl fecha fin</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Nov'26</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ENTREGA</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CASA ALMAGRO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Jesús/Marta</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PE antes 28 oct · Solo desayunador/bar · Obra enero 2 meses</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Feb'27</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>🔴ALTA</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>OBRA</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>PROY E</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>HOTEL SEVILLA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Marta</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Cliente confirma · Fin obra mayo 2027 · Honorarios ampliación pdte aceptar · Mobiliario: cliente</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>HOTEL GIJÓN</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Marta/Jesús</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bloqueado · Pendiente planos instalaciones de ingeniería</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>VINCCI VALENCIA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Marta/Jesús</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Obra en marcha · Licitación mobiliario · Piloto ene · Fin jul/ago · Visita próximas semanas</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Jul'27</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MARTÍNEZ CAMPOS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CASA CORREOS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Anteproyecto enviado Patrimonio · Comunicar al cliente: a la espera de su confirmación</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SEGUIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SUPERVISIÓN / SEGUIMIENTO PUNTUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>GONZALO CÓRDOBA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Jesús</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Continuo</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>AYALA OFICINAS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ale/Jesús</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Aceptado · Pendiente pago para iniciar</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Dic'26</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PROY DECO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>KANDA SÁNCHEZ PACHECO</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Jesús/Marta</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>KANDA CATALINA SUÁREZ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Jesús/Marta</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sin noticias.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ESTABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>🏖</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>VACACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LATENTES / PAUSADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PANTANO RURAL</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>4 MASOS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PARADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BLESS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>PARADO</t>
         </is>

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -677,8 +677,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -795,6 +799,16 @@
           <t>PEDIDOS CONFIRMADOS</t>
         </is>
       </c>
+      <c r="Q3" s="40" t="inlineStr">
+        <is>
+          <t>ACCIÓN CONCRETA</t>
+        </is>
+      </c>
+      <c r="R3" s="40" t="inlineStr">
+        <is>
+          <t>CUÁNDO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -869,6 +883,16 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Confirmar todos los pedidos a tiempo.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -924,6 +948,16 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Solicitar update.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -979,6 +1013,16 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Fijar fecha remates con cliente.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1034,6 +1078,16 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Solicitar update a Paula.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1097,6 +1151,16 @@
         </is>
       </c>
       <c r="M9" s="2" t="n"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Coordinar logística montaje.</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1152,6 +1216,16 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Solicitar update.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1207,6 +1281,16 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Definir responsable antes de reunión oct w4.</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1266,6 +1350,16 @@
       </c>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Elaborar calendario de avances y pendientes del cliente. Cerrar esta semana.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1331,6 +1425,16 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Seguimiento aprobación presu. Fijar fecha medición en cuanto esté aprobado.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
         </is>
       </c>
     </row>
@@ -1388,6 +1492,16 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Intentar contacto activo.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1443,6 +1557,16 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Cerrar PE. Esperar valoración constructora. Reunión cliente después.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1498,6 +1622,16 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Solicitar update.</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1553,6 +1687,16 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Solicitar update.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1612,6 +1756,16 @@
       </c>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Cerrar fecha de reunión con cliente esta semana.</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1667,6 +1821,16 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Contactar y presionar para decisiones.</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1722,6 +1886,16 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Fijar reunión con clientes. Actualizar mediciones y pasar a constructora.</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -1777,6 +1951,16 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Confirmar presupuesto.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1842,6 +2026,16 @@
       <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Ale revisa proyecto y deco. Fijar reunión cliente.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
         </is>
       </c>
     </row>
@@ -1899,6 +2093,16 @@
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Seguimiento a su ritmo.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1954,6 +2158,16 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Hacer seguimiento.</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Nov'26</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
@@ -2119,6 +2333,16 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Solicitar update. ¿Remates resueltos?</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -2174,6 +2398,16 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Cerrar renders. Resolver presupuesto carpintería con cliente.</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -2229,6 +2463,16 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Solicitar feedback para definir proyecto.</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
@@ -2288,6 +2532,16 @@
           <t>15 feb 2027</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Avanzar PE sin pausa. Entregar antes de fin de octubre.</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -2347,6 +2601,16 @@
       </c>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Update tras reunión mañana. Definir estado deco y próximo hito.</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>6 oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -2402,6 +2666,16 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Revisar y resolver los 2 puntos de Patrimonio esta semana.</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
@@ -2457,6 +2731,16 @@
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Confirmar estado entrega PE parcial.</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
@@ -2514,6 +2798,16 @@
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t>21 ene 2027</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Confirmar cierre constructora 16 oct. Presionar aceptación deco.</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>16 oct'26</t>
         </is>
       </c>
     </row>
@@ -2606,6 +2900,16 @@
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Cerrar acabados en reunión del jueves y pasar a constructora inmediatamente.</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Jueves 8 oct</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
@@ -2669,6 +2973,16 @@
         </is>
       </c>
       <c r="M37" s="2" t="n"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Confirmar nueva fecha de entrega final.</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
@@ -2728,6 +3042,16 @@
       </c>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Solicitar update progreso renders.</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
@@ -2783,6 +3107,16 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Preparar F2 para enero.</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Dic'26</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
@@ -2838,6 +3172,16 @@
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Hacer seguimiento del estimado enviado.</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
@@ -2897,6 +3241,16 @@
           <t>Feb 2027</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Concretar decisión y cerrar anteproyecto.</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -2952,6 +3306,16 @@
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Insistir en planning constructora. Hacer seguimiento deco cliente.</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -3007,6 +3371,16 @@
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Cuando llegue info estructural: revisar techos.</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -3070,6 +3444,16 @@
         </is>
       </c>
       <c r="M44" s="2" t="n"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Cerrar empresa de mobiliario.</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -3125,6 +3509,16 @@
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Insistir en respuesta contractual esta semana.</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
@@ -3238,6 +3632,16 @@
       <c r="O47" t="inlineStr">
         <is>
           <t>SÍ</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Confirmar pago → lanzar pedidos inmediatamente.</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Esta semana</t>
         </is>
       </c>
     </row>
@@ -3387,6 +3791,16 @@
       <c r="N51" s="41" t="n"/>
       <c r="O51" s="41" t="n"/>
       <c r="P51" s="41" t="n"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Solicitar update.</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="41" t="inlineStr">
@@ -3445,6 +3859,16 @@
       <c r="N52" s="41" t="n"/>
       <c r="O52" s="41" t="n"/>
       <c r="P52" s="41" t="n"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Solicitar update.</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Oct'26</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="26" t="inlineStr">

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Resumen Alejandra" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 MASTER GLOBAL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏠 Planning Vivienda" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏨 Planning Hoteles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="👤 FOCO POR PERSONA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 Vacaciones" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🍽️ Planning Restaurantes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🎨 Renders" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="📊 Resumen Alejandra" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="📋 MASTER GLOBAL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="🏠 Planning Vivienda" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="🏨 Planning Hoteles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="👤 FOCO POR PERSONA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="📅 Vacaciones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="🍽️ Planning Restaurantes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="🎨 Renders" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AUSENCIAS" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,8 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="80">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="DD/MM/YYYY HH:MM"/>
+  </numFmts>
+  <fonts count="81">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -497,8 +503,13 @@
       <color rgb="00CCCCCC"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00E65100"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="60">
+  <fills count="62">
     <fill>
       <patternFill/>
     </fill>
@@ -795,6 +806,16 @@
         <fgColor rgb="00DB7733"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -866,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="312">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1768,6 +1789,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="80" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="80" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6224,7 +6257,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="62" t="inlineStr">
         <is>
@@ -6824,7 +6856,6 @@
       <c r="N65" s="285" t="inlineStr"/>
       <c r="O65" s="285" t="inlineStr"/>
     </row>
-    <row r="66"/>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="269" t="inlineStr">
         <is>
@@ -9553,7 +9584,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="240" t="inlineStr">
         <is>
@@ -14239,4 +14269,7012 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="312" t="inlineStr">
+        <is>
+          <t>UID_ICAL</t>
+        </is>
+      </c>
+      <c r="B1" s="312" t="inlineStr">
+        <is>
+          <t>NOMBRE_PILA</t>
+        </is>
+      </c>
+      <c r="C1" s="312" t="inlineStr">
+        <is>
+          <t>NOMBRE_BIZNEO</t>
+        </is>
+      </c>
+      <c r="D1" s="312" t="inlineStr">
+        <is>
+          <t>TIPO_AUSENCIA</t>
+        </is>
+      </c>
+      <c r="E1" s="312" t="inlineStr">
+        <is>
+          <t>FECHA_INICIO</t>
+        </is>
+      </c>
+      <c r="F1" s="312" t="inlineStr">
+        <is>
+          <t>FECHA_FIN</t>
+        </is>
+      </c>
+      <c r="G1" s="312" t="inlineStr">
+        <is>
+          <t>HORA_INICIO</t>
+        </is>
+      </c>
+      <c r="H1" s="312" t="inlineStr">
+        <is>
+          <t>HORA_FIN</t>
+        </is>
+      </c>
+      <c r="I1" s="312" t="inlineStr">
+        <is>
+          <t>DIA_COMPLETO</t>
+        </is>
+      </c>
+      <c r="J1" s="312" t="inlineStr">
+        <is>
+          <t>SEMANAS_AFECTADAS</t>
+        </is>
+      </c>
+      <c r="K1" s="312" t="inlineStr">
+        <is>
+          <t>NUM_SEMANAS</t>
+        </is>
+      </c>
+      <c r="L1" s="312" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="M1" s="312" t="inlineStr">
+        <is>
+          <t>ES_ADMIN</t>
+        </is>
+      </c>
+      <c r="N1" s="312" t="inlineStr">
+        <is>
+          <t>SYNC_FECHA</t>
+        </is>
+      </c>
+      <c r="O1" s="312" t="inlineStr">
+        <is>
+          <t>BIZNEO_MODIFIED</t>
+        </is>
+      </c>
+      <c r="P1" s="312" t="inlineStr">
+        <is>
+          <t>PRIMERA_VEZ</t>
+        </is>
+      </c>
+      <c r="Q1" s="312" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="313" t="inlineStr">
+        <is>
+          <t>20294362</t>
+        </is>
+      </c>
+      <c r="B2" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C2" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D2" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E2" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F2" s="314" t="n">
+        <v>46029</v>
+      </c>
+      <c r="G2" s="313" t="inlineStr"/>
+      <c r="H2" s="313" t="inlineStr"/>
+      <c r="I2" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J2" s="313" t="inlineStr"/>
+      <c r="K2" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M2" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N2" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O2" s="313" t="n"/>
+      <c r="P2" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q2" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="313" t="inlineStr">
+        <is>
+          <t>20685980</t>
+        </is>
+      </c>
+      <c r="B3" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C3" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D3" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E3" s="314" t="n">
+        <v>46021</v>
+      </c>
+      <c r="F3" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G3" s="313" t="inlineStr"/>
+      <c r="H3" s="313" t="inlineStr"/>
+      <c r="I3" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J3" s="313" t="inlineStr"/>
+      <c r="K3" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M3" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N3" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O3" s="313" t="n"/>
+      <c r="P3" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q3" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="313" t="inlineStr">
+        <is>
+          <t>20687538</t>
+        </is>
+      </c>
+      <c r="B4" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C4" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D4" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E4" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F4" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G4" s="313" t="inlineStr"/>
+      <c r="H4" s="313" t="inlineStr"/>
+      <c r="I4" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J4" s="313" t="inlineStr"/>
+      <c r="K4" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M4" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N4" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O4" s="313" t="n"/>
+      <c r="P4" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q4" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="313" t="inlineStr">
+        <is>
+          <t>20739999</t>
+        </is>
+      </c>
+      <c r="B5" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C5" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D5" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E5" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F5" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G5" s="313" t="inlineStr"/>
+      <c r="H5" s="313" t="inlineStr"/>
+      <c r="I5" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J5" s="313" t="inlineStr"/>
+      <c r="K5" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M5" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N5" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O5" s="313" t="n"/>
+      <c r="P5" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q5" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="313" t="inlineStr">
+        <is>
+          <t>20740000</t>
+        </is>
+      </c>
+      <c r="B6" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C6" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D6" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E6" s="314" t="n">
+        <v>46048</v>
+      </c>
+      <c r="F6" s="314" t="n">
+        <v>46048</v>
+      </c>
+      <c r="G6" s="313" t="inlineStr"/>
+      <c r="H6" s="313" t="inlineStr"/>
+      <c r="I6" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J6" s="313" t="inlineStr"/>
+      <c r="K6" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M6" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N6" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O6" s="313" t="n"/>
+      <c r="P6" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q6" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="313" t="inlineStr">
+        <is>
+          <t>20740003</t>
+        </is>
+      </c>
+      <c r="B7" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C7" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D7" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E7" s="314" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F7" s="314" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G7" s="313" t="inlineStr"/>
+      <c r="H7" s="313" t="inlineStr"/>
+      <c r="I7" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J7" s="313" t="inlineStr"/>
+      <c r="K7" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M7" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N7" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O7" s="313" t="n"/>
+      <c r="P7" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q7" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="313" t="inlineStr">
+        <is>
+          <t>20934457</t>
+        </is>
+      </c>
+      <c r="B8" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C8" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D8" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E8" s="314" t="n">
+        <v>46050</v>
+      </c>
+      <c r="F8" s="314" t="n">
+        <v>46050</v>
+      </c>
+      <c r="G8" s="313" t="inlineStr"/>
+      <c r="H8" s="313" t="inlineStr"/>
+      <c r="I8" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J8" s="313" t="inlineStr"/>
+      <c r="K8" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M8" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N8" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O8" s="313" t="n"/>
+      <c r="P8" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q8" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="313" t="inlineStr">
+        <is>
+          <t>20934460</t>
+        </is>
+      </c>
+      <c r="B9" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C9" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D9" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E9" s="314" t="n">
+        <v>46051</v>
+      </c>
+      <c r="F9" s="314" t="n">
+        <v>46051</v>
+      </c>
+      <c r="G9" s="313" t="inlineStr"/>
+      <c r="H9" s="313" t="inlineStr"/>
+      <c r="I9" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J9" s="313" t="inlineStr"/>
+      <c r="K9" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M9" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N9" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O9" s="313" t="n"/>
+      <c r="P9" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q9" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="313" t="inlineStr">
+        <is>
+          <t>20934467</t>
+        </is>
+      </c>
+      <c r="B10" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C10" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D10" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E10" s="314" t="n">
+        <v>46052</v>
+      </c>
+      <c r="F10" s="314" t="n">
+        <v>46052</v>
+      </c>
+      <c r="G10" s="313" t="inlineStr"/>
+      <c r="H10" s="313" t="inlineStr"/>
+      <c r="I10" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J10" s="313" t="inlineStr"/>
+      <c r="K10" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M10" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N10" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O10" s="313" t="n"/>
+      <c r="P10" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q10" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="313" t="inlineStr">
+        <is>
+          <t>20938321</t>
+        </is>
+      </c>
+      <c r="B11" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C11" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D11" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E11" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F11" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G11" s="313" t="inlineStr"/>
+      <c r="H11" s="313" t="inlineStr"/>
+      <c r="I11" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J11" s="313" t="inlineStr"/>
+      <c r="K11" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M11" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N11" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O11" s="313" t="n"/>
+      <c r="P11" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q11" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="313" t="inlineStr">
+        <is>
+          <t>20938331</t>
+        </is>
+      </c>
+      <c r="B12" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C12" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D12" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E12" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F12" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G12" s="313" t="inlineStr"/>
+      <c r="H12" s="313" t="inlineStr"/>
+      <c r="I12" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J12" s="313" t="inlineStr"/>
+      <c r="K12" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M12" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N12" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O12" s="313" t="n"/>
+      <c r="P12" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q12" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="313" t="inlineStr">
+        <is>
+          <t>20988934</t>
+        </is>
+      </c>
+      <c r="B13" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C13" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D13" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E13" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F13" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G13" s="313" t="inlineStr"/>
+      <c r="H13" s="313" t="inlineStr"/>
+      <c r="I13" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J13" s="313" t="inlineStr"/>
+      <c r="K13" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M13" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N13" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O13" s="313" t="n"/>
+      <c r="P13" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q13" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="313" t="inlineStr">
+        <is>
+          <t>21021708</t>
+        </is>
+      </c>
+      <c r="B14" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C14" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D14" s="313" t="inlineStr"/>
+      <c r="E14" s="314" t="n">
+        <v>46014</v>
+      </c>
+      <c r="F14" s="314" t="n">
+        <v>46028</v>
+      </c>
+      <c r="G14" s="313" t="inlineStr"/>
+      <c r="H14" s="313" t="inlineStr"/>
+      <c r="I14" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J14" s="313" t="inlineStr"/>
+      <c r="K14" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M14" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N14" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O14" s="313" t="n"/>
+      <c r="P14" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q14" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="313" t="inlineStr">
+        <is>
+          <t>21073452</t>
+        </is>
+      </c>
+      <c r="B15" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C15" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D15" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E15" s="314" t="n">
+        <v>46029</v>
+      </c>
+      <c r="F15" s="314" t="n">
+        <v>46029</v>
+      </c>
+      <c r="G15" s="313" t="inlineStr"/>
+      <c r="H15" s="313" t="inlineStr"/>
+      <c r="I15" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J15" s="313" t="inlineStr"/>
+      <c r="K15" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M15" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N15" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O15" s="313" t="n"/>
+      <c r="P15" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q15" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="313" t="inlineStr">
+        <is>
+          <t>21077064</t>
+        </is>
+      </c>
+      <c r="B16" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C16" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D16" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E16" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F16" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G16" s="313" t="inlineStr"/>
+      <c r="H16" s="313" t="inlineStr"/>
+      <c r="I16" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J16" s="313" t="inlineStr"/>
+      <c r="K16" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M16" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N16" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O16" s="313" t="n"/>
+      <c r="P16" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q16" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="313" t="inlineStr">
+        <is>
+          <t>21112686</t>
+        </is>
+      </c>
+      <c r="B17" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C17" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D17" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E17" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F17" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G17" s="313" t="inlineStr"/>
+      <c r="H17" s="313" t="inlineStr"/>
+      <c r="I17" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J17" s="313" t="inlineStr"/>
+      <c r="K17" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M17" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N17" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O17" s="313" t="n"/>
+      <c r="P17" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q17" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="313" t="inlineStr">
+        <is>
+          <t>21112692</t>
+        </is>
+      </c>
+      <c r="B18" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C18" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D18" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E18" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F18" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G18" s="313" t="inlineStr"/>
+      <c r="H18" s="313" t="inlineStr"/>
+      <c r="I18" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J18" s="313" t="inlineStr"/>
+      <c r="K18" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M18" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N18" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O18" s="313" t="n"/>
+      <c r="P18" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q18" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="313" t="inlineStr">
+        <is>
+          <t>21161054</t>
+        </is>
+      </c>
+      <c r="B19" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C19" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D19" s="313" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="E19" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F19" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G19" s="313" t="inlineStr"/>
+      <c r="H19" s="313" t="inlineStr"/>
+      <c r="I19" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J19" s="313" t="inlineStr"/>
+      <c r="K19" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M19" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N19" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O19" s="313" t="n"/>
+      <c r="P19" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q19" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="313" t="inlineStr">
+        <is>
+          <t>21186659</t>
+        </is>
+      </c>
+      <c r="B20" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C20" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D20" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E20" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F20" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G20" s="313" t="inlineStr"/>
+      <c r="H20" s="313" t="inlineStr"/>
+      <c r="I20" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J20" s="313" t="inlineStr"/>
+      <c r="K20" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M20" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N20" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O20" s="313" t="n"/>
+      <c r="P20" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q20" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="313" t="inlineStr">
+        <is>
+          <t>21192128</t>
+        </is>
+      </c>
+      <c r="B21" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C21" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D21" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E21" s="314" t="n">
+        <v>46037</v>
+      </c>
+      <c r="F21" s="314" t="n">
+        <v>46041</v>
+      </c>
+      <c r="G21" s="313" t="inlineStr"/>
+      <c r="H21" s="313" t="inlineStr"/>
+      <c r="I21" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J21" s="313" t="inlineStr"/>
+      <c r="K21" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M21" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N21" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O21" s="313" t="n"/>
+      <c r="P21" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q21" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="313" t="inlineStr">
+        <is>
+          <t>21214479</t>
+        </is>
+      </c>
+      <c r="B22" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C22" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D22" s="313" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="E22" s="314" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F22" s="314" t="n">
+        <v>46071</v>
+      </c>
+      <c r="G22" s="313" t="inlineStr"/>
+      <c r="H22" s="313" t="inlineStr"/>
+      <c r="I22" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J22" s="313" t="inlineStr"/>
+      <c r="K22" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M22" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N22" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O22" s="313" t="n"/>
+      <c r="P22" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q22" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="313" t="inlineStr">
+        <is>
+          <t>21259374</t>
+        </is>
+      </c>
+      <c r="B23" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C23" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D23" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E23" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F23" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G23" s="313" t="inlineStr"/>
+      <c r="H23" s="313" t="inlineStr"/>
+      <c r="I23" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J23" s="313" t="inlineStr"/>
+      <c r="K23" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M23" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N23" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O23" s="313" t="n"/>
+      <c r="P23" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q23" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="313" t="inlineStr">
+        <is>
+          <t>21260259</t>
+        </is>
+      </c>
+      <c r="B24" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C24" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D24" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E24" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F24" s="314" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G24" s="313" t="inlineStr"/>
+      <c r="H24" s="313" t="inlineStr"/>
+      <c r="I24" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J24" s="313" t="inlineStr"/>
+      <c r="K24" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M24" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N24" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O24" s="313" t="n"/>
+      <c r="P24" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q24" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="313" t="inlineStr">
+        <is>
+          <t>21298488</t>
+        </is>
+      </c>
+      <c r="B25" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C25" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D25" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E25" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F25" s="314" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G25" s="313" t="inlineStr"/>
+      <c r="H25" s="313" t="inlineStr"/>
+      <c r="I25" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J25" s="313" t="inlineStr"/>
+      <c r="K25" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M25" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N25" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O25" s="313" t="n"/>
+      <c r="P25" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q25" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="313" t="inlineStr">
+        <is>
+          <t>21314780</t>
+        </is>
+      </c>
+      <c r="B26" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C26" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D26" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E26" s="314" t="n">
+        <v>46034</v>
+      </c>
+      <c r="F26" s="314" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G26" s="313" t="inlineStr"/>
+      <c r="H26" s="313" t="inlineStr"/>
+      <c r="I26" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J26" s="313" t="inlineStr"/>
+      <c r="K26" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M26" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N26" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O26" s="313" t="n"/>
+      <c r="P26" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q26" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="313" t="inlineStr">
+        <is>
+          <t>21368433</t>
+        </is>
+      </c>
+      <c r="B27" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C27" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D27" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E27" s="314" t="n">
+        <v>46066</v>
+      </c>
+      <c r="F27" s="314" t="n">
+        <v>46069</v>
+      </c>
+      <c r="G27" s="313" t="inlineStr"/>
+      <c r="H27" s="313" t="inlineStr"/>
+      <c r="I27" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J27" s="313" t="inlineStr"/>
+      <c r="K27" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M27" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N27" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O27" s="313" t="n"/>
+      <c r="P27" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q27" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="313" t="inlineStr">
+        <is>
+          <t>21386409</t>
+        </is>
+      </c>
+      <c r="B28" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C28" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D28" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E28" s="314" t="n">
+        <v>46090</v>
+      </c>
+      <c r="F28" s="314" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G28" s="313" t="inlineStr"/>
+      <c r="H28" s="313" t="inlineStr"/>
+      <c r="I28" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J28" s="313" t="inlineStr"/>
+      <c r="K28" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M28" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N28" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O28" s="313" t="n"/>
+      <c r="P28" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q28" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="313" t="inlineStr">
+        <is>
+          <t>21412114</t>
+        </is>
+      </c>
+      <c r="B29" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C29" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D29" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E29" s="314" t="n">
+        <v>46048</v>
+      </c>
+      <c r="F29" s="314" t="n">
+        <v>46049</v>
+      </c>
+      <c r="G29" s="313" t="inlineStr"/>
+      <c r="H29" s="313" t="inlineStr"/>
+      <c r="I29" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J29" s="313" t="inlineStr"/>
+      <c r="K29" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M29" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N29" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O29" s="313" t="n"/>
+      <c r="P29" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q29" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="313" t="inlineStr">
+        <is>
+          <t>21412194</t>
+        </is>
+      </c>
+      <c r="B30" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C30" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D30" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E30" s="314" t="n">
+        <v>46041</v>
+      </c>
+      <c r="F30" s="314" t="n">
+        <v>46041</v>
+      </c>
+      <c r="G30" s="313" t="inlineStr"/>
+      <c r="H30" s="313" t="inlineStr"/>
+      <c r="I30" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J30" s="313" t="inlineStr"/>
+      <c r="K30" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M30" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N30" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O30" s="313" t="n"/>
+      <c r="P30" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q30" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="313" t="inlineStr">
+        <is>
+          <t>21412202</t>
+        </is>
+      </c>
+      <c r="B31" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C31" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D31" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E31" s="314" t="n">
+        <v>46043</v>
+      </c>
+      <c r="F31" s="314" t="n">
+        <v>46044</v>
+      </c>
+      <c r="G31" s="313" t="inlineStr"/>
+      <c r="H31" s="313" t="inlineStr"/>
+      <c r="I31" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J31" s="313" t="inlineStr"/>
+      <c r="K31" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M31" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N31" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O31" s="313" t="n"/>
+      <c r="P31" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q31" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="313" t="inlineStr">
+        <is>
+          <t>21418301</t>
+        </is>
+      </c>
+      <c r="B32" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C32" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D32" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E32" s="314" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F32" s="314" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G32" s="313" t="inlineStr"/>
+      <c r="H32" s="313" t="inlineStr"/>
+      <c r="I32" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J32" s="313" t="inlineStr"/>
+      <c r="K32" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M32" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N32" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O32" s="313" t="n"/>
+      <c r="P32" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q32" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="313" t="inlineStr">
+        <is>
+          <t>21418389</t>
+        </is>
+      </c>
+      <c r="B33" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C33" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D33" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E33" s="314" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F33" s="314" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G33" s="313" t="inlineStr"/>
+      <c r="H33" s="313" t="inlineStr"/>
+      <c r="I33" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J33" s="313" t="inlineStr"/>
+      <c r="K33" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M33" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N33" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O33" s="313" t="n"/>
+      <c r="P33" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q33" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="313" t="inlineStr">
+        <is>
+          <t>21529165</t>
+        </is>
+      </c>
+      <c r="B34" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C34" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D34" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E34" s="314" t="n">
+        <v>46052</v>
+      </c>
+      <c r="F34" s="314" t="n">
+        <v>46052</v>
+      </c>
+      <c r="G34" s="313" t="inlineStr"/>
+      <c r="H34" s="313" t="inlineStr"/>
+      <c r="I34" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J34" s="313" t="inlineStr"/>
+      <c r="K34" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M34" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N34" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O34" s="313" t="n"/>
+      <c r="P34" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q34" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="313" t="inlineStr">
+        <is>
+          <t>21544112</t>
+        </is>
+      </c>
+      <c r="B35" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C35" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D35" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E35" s="314" t="n">
+        <v>46049</v>
+      </c>
+      <c r="F35" s="314" t="n">
+        <v>46049</v>
+      </c>
+      <c r="G35" s="313" t="inlineStr"/>
+      <c r="H35" s="313" t="inlineStr"/>
+      <c r="I35" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J35" s="313" t="inlineStr"/>
+      <c r="K35" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M35" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N35" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O35" s="313" t="n"/>
+      <c r="P35" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q35" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="313" t="inlineStr">
+        <is>
+          <t>21565587</t>
+        </is>
+      </c>
+      <c r="B36" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C36" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D36" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E36" s="314" t="n">
+        <v>46097</v>
+      </c>
+      <c r="F36" s="314" t="n">
+        <v>46097</v>
+      </c>
+      <c r="G36" s="313" t="inlineStr"/>
+      <c r="H36" s="313" t="inlineStr"/>
+      <c r="I36" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J36" s="313" t="inlineStr"/>
+      <c r="K36" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M36" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N36" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O36" s="313" t="n"/>
+      <c r="P36" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q36" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="313" t="inlineStr">
+        <is>
+          <t>21658965</t>
+        </is>
+      </c>
+      <c r="B37" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C37" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D37" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E37" s="314" t="n">
+        <v>46080</v>
+      </c>
+      <c r="F37" s="314" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G37" s="313" t="inlineStr"/>
+      <c r="H37" s="313" t="inlineStr"/>
+      <c r="I37" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J37" s="313" t="inlineStr"/>
+      <c r="K37" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M37" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N37" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O37" s="313" t="n"/>
+      <c r="P37" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q37" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="313" t="inlineStr">
+        <is>
+          <t>21662063</t>
+        </is>
+      </c>
+      <c r="B38" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C38" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D38" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E38" s="314" t="n">
+        <v>46065</v>
+      </c>
+      <c r="F38" s="314" t="n">
+        <v>46065</v>
+      </c>
+      <c r="G38" s="313" t="inlineStr"/>
+      <c r="H38" s="313" t="inlineStr"/>
+      <c r="I38" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J38" s="313" t="inlineStr"/>
+      <c r="K38" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M38" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N38" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O38" s="313" t="n"/>
+      <c r="P38" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q38" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="313" t="inlineStr">
+        <is>
+          <t>21786243</t>
+        </is>
+      </c>
+      <c r="B39" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C39" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D39" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E39" s="314" t="n">
+        <v>46085</v>
+      </c>
+      <c r="F39" s="314" t="n">
+        <v>46087</v>
+      </c>
+      <c r="G39" s="313" t="inlineStr"/>
+      <c r="H39" s="313" t="inlineStr"/>
+      <c r="I39" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J39" s="313" t="inlineStr"/>
+      <c r="K39" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M39" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N39" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O39" s="313" t="n"/>
+      <c r="P39" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q39" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="313" t="inlineStr">
+        <is>
+          <t>21786252</t>
+        </is>
+      </c>
+      <c r="B40" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C40" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D40" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E40" s="314" t="n">
+        <v>46072</v>
+      </c>
+      <c r="F40" s="314" t="n">
+        <v>46072</v>
+      </c>
+      <c r="G40" s="313" t="inlineStr"/>
+      <c r="H40" s="313" t="inlineStr"/>
+      <c r="I40" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J40" s="313" t="inlineStr"/>
+      <c r="K40" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M40" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N40" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O40" s="313" t="n"/>
+      <c r="P40" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q40" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="313" t="inlineStr">
+        <is>
+          <t>21931984</t>
+        </is>
+      </c>
+      <c r="B41" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C41" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D41" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E41" s="314" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F41" s="314" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G41" s="313" t="inlineStr"/>
+      <c r="H41" s="313" t="inlineStr"/>
+      <c r="I41" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J41" s="313" t="inlineStr"/>
+      <c r="K41" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M41" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N41" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O41" s="313" t="n"/>
+      <c r="P41" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q41" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="313" t="inlineStr">
+        <is>
+          <t>21997042</t>
+        </is>
+      </c>
+      <c r="B42" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C42" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D42" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E42" s="314" t="n">
+        <v>46108</v>
+      </c>
+      <c r="F42" s="314" t="n">
+        <v>46108</v>
+      </c>
+      <c r="G42" s="313" t="inlineStr"/>
+      <c r="H42" s="313" t="inlineStr"/>
+      <c r="I42" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J42" s="313" t="inlineStr"/>
+      <c r="K42" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M42" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N42" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O42" s="313" t="n"/>
+      <c r="P42" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q42" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="313" t="inlineStr">
+        <is>
+          <t>22050884</t>
+        </is>
+      </c>
+      <c r="B43" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C43" s="313" t="inlineStr">
+        <is>
+          <t>Mudanza, traslado domicilio habitual</t>
+        </is>
+      </c>
+      <c r="D43" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E43" s="314" t="n">
+        <v>46104</v>
+      </c>
+      <c r="F43" s="314" t="n">
+        <v>46104</v>
+      </c>
+      <c r="G43" s="313" t="inlineStr"/>
+      <c r="H43" s="313" t="inlineStr"/>
+      <c r="I43" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J43" s="313" t="inlineStr"/>
+      <c r="K43" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M43" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N43" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O43" s="313" t="n"/>
+      <c r="P43" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q43" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Mudanza, traslado domicilio habitual'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="313" t="inlineStr">
+        <is>
+          <t>22103829</t>
+        </is>
+      </c>
+      <c r="B44" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C44" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D44" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E44" s="314" t="n">
+        <v>46105</v>
+      </c>
+      <c r="F44" s="314" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G44" s="313" t="inlineStr"/>
+      <c r="H44" s="313" t="inlineStr"/>
+      <c r="I44" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J44" s="313" t="inlineStr"/>
+      <c r="K44" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M44" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N44" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O44" s="313" t="n"/>
+      <c r="P44" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q44" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="313" t="inlineStr">
+        <is>
+          <t>22138150</t>
+        </is>
+      </c>
+      <c r="B45" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C45" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D45" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E45" s="314" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F45" s="314" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G45" s="313" t="inlineStr"/>
+      <c r="H45" s="313" t="inlineStr"/>
+      <c r="I45" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J45" s="313" t="inlineStr"/>
+      <c r="K45" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M45" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N45" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O45" s="313" t="n"/>
+      <c r="P45" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q45" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="313" t="inlineStr">
+        <is>
+          <t>22143500</t>
+        </is>
+      </c>
+      <c r="B46" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C46" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D46" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E46" s="314" t="n">
+        <v>46100</v>
+      </c>
+      <c r="F46" s="314" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G46" s="313" t="inlineStr"/>
+      <c r="H46" s="313" t="inlineStr"/>
+      <c r="I46" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J46" s="313" t="inlineStr"/>
+      <c r="K46" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M46" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N46" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O46" s="313" t="n"/>
+      <c r="P46" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q46" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="313" t="inlineStr">
+        <is>
+          <t>22143517</t>
+        </is>
+      </c>
+      <c r="B47" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C47" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D47" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E47" s="314" t="n">
+        <v>46258</v>
+      </c>
+      <c r="F47" s="314" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G47" s="313" t="inlineStr"/>
+      <c r="H47" s="313" t="inlineStr"/>
+      <c r="I47" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J47" s="313" t="inlineStr"/>
+      <c r="K47" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M47" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N47" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O47" s="313" t="n"/>
+      <c r="P47" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q47" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="313" t="inlineStr">
+        <is>
+          <t>22203435</t>
+        </is>
+      </c>
+      <c r="B48" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C48" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D48" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E48" s="314" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F48" s="314" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G48" s="313" t="inlineStr"/>
+      <c r="H48" s="313" t="inlineStr"/>
+      <c r="I48" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J48" s="313" t="inlineStr"/>
+      <c r="K48" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M48" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N48" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O48" s="313" t="n"/>
+      <c r="P48" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q48" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="313" t="inlineStr">
+        <is>
+          <t>22261314</t>
+        </is>
+      </c>
+      <c r="B49" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C49" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D49" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E49" s="314" t="n">
+        <v>46117</v>
+      </c>
+      <c r="F49" s="314" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G49" s="313" t="inlineStr"/>
+      <c r="H49" s="313" t="inlineStr"/>
+      <c r="I49" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J49" s="313" t="inlineStr"/>
+      <c r="K49" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M49" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N49" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O49" s="313" t="n"/>
+      <c r="P49" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q49" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="313" t="inlineStr">
+        <is>
+          <t>22266121</t>
+        </is>
+      </c>
+      <c r="B50" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C50" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D50" s="313" t="inlineStr"/>
+      <c r="E50" s="314" t="n">
+        <v>46231</v>
+      </c>
+      <c r="F50" s="314" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G50" s="313" t="inlineStr"/>
+      <c r="H50" s="313" t="inlineStr"/>
+      <c r="I50" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J50" s="313" t="inlineStr"/>
+      <c r="K50" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M50" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N50" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O50" s="313" t="n"/>
+      <c r="P50" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q50" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="313" t="inlineStr">
+        <is>
+          <t>22266128</t>
+        </is>
+      </c>
+      <c r="B51" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C51" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D51" s="313" t="inlineStr"/>
+      <c r="E51" s="314" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F51" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G51" s="313" t="inlineStr"/>
+      <c r="H51" s="313" t="inlineStr"/>
+      <c r="I51" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J51" s="313" t="inlineStr"/>
+      <c r="K51" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M51" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N51" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O51" s="313" t="n"/>
+      <c r="P51" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q51" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="313" t="inlineStr">
+        <is>
+          <t>22300782</t>
+        </is>
+      </c>
+      <c r="B52" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C52" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D52" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E52" s="314" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F52" s="314" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G52" s="313" t="inlineStr"/>
+      <c r="H52" s="313" t="inlineStr"/>
+      <c r="I52" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J52" s="313" t="inlineStr"/>
+      <c r="K52" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M52" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N52" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O52" s="313" t="n"/>
+      <c r="P52" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q52" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="313" t="inlineStr">
+        <is>
+          <t>22442690</t>
+        </is>
+      </c>
+      <c r="B53" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C53" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D53" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E53" s="314" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F53" s="314" t="n">
+        <v>46136</v>
+      </c>
+      <c r="G53" s="313" t="inlineStr"/>
+      <c r="H53" s="313" t="inlineStr"/>
+      <c r="I53" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J53" s="313" t="inlineStr"/>
+      <c r="K53" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M53" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N53" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O53" s="313" t="n"/>
+      <c r="P53" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q53" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="313" t="inlineStr">
+        <is>
+          <t>22444279</t>
+        </is>
+      </c>
+      <c r="B54" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C54" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D54" s="313" t="inlineStr"/>
+      <c r="E54" s="314" t="n">
+        <v>46142</v>
+      </c>
+      <c r="F54" s="314" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G54" s="313" t="inlineStr"/>
+      <c r="H54" s="313" t="inlineStr"/>
+      <c r="I54" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J54" s="313" t="inlineStr"/>
+      <c r="K54" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M54" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N54" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O54" s="313" t="n"/>
+      <c r="P54" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q54" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="313" t="inlineStr">
+        <is>
+          <t>22542008</t>
+        </is>
+      </c>
+      <c r="B55" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C55" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D55" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E55" s="314" t="n">
+        <v>46156</v>
+      </c>
+      <c r="F55" s="314" t="n">
+        <v>46160</v>
+      </c>
+      <c r="G55" s="313" t="inlineStr"/>
+      <c r="H55" s="313" t="inlineStr"/>
+      <c r="I55" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J55" s="313" t="inlineStr"/>
+      <c r="K55" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M55" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N55" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O55" s="313" t="n"/>
+      <c r="P55" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q55" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="313" t="inlineStr">
+        <is>
+          <t>22747118</t>
+        </is>
+      </c>
+      <c r="B56" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C56" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D56" s="313" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="E56" s="314" t="n">
+        <v>46192</v>
+      </c>
+      <c r="F56" s="314" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G56" s="313" t="inlineStr"/>
+      <c r="H56" s="313" t="inlineStr"/>
+      <c r="I56" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J56" s="313" t="inlineStr"/>
+      <c r="K56" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M56" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N56" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O56" s="313" t="n"/>
+      <c r="P56" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q56" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="313" t="inlineStr">
+        <is>
+          <t>22747123</t>
+        </is>
+      </c>
+      <c r="B57" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C57" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D57" s="313" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="E57" s="314" t="n">
+        <v>46191</v>
+      </c>
+      <c r="F57" s="314" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G57" s="313" t="inlineStr"/>
+      <c r="H57" s="313" t="inlineStr"/>
+      <c r="I57" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J57" s="313" t="inlineStr"/>
+      <c r="K57" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M57" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N57" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O57" s="313" t="n"/>
+      <c r="P57" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q57" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="313" t="inlineStr">
+        <is>
+          <t>22780696</t>
+        </is>
+      </c>
+      <c r="B58" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C58" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D58" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E58" s="314" t="n">
+        <v>46154</v>
+      </c>
+      <c r="F58" s="314" t="n">
+        <v>46154</v>
+      </c>
+      <c r="G58" s="313" t="inlineStr"/>
+      <c r="H58" s="313" t="inlineStr"/>
+      <c r="I58" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J58" s="313" t="inlineStr"/>
+      <c r="K58" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M58" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N58" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O58" s="313" t="n"/>
+      <c r="P58" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q58" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="313" t="inlineStr">
+        <is>
+          <t>22780769</t>
+        </is>
+      </c>
+      <c r="B59" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C59" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D59" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E59" s="314" t="n">
+        <v>46150</v>
+      </c>
+      <c r="F59" s="314" t="n">
+        <v>46150</v>
+      </c>
+      <c r="G59" s="313" t="inlineStr"/>
+      <c r="H59" s="313" t="inlineStr"/>
+      <c r="I59" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J59" s="313" t="inlineStr"/>
+      <c r="K59" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M59" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N59" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O59" s="313" t="n"/>
+      <c r="P59" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q59" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="313" t="inlineStr">
+        <is>
+          <t>22780783</t>
+        </is>
+      </c>
+      <c r="B60" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C60" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D60" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E60" s="314" t="n">
+        <v>46149</v>
+      </c>
+      <c r="F60" s="314" t="n">
+        <v>46149</v>
+      </c>
+      <c r="G60" s="313" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H60" s="313" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="I60" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J60" s="313" t="inlineStr"/>
+      <c r="K60" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M60" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N60" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O60" s="313" t="n"/>
+      <c r="P60" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q60" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="313" t="inlineStr">
+        <is>
+          <t>22786996</t>
+        </is>
+      </c>
+      <c r="B61" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C61" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D61" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E61" s="314" t="n">
+        <v>46125</v>
+      </c>
+      <c r="F61" s="314" t="n">
+        <v>46129</v>
+      </c>
+      <c r="G61" s="313" t="inlineStr"/>
+      <c r="H61" s="313" t="inlineStr"/>
+      <c r="I61" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J61" s="313" t="inlineStr"/>
+      <c r="K61" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M61" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N61" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O61" s="313" t="n"/>
+      <c r="P61" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q61" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="313" t="inlineStr">
+        <is>
+          <t>22787732</t>
+        </is>
+      </c>
+      <c r="B62" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C62" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D62" s="313" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="E62" s="314" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F62" s="314" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G62" s="313" t="inlineStr"/>
+      <c r="H62" s="313" t="inlineStr"/>
+      <c r="I62" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J62" s="313" t="inlineStr"/>
+      <c r="K62" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M62" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N62" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O62" s="313" t="n"/>
+      <c r="P62" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q62" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="313" t="inlineStr">
+        <is>
+          <t>22787938</t>
+        </is>
+      </c>
+      <c r="B63" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C63" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D63" s="313" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="E63" s="314" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F63" s="314" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G63" s="313" t="inlineStr"/>
+      <c r="H63" s="313" t="inlineStr"/>
+      <c r="I63" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J63" s="313" t="inlineStr"/>
+      <c r="K63" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M63" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N63" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O63" s="313" t="n"/>
+      <c r="P63" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q63" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="313" t="inlineStr">
+        <is>
+          <t>22835854</t>
+        </is>
+      </c>
+      <c r="B64" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C64" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D64" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E64" s="314" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F64" s="314" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G64" s="313" t="inlineStr"/>
+      <c r="H64" s="313" t="inlineStr"/>
+      <c r="I64" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J64" s="313" t="inlineStr"/>
+      <c r="K64" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M64" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N64" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O64" s="313" t="n"/>
+      <c r="P64" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q64" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="313" t="inlineStr">
+        <is>
+          <t>22867375</t>
+        </is>
+      </c>
+      <c r="B65" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C65" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D65" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E65" s="314" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F65" s="314" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G65" s="313" t="inlineStr"/>
+      <c r="H65" s="313" t="inlineStr"/>
+      <c r="I65" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J65" s="313" t="inlineStr"/>
+      <c r="K65" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M65" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N65" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O65" s="313" t="n"/>
+      <c r="P65" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q65" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="313" t="inlineStr">
+        <is>
+          <t>22946102</t>
+        </is>
+      </c>
+      <c r="B66" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C66" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D66" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E66" s="314" t="n">
+        <v>46182</v>
+      </c>
+      <c r="F66" s="314" t="n">
+        <v>46184</v>
+      </c>
+      <c r="G66" s="313" t="inlineStr"/>
+      <c r="H66" s="313" t="inlineStr"/>
+      <c r="I66" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J66" s="313" t="inlineStr"/>
+      <c r="K66" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M66" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N66" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O66" s="313" t="n"/>
+      <c r="P66" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q66" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="313" t="inlineStr">
+        <is>
+          <t>22996653</t>
+        </is>
+      </c>
+      <c r="B67" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C67" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D67" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E67" s="314" t="n">
+        <v>46206</v>
+      </c>
+      <c r="F67" s="314" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G67" s="313" t="inlineStr"/>
+      <c r="H67" s="313" t="inlineStr"/>
+      <c r="I67" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J67" s="313" t="inlineStr"/>
+      <c r="K67" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M67" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N67" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O67" s="313" t="n"/>
+      <c r="P67" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q67" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="313" t="inlineStr">
+        <is>
+          <t>23101705</t>
+        </is>
+      </c>
+      <c r="B68" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C68" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D68" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E68" s="314" t="n">
+        <v>46195</v>
+      </c>
+      <c r="F68" s="314" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G68" s="313" t="inlineStr"/>
+      <c r="H68" s="313" t="inlineStr"/>
+      <c r="I68" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J68" s="313" t="inlineStr"/>
+      <c r="K68" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M68" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N68" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O68" s="313" t="n"/>
+      <c r="P68" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q68" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="313" t="inlineStr">
+        <is>
+          <t>23156430</t>
+        </is>
+      </c>
+      <c r="B69" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C69" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D69" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E69" s="314" t="n">
+        <v>46194</v>
+      </c>
+      <c r="F69" s="314" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G69" s="313" t="inlineStr"/>
+      <c r="H69" s="313" t="inlineStr"/>
+      <c r="I69" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J69" s="313" t="inlineStr"/>
+      <c r="K69" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M69" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N69" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O69" s="313" t="n"/>
+      <c r="P69" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q69" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="313" t="inlineStr">
+        <is>
+          <t>23173028</t>
+        </is>
+      </c>
+      <c r="B70" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C70" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D70" s="313" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="E70" s="314" t="n">
+        <v>46192</v>
+      </c>
+      <c r="F70" s="314" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G70" s="313" t="inlineStr"/>
+      <c r="H70" s="313" t="inlineStr"/>
+      <c r="I70" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J70" s="313" t="inlineStr"/>
+      <c r="K70" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M70" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N70" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O70" s="313" t="n"/>
+      <c r="P70" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q70" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="313" t="inlineStr">
+        <is>
+          <t>23173205</t>
+        </is>
+      </c>
+      <c r="B71" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C71" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D71" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E71" s="314" t="n">
+        <v>46199</v>
+      </c>
+      <c r="F71" s="314" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G71" s="313" t="inlineStr"/>
+      <c r="H71" s="313" t="inlineStr"/>
+      <c r="I71" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J71" s="313" t="inlineStr"/>
+      <c r="K71" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M71" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N71" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O71" s="313" t="n"/>
+      <c r="P71" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q71" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="313" t="inlineStr">
+        <is>
+          <t>23205323</t>
+        </is>
+      </c>
+      <c r="B72" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C72" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D72" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E72" s="314" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F72" s="314" t="n">
+        <v>46233</v>
+      </c>
+      <c r="G72" s="313" t="inlineStr"/>
+      <c r="H72" s="313" t="inlineStr"/>
+      <c r="I72" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J72" s="313" t="inlineStr"/>
+      <c r="K72" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M72" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N72" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O72" s="313" t="n"/>
+      <c r="P72" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q72" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="313" t="inlineStr">
+        <is>
+          <t>23205324</t>
+        </is>
+      </c>
+      <c r="B73" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C73" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D73" s="313" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E73" s="314" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F73" s="314" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G73" s="313" t="inlineStr"/>
+      <c r="H73" s="313" t="inlineStr"/>
+      <c r="I73" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J73" s="313" t="inlineStr"/>
+      <c r="K73" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M73" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N73" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O73" s="313" t="n"/>
+      <c r="P73" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q73" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="313" t="inlineStr">
+        <is>
+          <t>23363703</t>
+        </is>
+      </c>
+      <c r="B74" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C74" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D74" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E74" s="314" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F74" s="314" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G74" s="313" t="inlineStr"/>
+      <c r="H74" s="313" t="inlineStr"/>
+      <c r="I74" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J74" s="313" t="inlineStr"/>
+      <c r="K74" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M74" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N74" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O74" s="313" t="n"/>
+      <c r="P74" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q74" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="313" t="inlineStr">
+        <is>
+          <t>23369533</t>
+        </is>
+      </c>
+      <c r="B75" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C75" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D75" s="313" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="E75" s="314" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F75" s="314" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G75" s="313" t="inlineStr"/>
+      <c r="H75" s="313" t="inlineStr"/>
+      <c r="I75" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J75" s="313" t="inlineStr"/>
+      <c r="K75" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M75" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N75" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O75" s="313" t="n"/>
+      <c r="P75" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q75" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="313" t="inlineStr">
+        <is>
+          <t>23369536</t>
+        </is>
+      </c>
+      <c r="B76" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C76" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D76" s="313" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="E76" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F76" s="314" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G76" s="313" t="inlineStr"/>
+      <c r="H76" s="313" t="inlineStr"/>
+      <c r="I76" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J76" s="313" t="inlineStr"/>
+      <c r="K76" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M76" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N76" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O76" s="313" t="n"/>
+      <c r="P76" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q76" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="313" t="inlineStr">
+        <is>
+          <t>23420678</t>
+        </is>
+      </c>
+      <c r="B77" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C77" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D77" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E77" s="314" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F77" s="314" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G77" s="313" t="inlineStr"/>
+      <c r="H77" s="313" t="inlineStr"/>
+      <c r="I77" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J77" s="313" t="inlineStr"/>
+      <c r="K77" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M77" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N77" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O77" s="313" t="n"/>
+      <c r="P77" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q77" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="313" t="inlineStr">
+        <is>
+          <t>23590649</t>
+        </is>
+      </c>
+      <c r="B78" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C78" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D78" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E78" s="314" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F78" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G78" s="313" t="inlineStr"/>
+      <c r="H78" s="313" t="inlineStr"/>
+      <c r="I78" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J78" s="313" t="inlineStr"/>
+      <c r="K78" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M78" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N78" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O78" s="313" t="n"/>
+      <c r="P78" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q78" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="313" t="inlineStr">
+        <is>
+          <t>23590659</t>
+        </is>
+      </c>
+      <c r="B79" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C79" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D79" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E79" s="314" t="n">
+        <v>46269</v>
+      </c>
+      <c r="F79" s="314" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G79" s="313" t="inlineStr"/>
+      <c r="H79" s="313" t="inlineStr"/>
+      <c r="I79" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J79" s="313" t="inlineStr"/>
+      <c r="K79" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M79" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N79" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O79" s="313" t="n"/>
+      <c r="P79" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q79" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="313" t="inlineStr">
+        <is>
+          <t>23592834</t>
+        </is>
+      </c>
+      <c r="B80" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C80" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D80" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E80" s="314" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F80" s="314" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G80" s="313" t="inlineStr"/>
+      <c r="H80" s="313" t="inlineStr"/>
+      <c r="I80" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J80" s="313" t="inlineStr"/>
+      <c r="K80" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M80" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N80" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O80" s="313" t="n"/>
+      <c r="P80" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q80" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="313" t="inlineStr">
+        <is>
+          <t>23637682</t>
+        </is>
+      </c>
+      <c r="B81" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C81" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D81" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E81" s="314" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F81" s="314" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G81" s="313" t="inlineStr"/>
+      <c r="H81" s="313" t="inlineStr"/>
+      <c r="I81" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J81" s="313" t="inlineStr"/>
+      <c r="K81" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M81" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N81" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O81" s="313" t="n"/>
+      <c r="P81" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q81" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="313" t="inlineStr">
+        <is>
+          <t>23639791</t>
+        </is>
+      </c>
+      <c r="B82" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C82" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D82" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E82" s="314" t="n">
+        <v>46240</v>
+      </c>
+      <c r="F82" s="314" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G82" s="313" t="inlineStr"/>
+      <c r="H82" s="313" t="inlineStr"/>
+      <c r="I82" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J82" s="313" t="inlineStr"/>
+      <c r="K82" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M82" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N82" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O82" s="313" t="n"/>
+      <c r="P82" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q82" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="313" t="inlineStr">
+        <is>
+          <t>23639792</t>
+        </is>
+      </c>
+      <c r="B83" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C83" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D83" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E83" s="314" t="n">
+        <v>46241</v>
+      </c>
+      <c r="F83" s="314" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G83" s="313" t="inlineStr"/>
+      <c r="H83" s="313" t="inlineStr"/>
+      <c r="I83" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J83" s="313" t="inlineStr"/>
+      <c r="K83" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M83" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N83" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O83" s="313" t="n"/>
+      <c r="P83" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q83" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="313" t="inlineStr">
+        <is>
+          <t>23667173</t>
+        </is>
+      </c>
+      <c r="B84" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C84" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D84" s="313" t="inlineStr">
+        <is>
+          <t>NELA GONZALEZ SANZ</t>
+        </is>
+      </c>
+      <c r="E84" s="314" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F84" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G84" s="313" t="inlineStr"/>
+      <c r="H84" s="313" t="inlineStr"/>
+      <c r="I84" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J84" s="313" t="inlineStr"/>
+      <c r="K84" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M84" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N84" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O84" s="313" t="n"/>
+      <c r="P84" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q84" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="313" t="inlineStr">
+        <is>
+          <t>23693008</t>
+        </is>
+      </c>
+      <c r="B85" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C85" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D85" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E85" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F85" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G85" s="313" t="inlineStr"/>
+      <c r="H85" s="313" t="inlineStr"/>
+      <c r="I85" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J85" s="313" t="inlineStr"/>
+      <c r="K85" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M85" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N85" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O85" s="313" t="n"/>
+      <c r="P85" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q85" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="313" t="inlineStr">
+        <is>
+          <t>23817184</t>
+        </is>
+      </c>
+      <c r="B86" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C86" s="313" t="inlineStr">
+        <is>
+          <t>Mudanza, traslado domicilio habitual</t>
+        </is>
+      </c>
+      <c r="D86" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E86" s="314" t="n">
+        <v>46268</v>
+      </c>
+      <c r="F86" s="314" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G86" s="313" t="inlineStr"/>
+      <c r="H86" s="313" t="inlineStr"/>
+      <c r="I86" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J86" s="313" t="inlineStr"/>
+      <c r="K86" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M86" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N86" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O86" s="313" t="n"/>
+      <c r="P86" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q86" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Mudanza, traslado domicilio habitual'</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="313" t="inlineStr">
+        <is>
+          <t>23819314</t>
+        </is>
+      </c>
+      <c r="B87" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C87" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D87" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E87" s="314" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F87" s="314" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G87" s="313" t="inlineStr"/>
+      <c r="H87" s="313" t="inlineStr"/>
+      <c r="I87" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J87" s="313" t="inlineStr"/>
+      <c r="K87" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M87" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N87" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O87" s="313" t="n"/>
+      <c r="P87" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q87" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="313" t="inlineStr">
+        <is>
+          <t>23819318</t>
+        </is>
+      </c>
+      <c r="B88" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C88" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D88" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E88" s="314" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F88" s="314" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G88" s="313" t="inlineStr"/>
+      <c r="H88" s="313" t="inlineStr"/>
+      <c r="I88" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J88" s="313" t="inlineStr"/>
+      <c r="K88" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M88" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N88" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O88" s="313" t="n"/>
+      <c r="P88" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q88" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="313" t="inlineStr">
+        <is>
+          <t>23866201</t>
+        </is>
+      </c>
+      <c r="B89" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C89" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D89" s="313" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E89" s="314" t="n">
+        <v>46275</v>
+      </c>
+      <c r="F89" s="314" t="n">
+        <v>46275</v>
+      </c>
+      <c r="G89" s="313" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="H89" s="313" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="I89" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J89" s="313" t="inlineStr"/>
+      <c r="K89" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M89" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N89" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O89" s="313" t="n"/>
+      <c r="P89" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q89" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="313" t="inlineStr">
+        <is>
+          <t>23874960</t>
+        </is>
+      </c>
+      <c r="B90" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C90" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D90" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E90" s="314" t="n">
+        <v>46261</v>
+      </c>
+      <c r="F90" s="314" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G90" s="313" t="inlineStr"/>
+      <c r="H90" s="313" t="inlineStr"/>
+      <c r="I90" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J90" s="313" t="inlineStr"/>
+      <c r="K90" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M90" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N90" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O90" s="313" t="n"/>
+      <c r="P90" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q90" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="313" t="inlineStr">
+        <is>
+          <t>23874961</t>
+        </is>
+      </c>
+      <c r="B91" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C91" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D91" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E91" s="314" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F91" s="314" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G91" s="313" t="inlineStr"/>
+      <c r="H91" s="313" t="inlineStr"/>
+      <c r="I91" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J91" s="313" t="inlineStr"/>
+      <c r="K91" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M91" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N91" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O91" s="313" t="n"/>
+      <c r="P91" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q91" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="313" t="inlineStr">
+        <is>
+          <t>23945228</t>
+        </is>
+      </c>
+      <c r="B92" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C92" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D92" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E92" s="314" t="n">
+        <v>46272</v>
+      </c>
+      <c r="F92" s="314" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G92" s="313" t="inlineStr"/>
+      <c r="H92" s="313" t="inlineStr"/>
+      <c r="I92" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J92" s="313" t="inlineStr"/>
+      <c r="K92" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M92" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N92" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O92" s="313" t="n"/>
+      <c r="P92" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q92" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="313" t="inlineStr">
+        <is>
+          <t>24092042</t>
+        </is>
+      </c>
+      <c r="B93" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C93" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D93" s="313" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="E93" s="314" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F93" s="314" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G93" s="313" t="inlineStr"/>
+      <c r="H93" s="313" t="inlineStr"/>
+      <c r="I93" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J93" s="313" t="inlineStr"/>
+      <c r="K93" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M93" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N93" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O93" s="313" t="n"/>
+      <c r="P93" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q93" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="313" t="inlineStr">
+        <is>
+          <t>24169390</t>
+        </is>
+      </c>
+      <c r="B94" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C94" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D94" s="313" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="E94" s="314" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F94" s="314" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G94" s="313" t="inlineStr"/>
+      <c r="H94" s="313" t="inlineStr"/>
+      <c r="I94" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J94" s="313" t="inlineStr"/>
+      <c r="K94" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M94" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N94" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O94" s="313" t="n"/>
+      <c r="P94" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q94" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="313" t="inlineStr">
+        <is>
+          <t>24222005</t>
+        </is>
+      </c>
+      <c r="B95" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C95" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D95" s="313" t="inlineStr">
+        <is>
+          <t>ANA MAZA MORENO</t>
+        </is>
+      </c>
+      <c r="E95" s="314" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F95" s="314" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G95" s="313" t="inlineStr"/>
+      <c r="H95" s="313" t="inlineStr"/>
+      <c r="I95" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J95" s="313" t="inlineStr"/>
+      <c r="K95" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M95" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N95" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O95" s="313" t="n"/>
+      <c r="P95" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q95" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="313" t="inlineStr">
+        <is>
+          <t>24292891</t>
+        </is>
+      </c>
+      <c r="B96" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C96" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D96" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E96" s="314" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F96" s="314" t="n">
+        <v>46316</v>
+      </c>
+      <c r="G96" s="313" t="inlineStr"/>
+      <c r="H96" s="313" t="inlineStr"/>
+      <c r="I96" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J96" s="313" t="inlineStr">
+        <is>
+          <t>12 OCT, 19 OCT</t>
+        </is>
+      </c>
+      <c r="K96" s="313" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M96" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N96" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O96" s="313" t="n"/>
+      <c r="P96" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q96" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="313" t="inlineStr">
+        <is>
+          <t>24298665</t>
+        </is>
+      </c>
+      <c r="B97" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C97" s="313" t="inlineStr">
+        <is>
+          <t>Mudanza, traslado domicilio habitual</t>
+        </is>
+      </c>
+      <c r="D97" s="313" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="E97" s="314" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F97" s="314" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G97" s="313" t="inlineStr"/>
+      <c r="H97" s="313" t="inlineStr"/>
+      <c r="I97" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J97" s="313" t="inlineStr"/>
+      <c r="K97" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M97" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N97" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O97" s="313" t="n"/>
+      <c r="P97" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q97" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Mudanza, traslado domicilio habitual'</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="313" t="inlineStr">
+        <is>
+          <t>24305977</t>
+        </is>
+      </c>
+      <c r="B98" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C98" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D98" s="313" t="inlineStr">
+        <is>
+          <t>NELA GONZALEZ SANZ</t>
+        </is>
+      </c>
+      <c r="E98" s="314" t="n">
+        <v>46336</v>
+      </c>
+      <c r="F98" s="314" t="n">
+        <v>46336</v>
+      </c>
+      <c r="G98" s="313" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H98" s="313" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="I98" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J98" s="313" t="inlineStr">
+        <is>
+          <t>9 NOV</t>
+        </is>
+      </c>
+      <c r="K98" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M98" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N98" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O98" s="313" t="n"/>
+      <c r="P98" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q98" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="313" t="inlineStr">
+        <is>
+          <t>24328988</t>
+        </is>
+      </c>
+      <c r="B99" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C99" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D99" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E99" s="314" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F99" s="314" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G99" s="313" t="inlineStr"/>
+      <c r="H99" s="313" t="inlineStr"/>
+      <c r="I99" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J99" s="313" t="inlineStr"/>
+      <c r="K99" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M99" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N99" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O99" s="313" t="n"/>
+      <c r="P99" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q99" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="313" t="inlineStr">
+        <is>
+          <t>24328991</t>
+        </is>
+      </c>
+      <c r="B100" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C100" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D100" s="313" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="E100" s="314" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F100" s="314" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G100" s="313" t="inlineStr"/>
+      <c r="H100" s="313" t="inlineStr"/>
+      <c r="I100" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J100" s="313" t="inlineStr">
+        <is>
+          <t>12 OCT</t>
+        </is>
+      </c>
+      <c r="K100" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M100" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N100" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O100" s="313" t="n"/>
+      <c r="P100" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q100" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="313" t="inlineStr">
+        <is>
+          <t>24387983</t>
+        </is>
+      </c>
+      <c r="B101" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C101" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D101" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E101" s="314" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F101" s="314" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G101" s="313" t="inlineStr"/>
+      <c r="H101" s="313" t="inlineStr"/>
+      <c r="I101" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J101" s="313" t="inlineStr"/>
+      <c r="K101" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M101" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N101" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O101" s="313" t="n"/>
+      <c r="P101" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q101" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="313" t="inlineStr">
+        <is>
+          <t>24413021</t>
+        </is>
+      </c>
+      <c r="B102" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C102" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D102" s="313" t="inlineStr"/>
+      <c r="E102" s="314" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F102" s="314" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G102" s="313" t="inlineStr"/>
+      <c r="H102" s="313" t="inlineStr"/>
+      <c r="I102" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J102" s="313" t="inlineStr"/>
+      <c r="K102" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M102" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N102" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O102" s="313" t="n"/>
+      <c r="P102" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q102" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="313" t="inlineStr">
+        <is>
+          <t>24426873</t>
+        </is>
+      </c>
+      <c r="B103" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C103" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D103" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E103" s="314" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F103" s="314" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G103" s="313" t="inlineStr"/>
+      <c r="H103" s="313" t="inlineStr"/>
+      <c r="I103" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J103" s="313" t="inlineStr"/>
+      <c r="K103" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M103" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N103" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O103" s="313" t="n"/>
+      <c r="P103" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q103" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="313" t="inlineStr">
+        <is>
+          <t>24432902</t>
+        </is>
+      </c>
+      <c r="B104" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C104" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D104" s="313" t="inlineStr">
+        <is>
+          <t>NELA GONZALEZ SANZ</t>
+        </is>
+      </c>
+      <c r="E104" s="314" t="n">
+        <v>46377</v>
+      </c>
+      <c r="F104" s="314" t="n">
+        <v>46379</v>
+      </c>
+      <c r="G104" s="313" t="inlineStr"/>
+      <c r="H104" s="313" t="inlineStr"/>
+      <c r="I104" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J104" s="313" t="inlineStr">
+        <is>
+          <t>21 DIC</t>
+        </is>
+      </c>
+      <c r="K104" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M104" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N104" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O104" s="313" t="n"/>
+      <c r="P104" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q104" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="313" t="inlineStr">
+        <is>
+          <t>24443552</t>
+        </is>
+      </c>
+      <c r="B105" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C105" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D105" s="313" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="E105" s="314" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F105" s="314" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G105" s="313" t="inlineStr"/>
+      <c r="H105" s="313" t="inlineStr"/>
+      <c r="I105" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J105" s="313" t="inlineStr"/>
+      <c r="K105" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M105" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N105" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O105" s="313" t="n"/>
+      <c r="P105" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q105" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="313" t="inlineStr">
+        <is>
+          <t>24466993</t>
+        </is>
+      </c>
+      <c r="B106" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C106" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D106" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E106" s="314" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F106" s="314" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G106" s="313" t="inlineStr"/>
+      <c r="H106" s="313" t="inlineStr"/>
+      <c r="I106" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J106" s="313" t="inlineStr">
+        <is>
+          <t>12 OCT</t>
+        </is>
+      </c>
+      <c r="K106" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M106" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N106" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O106" s="313" t="n"/>
+      <c r="P106" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q106" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="313" t="inlineStr">
+        <is>
+          <t>24467029</t>
+        </is>
+      </c>
+      <c r="B107" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C107" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D107" s="313" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="E107" s="314" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F107" s="314" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G107" s="313" t="inlineStr"/>
+      <c r="H107" s="313" t="inlineStr"/>
+      <c r="I107" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J107" s="313" t="inlineStr"/>
+      <c r="K107" s="313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M107" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N107" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O107" s="313" t="n"/>
+      <c r="P107" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q107" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="313" t="inlineStr">
+        <is>
+          <t>24512966</t>
+        </is>
+      </c>
+      <c r="B108" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C108" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D108" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E108" s="314" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F108" s="314" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G108" s="313" t="inlineStr"/>
+      <c r="H108" s="313" t="inlineStr"/>
+      <c r="I108" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J108" s="313" t="inlineStr">
+        <is>
+          <t>19 OCT</t>
+        </is>
+      </c>
+      <c r="K108" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M108" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N108" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O108" s="313" t="n"/>
+      <c r="P108" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q108" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="313" t="inlineStr">
+        <is>
+          <t>24673609</t>
+        </is>
+      </c>
+      <c r="B109" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C109" s="313" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="D109" s="313" t="inlineStr">
+        <is>
+          <t>ANA MAZA MORENO</t>
+        </is>
+      </c>
+      <c r="E109" s="314" t="n">
+        <v>46345</v>
+      </c>
+      <c r="F109" s="314" t="n">
+        <v>46345</v>
+      </c>
+      <c r="G109" s="313" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H109" s="313" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="I109" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J109" s="313" t="inlineStr">
+        <is>
+          <t>16 NOV</t>
+        </is>
+      </c>
+      <c r="K109" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M109" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N109" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O109" s="313" t="n"/>
+      <c r="P109" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q109" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Ausencia'</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="313" t="inlineStr">
+        <is>
+          <t>24674162</t>
+        </is>
+      </c>
+      <c r="B110" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C110" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D110" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E110" s="314" t="n">
+        <v>46365</v>
+      </c>
+      <c r="F110" s="314" t="n">
+        <v>46367</v>
+      </c>
+      <c r="G110" s="313" t="inlineStr"/>
+      <c r="H110" s="313" t="inlineStr"/>
+      <c r="I110" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J110" s="313" t="inlineStr">
+        <is>
+          <t>7 DIC</t>
+        </is>
+      </c>
+      <c r="K110" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M110" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N110" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O110" s="313" t="n"/>
+      <c r="P110" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q110" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="313" t="inlineStr">
+        <is>
+          <t>24674183</t>
+        </is>
+      </c>
+      <c r="B111" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C111" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D111" s="313" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="E111" s="314" t="n">
+        <v>46379</v>
+      </c>
+      <c r="F111" s="314" t="n">
+        <v>46394</v>
+      </c>
+      <c r="G111" s="313" t="inlineStr"/>
+      <c r="H111" s="313" t="inlineStr"/>
+      <c r="I111" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J111" s="313" t="inlineStr">
+        <is>
+          <t>21 DIC, 28 DIC, 4 ENE</t>
+        </is>
+      </c>
+      <c r="K111" s="313" t="n">
+        <v>3</v>
+      </c>
+      <c r="L111" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M111" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N111" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O111" s="313" t="n"/>
+      <c r="P111" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q111" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="313" t="inlineStr">
+        <is>
+          <t>24677175</t>
+        </is>
+      </c>
+      <c r="B112" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C112" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D112" s="313" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="E112" s="314" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F112" s="314" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G112" s="313" t="inlineStr"/>
+      <c r="H112" s="313" t="inlineStr"/>
+      <c r="I112" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J112" s="313" t="inlineStr">
+        <is>
+          <t>19 OCT</t>
+        </is>
+      </c>
+      <c r="K112" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M112" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N112" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O112" s="313" t="n"/>
+      <c r="P112" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q112" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="313" t="inlineStr">
+        <is>
+          <t>24693127</t>
+        </is>
+      </c>
+      <c r="B113" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C113" s="313" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D113" s="313" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="E113" s="314" t="n">
+        <v>46353</v>
+      </c>
+      <c r="F113" s="314" t="n">
+        <v>46353</v>
+      </c>
+      <c r="G113" s="313" t="inlineStr"/>
+      <c r="H113" s="313" t="inlineStr"/>
+      <c r="I113" s="313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J113" s="313" t="inlineStr">
+        <is>
+          <t>23 NOV</t>
+        </is>
+      </c>
+      <c r="K113" s="313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="313" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M113" s="313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N113" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="O113" s="313" t="n"/>
+      <c r="P113" s="315" t="n">
+        <v>46322.56631944444</v>
+      </c>
+      <c r="Q113" s="313" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER GLOBAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEYENDA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESTAURANTES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIVIENDA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOTELES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUSENCIAS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MASTER GLOBAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LEYENDA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="RESTAURANTES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="VIVIENDA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HOTELES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AUSENCIAS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MASTER GLOBAL'!$1:$3</definedName>
@@ -24,8 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="17">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="DD/MM/YYYY HH:MM"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,8 +129,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B5E20"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00E65100"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -202,6 +217,16 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -234,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -370,6 +395,24 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9095,7 +9138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9204,6 +9247,6543 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>20294362</t>
+        </is>
+      </c>
+      <c r="B2" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C2" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D2" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E2" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F2" s="47" t="n">
+        <v>46029</v>
+      </c>
+      <c r="G2" s="46" t="inlineStr"/>
+      <c r="H2" s="46" t="inlineStr"/>
+      <c r="I2" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J2" s="46" t="inlineStr"/>
+      <c r="K2" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M2" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N2" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O2" s="46" t="n"/>
+      <c r="P2" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q2" s="46" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>20685980</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C3" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E3" s="47" t="n">
+        <v>46021</v>
+      </c>
+      <c r="F3" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G3" s="46" t="inlineStr"/>
+      <c r="H3" s="46" t="inlineStr"/>
+      <c r="I3" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J3" s="46" t="inlineStr"/>
+      <c r="K3" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M3" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N3" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q3" s="46" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>20687538</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F4" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G4" s="46" t="inlineStr"/>
+      <c r="H4" s="46" t="inlineStr"/>
+      <c r="I4" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J4" s="46" t="inlineStr"/>
+      <c r="K4" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M4" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N4" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q4" s="46" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>20739999</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F5" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G5" s="46" t="inlineStr"/>
+      <c r="H5" s="46" t="inlineStr"/>
+      <c r="I5" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J5" s="46" t="inlineStr"/>
+      <c r="K5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M5" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N5" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q5" s="46" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>20740000</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>46048</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <v>46048</v>
+      </c>
+      <c r="G6" s="46" t="inlineStr"/>
+      <c r="H6" s="46" t="inlineStr"/>
+      <c r="I6" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J6" s="46" t="inlineStr"/>
+      <c r="K6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M6" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N6" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O6" s="46" t="n"/>
+      <c r="P6" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q6" s="46" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t>20740003</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F7" s="47" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G7" s="46" t="inlineStr"/>
+      <c r="H7" s="46" t="inlineStr"/>
+      <c r="I7" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J7" s="46" t="inlineStr"/>
+      <c r="K7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M7" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N7" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O7" s="46" t="n"/>
+      <c r="P7" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q7" s="46" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t>20934457</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>46050</v>
+      </c>
+      <c r="F8" s="47" t="n">
+        <v>46050</v>
+      </c>
+      <c r="G8" s="46" t="inlineStr"/>
+      <c r="H8" s="46" t="inlineStr"/>
+      <c r="I8" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J8" s="46" t="inlineStr"/>
+      <c r="K8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M8" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N8" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O8" s="46" t="n"/>
+      <c r="P8" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q8" s="46" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>20934460</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="n">
+        <v>46051</v>
+      </c>
+      <c r="F9" s="47" t="n">
+        <v>46051</v>
+      </c>
+      <c r="G9" s="46" t="inlineStr"/>
+      <c r="H9" s="46" t="inlineStr"/>
+      <c r="I9" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J9" s="46" t="inlineStr"/>
+      <c r="K9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M9" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N9" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O9" s="46" t="n"/>
+      <c r="P9" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q9" s="46" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>20934467</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>46052</v>
+      </c>
+      <c r="F10" s="47" t="n">
+        <v>46052</v>
+      </c>
+      <c r="G10" s="46" t="inlineStr"/>
+      <c r="H10" s="46" t="inlineStr"/>
+      <c r="I10" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J10" s="46" t="inlineStr"/>
+      <c r="K10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M10" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N10" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O10" s="46" t="n"/>
+      <c r="P10" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q10" s="46" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>20938321</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F11" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G11" s="46" t="inlineStr"/>
+      <c r="H11" s="46" t="inlineStr"/>
+      <c r="I11" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr"/>
+      <c r="K11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M11" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N11" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O11" s="46" t="n"/>
+      <c r="P11" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q11" s="46" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>20938331</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F12" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G12" s="46" t="inlineStr"/>
+      <c r="H12" s="46" t="inlineStr"/>
+      <c r="I12" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J12" s="46" t="inlineStr"/>
+      <c r="K12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M12" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N12" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O12" s="46" t="n"/>
+      <c r="P12" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q12" s="46" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="46" t="inlineStr">
+        <is>
+          <t>20988934</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E13" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F13" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G13" s="46" t="inlineStr"/>
+      <c r="H13" s="46" t="inlineStr"/>
+      <c r="I13" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J13" s="46" t="inlineStr"/>
+      <c r="K13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M13" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N13" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O13" s="46" t="n"/>
+      <c r="P13" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q13" s="46" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>21021708</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="inlineStr"/>
+      <c r="E14" s="50" t="n">
+        <v>46014</v>
+      </c>
+      <c r="F14" s="50" t="n">
+        <v>46028</v>
+      </c>
+      <c r="G14" s="49" t="inlineStr"/>
+      <c r="H14" s="49" t="inlineStr"/>
+      <c r="I14" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J14" s="49" t="inlineStr"/>
+      <c r="K14" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M14" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N14" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O14" s="49" t="n"/>
+      <c r="P14" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q14" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
+          <t>21073452</t>
+        </is>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E15" s="47" t="n">
+        <v>46029</v>
+      </c>
+      <c r="F15" s="47" t="n">
+        <v>46029</v>
+      </c>
+      <c r="G15" s="46" t="inlineStr"/>
+      <c r="H15" s="46" t="inlineStr"/>
+      <c r="I15" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J15" s="46" t="inlineStr"/>
+      <c r="K15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M15" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N15" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O15" s="46" t="n"/>
+      <c r="P15" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q15" s="46" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>21077064</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F16" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G16" s="46" t="inlineStr"/>
+      <c r="H16" s="46" t="inlineStr"/>
+      <c r="I16" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J16" s="46" t="inlineStr"/>
+      <c r="K16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M16" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N16" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O16" s="46" t="n"/>
+      <c r="P16" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q16" s="46" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>21112686</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F17" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G17" s="46" t="inlineStr"/>
+      <c r="H17" s="46" t="inlineStr"/>
+      <c r="I17" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J17" s="46" t="inlineStr"/>
+      <c r="K17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M17" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N17" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O17" s="46" t="n"/>
+      <c r="P17" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q17" s="46" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>21112692</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F18" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G18" s="46" t="inlineStr"/>
+      <c r="H18" s="46" t="inlineStr"/>
+      <c r="I18" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J18" s="46" t="inlineStr"/>
+      <c r="K18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M18" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N18" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O18" s="46" t="n"/>
+      <c r="P18" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q18" s="46" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>21161054</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F19" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G19" s="46" t="inlineStr"/>
+      <c r="H19" s="46" t="inlineStr"/>
+      <c r="I19" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J19" s="46" t="inlineStr"/>
+      <c r="K19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M19" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N19" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O19" s="46" t="n"/>
+      <c r="P19" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q19" s="46" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>21186659</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E20" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F20" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G20" s="46" t="inlineStr"/>
+      <c r="H20" s="46" t="inlineStr"/>
+      <c r="I20" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J20" s="46" t="inlineStr"/>
+      <c r="K20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M20" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N20" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O20" s="46" t="n"/>
+      <c r="P20" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q20" s="46" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="46" t="inlineStr">
+        <is>
+          <t>21192128</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E21" s="47" t="n">
+        <v>46037</v>
+      </c>
+      <c r="F21" s="47" t="n">
+        <v>46041</v>
+      </c>
+      <c r="G21" s="46" t="inlineStr"/>
+      <c r="H21" s="46" t="inlineStr"/>
+      <c r="I21" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J21" s="46" t="inlineStr"/>
+      <c r="K21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M21" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N21" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O21" s="46" t="n"/>
+      <c r="P21" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q21" s="46" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>21214479</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E22" s="47" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>46071</v>
+      </c>
+      <c r="G22" s="46" t="inlineStr"/>
+      <c r="H22" s="46" t="inlineStr"/>
+      <c r="I22" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J22" s="46" t="inlineStr"/>
+      <c r="K22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M22" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N22" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O22" s="46" t="n"/>
+      <c r="P22" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q22" s="46" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>21259374</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F23" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G23" s="46" t="inlineStr"/>
+      <c r="H23" s="46" t="inlineStr"/>
+      <c r="I23" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J23" s="46" t="inlineStr"/>
+      <c r="K23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M23" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N23" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O23" s="46" t="n"/>
+      <c r="P23" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q23" s="46" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>21260259</t>
+        </is>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="F24" s="47" t="n">
+        <v>46024</v>
+      </c>
+      <c r="G24" s="46" t="inlineStr"/>
+      <c r="H24" s="46" t="inlineStr"/>
+      <c r="I24" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J24" s="46" t="inlineStr"/>
+      <c r="K24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M24" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N24" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O24" s="46" t="n"/>
+      <c r="P24" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q24" s="46" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="46" t="inlineStr">
+        <is>
+          <t>21298488</t>
+        </is>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E25" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="F25" s="47" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G25" s="46" t="inlineStr"/>
+      <c r="H25" s="46" t="inlineStr"/>
+      <c r="I25" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J25" s="46" t="inlineStr"/>
+      <c r="K25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M25" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N25" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O25" s="46" t="n"/>
+      <c r="P25" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q25" s="46" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>21314780</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E26" s="47" t="n">
+        <v>46034</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G26" s="46" t="inlineStr"/>
+      <c r="H26" s="46" t="inlineStr"/>
+      <c r="I26" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J26" s="46" t="inlineStr"/>
+      <c r="K26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M26" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N26" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O26" s="46" t="n"/>
+      <c r="P26" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q26" s="46" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>21368433</t>
+        </is>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E27" s="47" t="n">
+        <v>46066</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <v>46069</v>
+      </c>
+      <c r="G27" s="46" t="inlineStr"/>
+      <c r="H27" s="46" t="inlineStr"/>
+      <c r="I27" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J27" s="46" t="inlineStr"/>
+      <c r="K27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M27" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N27" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O27" s="46" t="n"/>
+      <c r="P27" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q27" s="46" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>21386409</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E28" s="47" t="n">
+        <v>46090</v>
+      </c>
+      <c r="F28" s="47" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G28" s="46" t="inlineStr"/>
+      <c r="H28" s="46" t="inlineStr"/>
+      <c r="I28" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J28" s="46" t="inlineStr"/>
+      <c r="K28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M28" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N28" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O28" s="46" t="n"/>
+      <c r="P28" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q28" s="46" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>21412114</t>
+        </is>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E29" s="47" t="n">
+        <v>46048</v>
+      </c>
+      <c r="F29" s="47" t="n">
+        <v>46049</v>
+      </c>
+      <c r="G29" s="46" t="inlineStr"/>
+      <c r="H29" s="46" t="inlineStr"/>
+      <c r="I29" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J29" s="46" t="inlineStr"/>
+      <c r="K29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M29" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N29" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O29" s="46" t="n"/>
+      <c r="P29" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q29" s="46" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="46" t="inlineStr">
+        <is>
+          <t>21412194</t>
+        </is>
+      </c>
+      <c r="B30" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E30" s="47" t="n">
+        <v>46041</v>
+      </c>
+      <c r="F30" s="47" t="n">
+        <v>46041</v>
+      </c>
+      <c r="G30" s="46" t="inlineStr"/>
+      <c r="H30" s="46" t="inlineStr"/>
+      <c r="I30" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J30" s="46" t="inlineStr"/>
+      <c r="K30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M30" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N30" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O30" s="46" t="n"/>
+      <c r="P30" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q30" s="46" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>21412202</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E31" s="47" t="n">
+        <v>46043</v>
+      </c>
+      <c r="F31" s="47" t="n">
+        <v>46044</v>
+      </c>
+      <c r="G31" s="46" t="inlineStr"/>
+      <c r="H31" s="46" t="inlineStr"/>
+      <c r="I31" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J31" s="46" t="inlineStr"/>
+      <c r="K31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M31" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N31" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O31" s="46" t="n"/>
+      <c r="P31" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q31" s="46" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="inlineStr">
+        <is>
+          <t>21418301</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E32" s="47" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F32" s="47" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G32" s="46" t="inlineStr"/>
+      <c r="H32" s="46" t="inlineStr"/>
+      <c r="I32" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J32" s="46" t="inlineStr"/>
+      <c r="K32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M32" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N32" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O32" s="46" t="n"/>
+      <c r="P32" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q32" s="46" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t>21418389</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F33" s="47" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G33" s="46" t="inlineStr"/>
+      <c r="H33" s="46" t="inlineStr"/>
+      <c r="I33" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J33" s="46" t="inlineStr"/>
+      <c r="K33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M33" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N33" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O33" s="46" t="n"/>
+      <c r="P33" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q33" s="46" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="inlineStr">
+        <is>
+          <t>21529165</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C34" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E34" s="47" t="n">
+        <v>46052</v>
+      </c>
+      <c r="F34" s="47" t="n">
+        <v>46052</v>
+      </c>
+      <c r="G34" s="46" t="inlineStr"/>
+      <c r="H34" s="46" t="inlineStr"/>
+      <c r="I34" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J34" s="46" t="inlineStr"/>
+      <c r="K34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M34" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N34" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O34" s="46" t="n"/>
+      <c r="P34" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q34" s="46" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>21544112</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E35" s="47" t="n">
+        <v>46049</v>
+      </c>
+      <c r="F35" s="47" t="n">
+        <v>46049</v>
+      </c>
+      <c r="G35" s="46" t="inlineStr"/>
+      <c r="H35" s="46" t="inlineStr"/>
+      <c r="I35" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J35" s="46" t="inlineStr"/>
+      <c r="K35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M35" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N35" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O35" s="46" t="n"/>
+      <c r="P35" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q35" s="46" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="inlineStr">
+        <is>
+          <t>21565587</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E36" s="47" t="n">
+        <v>46097</v>
+      </c>
+      <c r="F36" s="47" t="n">
+        <v>46097</v>
+      </c>
+      <c r="G36" s="46" t="inlineStr"/>
+      <c r="H36" s="46" t="inlineStr"/>
+      <c r="I36" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J36" s="46" t="inlineStr"/>
+      <c r="K36" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M36" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N36" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O36" s="46" t="n"/>
+      <c r="P36" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q36" s="46" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="46" t="inlineStr">
+        <is>
+          <t>21658965</t>
+        </is>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E37" s="47" t="n">
+        <v>46080</v>
+      </c>
+      <c r="F37" s="47" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G37" s="46" t="inlineStr"/>
+      <c r="H37" s="46" t="inlineStr"/>
+      <c r="I37" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J37" s="46" t="inlineStr"/>
+      <c r="K37" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M37" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N37" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O37" s="46" t="n"/>
+      <c r="P37" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q37" s="46" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t>21662063</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E38" s="47" t="n">
+        <v>46065</v>
+      </c>
+      <c r="F38" s="47" t="n">
+        <v>46065</v>
+      </c>
+      <c r="G38" s="46" t="inlineStr"/>
+      <c r="H38" s="46" t="inlineStr"/>
+      <c r="I38" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J38" s="46" t="inlineStr"/>
+      <c r="K38" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M38" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N38" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O38" s="46" t="n"/>
+      <c r="P38" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q38" s="46" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="46" t="inlineStr">
+        <is>
+          <t>21786243</t>
+        </is>
+      </c>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E39" s="47" t="n">
+        <v>46085</v>
+      </c>
+      <c r="F39" s="47" t="n">
+        <v>46087</v>
+      </c>
+      <c r="G39" s="46" t="inlineStr"/>
+      <c r="H39" s="46" t="inlineStr"/>
+      <c r="I39" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J39" s="46" t="inlineStr"/>
+      <c r="K39" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M39" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N39" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O39" s="46" t="n"/>
+      <c r="P39" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q39" s="46" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="46" t="inlineStr">
+        <is>
+          <t>21786252</t>
+        </is>
+      </c>
+      <c r="B40" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E40" s="47" t="n">
+        <v>46072</v>
+      </c>
+      <c r="F40" s="47" t="n">
+        <v>46072</v>
+      </c>
+      <c r="G40" s="46" t="inlineStr"/>
+      <c r="H40" s="46" t="inlineStr"/>
+      <c r="I40" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J40" s="46" t="inlineStr"/>
+      <c r="K40" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M40" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N40" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O40" s="46" t="n"/>
+      <c r="P40" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q40" s="46" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="46" t="inlineStr">
+        <is>
+          <t>21931984</t>
+        </is>
+      </c>
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E41" s="47" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F41" s="47" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G41" s="46" t="inlineStr"/>
+      <c r="H41" s="46" t="inlineStr"/>
+      <c r="I41" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J41" s="46" t="inlineStr"/>
+      <c r="K41" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M41" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N41" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O41" s="46" t="n"/>
+      <c r="P41" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q41" s="46" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="46" t="inlineStr">
+        <is>
+          <t>21997042</t>
+        </is>
+      </c>
+      <c r="B42" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C42" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E42" s="47" t="n">
+        <v>46108</v>
+      </c>
+      <c r="F42" s="47" t="n">
+        <v>46108</v>
+      </c>
+      <c r="G42" s="46" t="inlineStr"/>
+      <c r="H42" s="46" t="inlineStr"/>
+      <c r="I42" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J42" s="46" t="inlineStr"/>
+      <c r="K42" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M42" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N42" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O42" s="46" t="n"/>
+      <c r="P42" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q42" s="46" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="46" t="inlineStr">
+        <is>
+          <t>22050884</t>
+        </is>
+      </c>
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>Mudanza, traslado domicilio habitual</t>
+        </is>
+      </c>
+      <c r="E43" s="47" t="n">
+        <v>46104</v>
+      </c>
+      <c r="F43" s="47" t="n">
+        <v>46104</v>
+      </c>
+      <c r="G43" s="46" t="inlineStr"/>
+      <c r="H43" s="46" t="inlineStr"/>
+      <c r="I43" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J43" s="46" t="inlineStr"/>
+      <c r="K43" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M43" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N43" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O43" s="46" t="n"/>
+      <c r="P43" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q43" s="46" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="46" t="inlineStr">
+        <is>
+          <t>22103829</t>
+        </is>
+      </c>
+      <c r="B44" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="n">
+        <v>46105</v>
+      </c>
+      <c r="F44" s="47" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G44" s="46" t="inlineStr"/>
+      <c r="H44" s="46" t="inlineStr"/>
+      <c r="I44" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J44" s="46" t="inlineStr"/>
+      <c r="K44" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M44" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N44" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O44" s="46" t="n"/>
+      <c r="P44" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q44" s="46" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="46" t="inlineStr">
+        <is>
+          <t>22138150</t>
+        </is>
+      </c>
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E45" s="47" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F45" s="47" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G45" s="46" t="inlineStr"/>
+      <c r="H45" s="46" t="inlineStr"/>
+      <c r="I45" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J45" s="46" t="inlineStr"/>
+      <c r="K45" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M45" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N45" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O45" s="46" t="n"/>
+      <c r="P45" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q45" s="46" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="46" t="inlineStr">
+        <is>
+          <t>22143500</t>
+        </is>
+      </c>
+      <c r="B46" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C46" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E46" s="47" t="n">
+        <v>46100</v>
+      </c>
+      <c r="F46" s="47" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G46" s="46" t="inlineStr"/>
+      <c r="H46" s="46" t="inlineStr"/>
+      <c r="I46" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J46" s="46" t="inlineStr"/>
+      <c r="K46" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M46" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N46" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O46" s="46" t="n"/>
+      <c r="P46" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q46" s="46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="46" t="inlineStr">
+        <is>
+          <t>22143517</t>
+        </is>
+      </c>
+      <c r="B47" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E47" s="47" t="n">
+        <v>46258</v>
+      </c>
+      <c r="F47" s="47" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G47" s="46" t="inlineStr"/>
+      <c r="H47" s="46" t="inlineStr"/>
+      <c r="I47" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J47" s="46" t="inlineStr"/>
+      <c r="K47" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M47" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N47" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O47" s="46" t="n"/>
+      <c r="P47" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q47" s="46" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="46" t="inlineStr">
+        <is>
+          <t>22203435</t>
+        </is>
+      </c>
+      <c r="B48" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C48" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F48" s="47" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G48" s="46" t="inlineStr"/>
+      <c r="H48" s="46" t="inlineStr"/>
+      <c r="I48" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J48" s="46" t="inlineStr"/>
+      <c r="K48" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M48" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N48" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O48" s="46" t="n"/>
+      <c r="P48" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q48" s="46" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="46" t="inlineStr">
+        <is>
+          <t>22261314</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E49" s="47" t="n">
+        <v>46117</v>
+      </c>
+      <c r="F49" s="47" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G49" s="46" t="inlineStr"/>
+      <c r="H49" s="46" t="inlineStr"/>
+      <c r="I49" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J49" s="46" t="inlineStr"/>
+      <c r="K49" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M49" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N49" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O49" s="46" t="n"/>
+      <c r="P49" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q49" s="46" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>22266121</t>
+        </is>
+      </c>
+      <c r="B50" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="inlineStr"/>
+      <c r="E50" s="50" t="n">
+        <v>46231</v>
+      </c>
+      <c r="F50" s="50" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G50" s="49" t="inlineStr"/>
+      <c r="H50" s="49" t="inlineStr"/>
+      <c r="I50" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J50" s="49" t="inlineStr"/>
+      <c r="K50" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M50" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N50" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O50" s="49" t="n"/>
+      <c r="P50" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q50" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t>22266128</t>
+        </is>
+      </c>
+      <c r="B51" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C51" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D51" s="49" t="inlineStr"/>
+      <c r="E51" s="50" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F51" s="50" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G51" s="49" t="inlineStr"/>
+      <c r="H51" s="49" t="inlineStr"/>
+      <c r="I51" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J51" s="49" t="inlineStr"/>
+      <c r="K51" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M51" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N51" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O51" s="49" t="n"/>
+      <c r="P51" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q51" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="46" t="inlineStr">
+        <is>
+          <t>22300782</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C52" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E52" s="47" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F52" s="47" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G52" s="46" t="inlineStr"/>
+      <c r="H52" s="46" t="inlineStr"/>
+      <c r="I52" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J52" s="46" t="inlineStr"/>
+      <c r="K52" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M52" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N52" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O52" s="46" t="n"/>
+      <c r="P52" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q52" s="46" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="46" t="inlineStr">
+        <is>
+          <t>22442690</t>
+        </is>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C53" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E53" s="47" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F53" s="47" t="n">
+        <v>46136</v>
+      </c>
+      <c r="G53" s="46" t="inlineStr"/>
+      <c r="H53" s="46" t="inlineStr"/>
+      <c r="I53" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J53" s="46" t="inlineStr"/>
+      <c r="K53" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M53" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N53" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O53" s="46" t="n"/>
+      <c r="P53" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q53" s="46" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="inlineStr">
+        <is>
+          <t>22444279</t>
+        </is>
+      </c>
+      <c r="B54" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="inlineStr"/>
+      <c r="E54" s="50" t="n">
+        <v>46142</v>
+      </c>
+      <c r="F54" s="50" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G54" s="49" t="inlineStr"/>
+      <c r="H54" s="49" t="inlineStr"/>
+      <c r="I54" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J54" s="49" t="inlineStr"/>
+      <c r="K54" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M54" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N54" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O54" s="49" t="n"/>
+      <c r="P54" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q54" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="46" t="inlineStr">
+        <is>
+          <t>22542008</t>
+        </is>
+      </c>
+      <c r="B55" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C55" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E55" s="47" t="n">
+        <v>46156</v>
+      </c>
+      <c r="F55" s="47" t="n">
+        <v>46160</v>
+      </c>
+      <c r="G55" s="46" t="inlineStr"/>
+      <c r="H55" s="46" t="inlineStr"/>
+      <c r="I55" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J55" s="46" t="inlineStr"/>
+      <c r="K55" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M55" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N55" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O55" s="46" t="n"/>
+      <c r="P55" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q55" s="46" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="46" t="inlineStr">
+        <is>
+          <t>22747118</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C56" s="46" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E56" s="47" t="n">
+        <v>46192</v>
+      </c>
+      <c r="F56" s="47" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G56" s="46" t="inlineStr"/>
+      <c r="H56" s="46" t="inlineStr"/>
+      <c r="I56" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J56" s="46" t="inlineStr"/>
+      <c r="K56" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M56" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N56" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O56" s="46" t="n"/>
+      <c r="P56" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q56" s="46" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="46" t="inlineStr">
+        <is>
+          <t>22747123</t>
+        </is>
+      </c>
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C57" s="46" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E57" s="47" t="n">
+        <v>46191</v>
+      </c>
+      <c r="F57" s="47" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G57" s="46" t="inlineStr"/>
+      <c r="H57" s="46" t="inlineStr"/>
+      <c r="I57" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J57" s="46" t="inlineStr"/>
+      <c r="K57" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M57" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N57" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O57" s="46" t="n"/>
+      <c r="P57" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q57" s="46" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="46" t="inlineStr">
+        <is>
+          <t>22780696</t>
+        </is>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C58" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D58" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E58" s="47" t="n">
+        <v>46154</v>
+      </c>
+      <c r="F58" s="47" t="n">
+        <v>46154</v>
+      </c>
+      <c r="G58" s="46" t="inlineStr"/>
+      <c r="H58" s="46" t="inlineStr"/>
+      <c r="I58" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J58" s="46" t="inlineStr"/>
+      <c r="K58" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M58" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N58" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O58" s="46" t="n"/>
+      <c r="P58" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q58" s="46" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="46" t="inlineStr">
+        <is>
+          <t>22780769</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C59" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D59" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E59" s="47" t="n">
+        <v>46150</v>
+      </c>
+      <c r="F59" s="47" t="n">
+        <v>46150</v>
+      </c>
+      <c r="G59" s="46" t="inlineStr"/>
+      <c r="H59" s="46" t="inlineStr"/>
+      <c r="I59" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J59" s="46" t="inlineStr"/>
+      <c r="K59" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M59" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N59" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O59" s="46" t="n"/>
+      <c r="P59" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q59" s="46" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="46" t="inlineStr">
+        <is>
+          <t>22780783</t>
+        </is>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C60" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D60" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E60" s="47" t="n">
+        <v>46149</v>
+      </c>
+      <c r="F60" s="47" t="n">
+        <v>46149</v>
+      </c>
+      <c r="G60" s="46" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H60" s="46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="I60" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J60" s="46" t="inlineStr"/>
+      <c r="K60" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M60" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N60" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O60" s="46" t="n"/>
+      <c r="P60" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q60" s="46" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="46" t="inlineStr">
+        <is>
+          <t>22786996</t>
+        </is>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C61" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D61" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E61" s="47" t="n">
+        <v>46125</v>
+      </c>
+      <c r="F61" s="47" t="n">
+        <v>46129</v>
+      </c>
+      <c r="G61" s="46" t="inlineStr"/>
+      <c r="H61" s="46" t="inlineStr"/>
+      <c r="I61" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J61" s="46" t="inlineStr"/>
+      <c r="K61" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M61" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N61" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O61" s="46" t="n"/>
+      <c r="P61" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q61" s="46" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="inlineStr">
+        <is>
+          <t>22787732</t>
+        </is>
+      </c>
+      <c r="B62" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C62" s="49" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="D62" s="49" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E62" s="50" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F62" s="50" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G62" s="49" t="inlineStr"/>
+      <c r="H62" s="49" t="inlineStr"/>
+      <c r="I62" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J62" s="49" t="inlineStr"/>
+      <c r="K62" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M62" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N62" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O62" s="49" t="n"/>
+      <c r="P62" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q62" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'MARIA CRISTINA FERNANDEZ NELSON'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="49" t="inlineStr">
+        <is>
+          <t>22787938</t>
+        </is>
+      </c>
+      <c r="B63" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C63" s="49" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="D63" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E63" s="50" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F63" s="50" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G63" s="49" t="inlineStr"/>
+      <c r="H63" s="49" t="inlineStr"/>
+      <c r="I63" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J63" s="49" t="inlineStr"/>
+      <c r="K63" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M63" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N63" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O63" s="49" t="n"/>
+      <c r="P63" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q63" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'MARIA CRISTINA FERNANDEZ NELSON'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="46" t="inlineStr">
+        <is>
+          <t>22835854</t>
+        </is>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C64" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D64" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E64" s="47" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F64" s="47" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G64" s="46" t="inlineStr"/>
+      <c r="H64" s="46" t="inlineStr"/>
+      <c r="I64" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J64" s="46" t="inlineStr"/>
+      <c r="K64" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M64" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N64" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O64" s="46" t="n"/>
+      <c r="P64" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q64" s="46" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="46" t="inlineStr">
+        <is>
+          <t>22867375</t>
+        </is>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C65" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E65" s="47" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F65" s="47" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G65" s="46" t="inlineStr"/>
+      <c r="H65" s="46" t="inlineStr"/>
+      <c r="I65" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J65" s="46" t="inlineStr"/>
+      <c r="K65" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M65" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N65" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O65" s="46" t="n"/>
+      <c r="P65" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q65" s="46" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="46" t="inlineStr">
+        <is>
+          <t>22946102</t>
+        </is>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C66" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D66" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E66" s="47" t="n">
+        <v>46182</v>
+      </c>
+      <c r="F66" s="47" t="n">
+        <v>46184</v>
+      </c>
+      <c r="G66" s="46" t="inlineStr"/>
+      <c r="H66" s="46" t="inlineStr"/>
+      <c r="I66" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J66" s="46" t="inlineStr"/>
+      <c r="K66" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M66" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N66" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O66" s="46" t="n"/>
+      <c r="P66" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q66" s="46" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="46" t="inlineStr">
+        <is>
+          <t>22996653</t>
+        </is>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C67" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D67" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E67" s="47" t="n">
+        <v>46206</v>
+      </c>
+      <c r="F67" s="47" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G67" s="46" t="inlineStr"/>
+      <c r="H67" s="46" t="inlineStr"/>
+      <c r="I67" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J67" s="46" t="inlineStr"/>
+      <c r="K67" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M67" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N67" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O67" s="46" t="n"/>
+      <c r="P67" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q67" s="46" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="46" t="inlineStr">
+        <is>
+          <t>23101705</t>
+        </is>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C68" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E68" s="47" t="n">
+        <v>46195</v>
+      </c>
+      <c r="F68" s="47" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G68" s="46" t="inlineStr"/>
+      <c r="H68" s="46" t="inlineStr"/>
+      <c r="I68" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J68" s="46" t="inlineStr"/>
+      <c r="K68" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M68" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N68" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O68" s="46" t="n"/>
+      <c r="P68" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q68" s="46" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="46" t="inlineStr">
+        <is>
+          <t>23156430</t>
+        </is>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C69" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D69" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E69" s="47" t="n">
+        <v>46194</v>
+      </c>
+      <c r="F69" s="47" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G69" s="46" t="inlineStr"/>
+      <c r="H69" s="46" t="inlineStr"/>
+      <c r="I69" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J69" s="46" t="inlineStr"/>
+      <c r="K69" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M69" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N69" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O69" s="46" t="n"/>
+      <c r="P69" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q69" s="46" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="49" t="inlineStr">
+        <is>
+          <t>23173028</t>
+        </is>
+      </c>
+      <c r="B70" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C70" s="49" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="D70" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E70" s="50" t="n">
+        <v>46192</v>
+      </c>
+      <c r="F70" s="50" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G70" s="49" t="inlineStr"/>
+      <c r="H70" s="49" t="inlineStr"/>
+      <c r="I70" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J70" s="49" t="inlineStr"/>
+      <c r="K70" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M70" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N70" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O70" s="49" t="n"/>
+      <c r="P70" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q70" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'MARIA CRISTINA FERNANDEZ NELSON'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="46" t="inlineStr">
+        <is>
+          <t>23173205</t>
+        </is>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C71" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E71" s="47" t="n">
+        <v>46199</v>
+      </c>
+      <c r="F71" s="47" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G71" s="46" t="inlineStr"/>
+      <c r="H71" s="46" t="inlineStr"/>
+      <c r="I71" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J71" s="46" t="inlineStr"/>
+      <c r="K71" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M71" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N71" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O71" s="46" t="n"/>
+      <c r="P71" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q71" s="46" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="46" t="inlineStr">
+        <is>
+          <t>23205323</t>
+        </is>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C72" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D72" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E72" s="47" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F72" s="47" t="n">
+        <v>46233</v>
+      </c>
+      <c r="G72" s="46" t="inlineStr"/>
+      <c r="H72" s="46" t="inlineStr"/>
+      <c r="I72" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J72" s="46" t="inlineStr"/>
+      <c r="K72" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M72" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N72" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O72" s="46" t="n"/>
+      <c r="P72" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q72" s="46" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="46" t="inlineStr">
+        <is>
+          <t>23205324</t>
+        </is>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C73" s="46" t="inlineStr">
+        <is>
+          <t>JESUS MARIA GOICOECHEA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D73" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E73" s="47" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F73" s="47" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G73" s="46" t="inlineStr"/>
+      <c r="H73" s="46" t="inlineStr"/>
+      <c r="I73" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J73" s="46" t="inlineStr"/>
+      <c r="K73" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M73" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N73" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O73" s="46" t="n"/>
+      <c r="P73" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q73" s="46" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="46" t="inlineStr">
+        <is>
+          <t>23363703</t>
+        </is>
+      </c>
+      <c r="B74" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C74" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D74" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E74" s="47" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F74" s="47" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G74" s="46" t="inlineStr"/>
+      <c r="H74" s="46" t="inlineStr"/>
+      <c r="I74" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J74" s="46" t="inlineStr"/>
+      <c r="K74" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M74" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N74" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O74" s="46" t="n"/>
+      <c r="P74" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q74" s="46" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="46" t="inlineStr">
+        <is>
+          <t>23369533</t>
+        </is>
+      </c>
+      <c r="B75" s="46" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C75" s="46" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="D75" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E75" s="47" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F75" s="47" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G75" s="46" t="inlineStr"/>
+      <c r="H75" s="46" t="inlineStr"/>
+      <c r="I75" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J75" s="46" t="inlineStr"/>
+      <c r="K75" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M75" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N75" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O75" s="46" t="n"/>
+      <c r="P75" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q75" s="46" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="46" t="inlineStr">
+        <is>
+          <t>23369536</t>
+        </is>
+      </c>
+      <c r="B76" s="46" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C76" s="46" t="inlineStr">
+        <is>
+          <t>ANDREA PANO MARTIN</t>
+        </is>
+      </c>
+      <c r="D76" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E76" s="47" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F76" s="47" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G76" s="46" t="inlineStr"/>
+      <c r="H76" s="46" t="inlineStr"/>
+      <c r="I76" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J76" s="46" t="inlineStr"/>
+      <c r="K76" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M76" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N76" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O76" s="46" t="n"/>
+      <c r="P76" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q76" s="46" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="46" t="inlineStr">
+        <is>
+          <t>23420678</t>
+        </is>
+      </c>
+      <c r="B77" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C77" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D77" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E77" s="47" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F77" s="47" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G77" s="46" t="inlineStr"/>
+      <c r="H77" s="46" t="inlineStr"/>
+      <c r="I77" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J77" s="46" t="inlineStr"/>
+      <c r="K77" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M77" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N77" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O77" s="46" t="n"/>
+      <c r="P77" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q77" s="46" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="46" t="inlineStr">
+        <is>
+          <t>23590649</t>
+        </is>
+      </c>
+      <c r="B78" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C78" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D78" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E78" s="47" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F78" s="47" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G78" s="46" t="inlineStr"/>
+      <c r="H78" s="46" t="inlineStr"/>
+      <c r="I78" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J78" s="46" t="inlineStr"/>
+      <c r="K78" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M78" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N78" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O78" s="46" t="n"/>
+      <c r="P78" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q78" s="46" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="46" t="inlineStr">
+        <is>
+          <t>23590659</t>
+        </is>
+      </c>
+      <c r="B79" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C79" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D79" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E79" s="47" t="n">
+        <v>46269</v>
+      </c>
+      <c r="F79" s="47" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G79" s="46" t="inlineStr"/>
+      <c r="H79" s="46" t="inlineStr"/>
+      <c r="I79" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J79" s="46" t="inlineStr"/>
+      <c r="K79" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M79" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N79" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O79" s="46" t="n"/>
+      <c r="P79" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q79" s="46" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="46" t="inlineStr">
+        <is>
+          <t>23592834</t>
+        </is>
+      </c>
+      <c r="B80" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C80" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D80" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E80" s="47" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F80" s="47" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G80" s="46" t="inlineStr"/>
+      <c r="H80" s="46" t="inlineStr"/>
+      <c r="I80" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J80" s="46" t="inlineStr"/>
+      <c r="K80" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M80" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N80" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O80" s="46" t="n"/>
+      <c r="P80" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q80" s="46" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="46" t="inlineStr">
+        <is>
+          <t>23637682</t>
+        </is>
+      </c>
+      <c r="B81" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C81" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D81" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E81" s="47" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F81" s="47" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G81" s="46" t="inlineStr"/>
+      <c r="H81" s="46" t="inlineStr"/>
+      <c r="I81" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J81" s="46" t="inlineStr"/>
+      <c r="K81" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M81" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N81" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O81" s="46" t="n"/>
+      <c r="P81" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q81" s="46" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="46" t="inlineStr">
+        <is>
+          <t>23639791</t>
+        </is>
+      </c>
+      <c r="B82" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C82" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D82" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E82" s="47" t="n">
+        <v>46240</v>
+      </c>
+      <c r="F82" s="47" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G82" s="46" t="inlineStr"/>
+      <c r="H82" s="46" t="inlineStr"/>
+      <c r="I82" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J82" s="46" t="inlineStr"/>
+      <c r="K82" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M82" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N82" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O82" s="46" t="n"/>
+      <c r="P82" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q82" s="46" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="46" t="inlineStr">
+        <is>
+          <t>23639792</t>
+        </is>
+      </c>
+      <c r="B83" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C83" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D83" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E83" s="47" t="n">
+        <v>46241</v>
+      </c>
+      <c r="F83" s="47" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G83" s="46" t="inlineStr"/>
+      <c r="H83" s="46" t="inlineStr"/>
+      <c r="I83" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J83" s="46" t="inlineStr"/>
+      <c r="K83" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M83" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N83" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O83" s="46" t="n"/>
+      <c r="P83" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q83" s="46" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="46" t="inlineStr">
+        <is>
+          <t>23667173</t>
+        </is>
+      </c>
+      <c r="B84" s="46" t="inlineStr">
+        <is>
+          <t>Nela</t>
+        </is>
+      </c>
+      <c r="C84" s="46" t="inlineStr">
+        <is>
+          <t>NELA GONZALEZ SANZ</t>
+        </is>
+      </c>
+      <c r="D84" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E84" s="47" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F84" s="47" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G84" s="46" t="inlineStr"/>
+      <c r="H84" s="46" t="inlineStr"/>
+      <c r="I84" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J84" s="46" t="inlineStr"/>
+      <c r="K84" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M84" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N84" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O84" s="46" t="n"/>
+      <c r="P84" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q84" s="46" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="46" t="inlineStr">
+        <is>
+          <t>23693008</t>
+        </is>
+      </c>
+      <c r="B85" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C85" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D85" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E85" s="47" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F85" s="47" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G85" s="46" t="inlineStr"/>
+      <c r="H85" s="46" t="inlineStr"/>
+      <c r="I85" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J85" s="46" t="inlineStr"/>
+      <c r="K85" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M85" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N85" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O85" s="46" t="n"/>
+      <c r="P85" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q85" s="46" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="46" t="inlineStr">
+        <is>
+          <t>23817184</t>
+        </is>
+      </c>
+      <c r="B86" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C86" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D86" s="46" t="inlineStr">
+        <is>
+          <t>Mudanza, traslado domicilio habitual</t>
+        </is>
+      </c>
+      <c r="E86" s="47" t="n">
+        <v>46268</v>
+      </c>
+      <c r="F86" s="47" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G86" s="46" t="inlineStr"/>
+      <c r="H86" s="46" t="inlineStr"/>
+      <c r="I86" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J86" s="46" t="inlineStr"/>
+      <c r="K86" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M86" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N86" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O86" s="46" t="n"/>
+      <c r="P86" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q86" s="46" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="46" t="inlineStr">
+        <is>
+          <t>23819314</t>
+        </is>
+      </c>
+      <c r="B87" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C87" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D87" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E87" s="47" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F87" s="47" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G87" s="46" t="inlineStr"/>
+      <c r="H87" s="46" t="inlineStr"/>
+      <c r="I87" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J87" s="46" t="inlineStr"/>
+      <c r="K87" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M87" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N87" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O87" s="46" t="n"/>
+      <c r="P87" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q87" s="46" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="46" t="inlineStr">
+        <is>
+          <t>23819318</t>
+        </is>
+      </c>
+      <c r="B88" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C88" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D88" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E88" s="47" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F88" s="47" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G88" s="46" t="inlineStr"/>
+      <c r="H88" s="46" t="inlineStr"/>
+      <c r="I88" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J88" s="46" t="inlineStr"/>
+      <c r="K88" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M88" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N88" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O88" s="46" t="n"/>
+      <c r="P88" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q88" s="46" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="46" t="inlineStr">
+        <is>
+          <t>23866201</t>
+        </is>
+      </c>
+      <c r="B89" s="46" t="inlineStr">
+        <is>
+          <t>Susana</t>
+        </is>
+      </c>
+      <c r="C89" s="46" t="inlineStr">
+        <is>
+          <t>SUSANA SERRANO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D89" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E89" s="47" t="n">
+        <v>46275</v>
+      </c>
+      <c r="F89" s="47" t="n">
+        <v>46275</v>
+      </c>
+      <c r="G89" s="46" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="H89" s="46" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="I89" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J89" s="46" t="inlineStr"/>
+      <c r="K89" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M89" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N89" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O89" s="46" t="n"/>
+      <c r="P89" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q89" s="46" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="46" t="inlineStr">
+        <is>
+          <t>23874960</t>
+        </is>
+      </c>
+      <c r="B90" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C90" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D90" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E90" s="47" t="n">
+        <v>46261</v>
+      </c>
+      <c r="F90" s="47" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G90" s="46" t="inlineStr"/>
+      <c r="H90" s="46" t="inlineStr"/>
+      <c r="I90" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J90" s="46" t="inlineStr"/>
+      <c r="K90" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M90" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N90" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O90" s="46" t="n"/>
+      <c r="P90" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q90" s="46" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="46" t="inlineStr">
+        <is>
+          <t>23874961</t>
+        </is>
+      </c>
+      <c r="B91" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C91" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D91" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E91" s="47" t="n">
+        <v>46262</v>
+      </c>
+      <c r="F91" s="47" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G91" s="46" t="inlineStr"/>
+      <c r="H91" s="46" t="inlineStr"/>
+      <c r="I91" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J91" s="46" t="inlineStr"/>
+      <c r="K91" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M91" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N91" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O91" s="46" t="n"/>
+      <c r="P91" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q91" s="46" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="46" t="inlineStr">
+        <is>
+          <t>23945228</t>
+        </is>
+      </c>
+      <c r="B92" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C92" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D92" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E92" s="47" t="n">
+        <v>46272</v>
+      </c>
+      <c r="F92" s="47" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G92" s="46" t="inlineStr"/>
+      <c r="H92" s="46" t="inlineStr"/>
+      <c r="I92" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J92" s="46" t="inlineStr"/>
+      <c r="K92" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M92" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N92" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O92" s="46" t="n"/>
+      <c r="P92" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q92" s="46" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="46" t="inlineStr">
+        <is>
+          <t>24092042</t>
+        </is>
+      </c>
+      <c r="B93" s="46" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="C93" s="46" t="inlineStr">
+        <is>
+          <t>IRENE TAÚS  VALLE</t>
+        </is>
+      </c>
+      <c r="D93" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E93" s="47" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F93" s="47" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G93" s="46" t="inlineStr"/>
+      <c r="H93" s="46" t="inlineStr"/>
+      <c r="I93" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J93" s="46" t="inlineStr"/>
+      <c r="K93" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M93" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N93" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O93" s="46" t="n"/>
+      <c r="P93" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q93" s="46" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="49" t="inlineStr">
+        <is>
+          <t>24169390</t>
+        </is>
+      </c>
+      <c r="B94" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C94" s="49" t="inlineStr">
+        <is>
+          <t>MARIA CRISTINA FERNANDEZ NELSON</t>
+        </is>
+      </c>
+      <c r="D94" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E94" s="50" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F94" s="50" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G94" s="49" t="inlineStr"/>
+      <c r="H94" s="49" t="inlineStr"/>
+      <c r="I94" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J94" s="49" t="inlineStr"/>
+      <c r="K94" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M94" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N94" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O94" s="49" t="n"/>
+      <c r="P94" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q94" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'MARIA CRISTINA FERNANDEZ NELSON'</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="46" t="inlineStr">
+        <is>
+          <t>24222005</t>
+        </is>
+      </c>
+      <c r="B95" s="46" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C95" s="46" t="inlineStr">
+        <is>
+          <t>ANA MAZA MORENO</t>
+        </is>
+      </c>
+      <c r="D95" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E95" s="47" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F95" s="47" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G95" s="46" t="inlineStr"/>
+      <c r="H95" s="46" t="inlineStr"/>
+      <c r="I95" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J95" s="46" t="inlineStr"/>
+      <c r="K95" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M95" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N95" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O95" s="46" t="n"/>
+      <c r="P95" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q95" s="46" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="46" t="inlineStr">
+        <is>
+          <t>24292891</t>
+        </is>
+      </c>
+      <c r="B96" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C96" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D96" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E96" s="47" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F96" s="47" t="n">
+        <v>46316</v>
+      </c>
+      <c r="G96" s="46" t="inlineStr"/>
+      <c r="H96" s="46" t="inlineStr"/>
+      <c r="I96" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J96" s="46" t="inlineStr">
+        <is>
+          <t>12 OCT, 19 OCT</t>
+        </is>
+      </c>
+      <c r="K96" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M96" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N96" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O96" s="46" t="n"/>
+      <c r="P96" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q96" s="46" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="46" t="inlineStr">
+        <is>
+          <t>24298665</t>
+        </is>
+      </c>
+      <c r="B97" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C97" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D97" s="46" t="inlineStr">
+        <is>
+          <t>Mudanza, traslado domicilio habitual</t>
+        </is>
+      </c>
+      <c r="E97" s="47" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F97" s="47" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G97" s="46" t="inlineStr"/>
+      <c r="H97" s="46" t="inlineStr"/>
+      <c r="I97" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J97" s="46" t="inlineStr"/>
+      <c r="K97" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M97" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N97" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O97" s="46" t="n"/>
+      <c r="P97" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q97" s="46" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="46" t="inlineStr">
+        <is>
+          <t>24305977</t>
+        </is>
+      </c>
+      <c r="B98" s="46" t="inlineStr">
+        <is>
+          <t>Nela</t>
+        </is>
+      </c>
+      <c r="C98" s="46" t="inlineStr">
+        <is>
+          <t>NELA GONZALEZ SANZ</t>
+        </is>
+      </c>
+      <c r="D98" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E98" s="47" t="n">
+        <v>46336</v>
+      </c>
+      <c r="F98" s="47" t="n">
+        <v>46336</v>
+      </c>
+      <c r="G98" s="46" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H98" s="46" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="I98" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J98" s="46" t="inlineStr">
+        <is>
+          <t>9 NOV</t>
+        </is>
+      </c>
+      <c r="K98" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M98" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N98" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O98" s="46" t="n"/>
+      <c r="P98" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q98" s="46" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="46" t="inlineStr">
+        <is>
+          <t>24328988</t>
+        </is>
+      </c>
+      <c r="B99" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C99" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D99" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E99" s="47" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F99" s="47" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G99" s="46" t="inlineStr"/>
+      <c r="H99" s="46" t="inlineStr"/>
+      <c r="I99" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J99" s="46" t="inlineStr"/>
+      <c r="K99" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M99" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N99" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O99" s="46" t="n"/>
+      <c r="P99" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q99" s="46" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="46" t="inlineStr">
+        <is>
+          <t>24328991</t>
+        </is>
+      </c>
+      <c r="B100" s="46" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C100" s="46" t="inlineStr">
+        <is>
+          <t>PAULA CALERO HERVADA</t>
+        </is>
+      </c>
+      <c r="D100" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E100" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F100" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G100" s="46" t="inlineStr"/>
+      <c r="H100" s="46" t="inlineStr"/>
+      <c r="I100" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J100" s="46" t="inlineStr">
+        <is>
+          <t>12 OCT</t>
+        </is>
+      </c>
+      <c r="K100" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M100" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N100" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O100" s="46" t="n"/>
+      <c r="P100" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q100" s="46" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="46" t="inlineStr">
+        <is>
+          <t>24387983</t>
+        </is>
+      </c>
+      <c r="B101" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C101" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D101" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E101" s="47" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F101" s="47" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G101" s="46" t="inlineStr"/>
+      <c r="H101" s="46" t="inlineStr"/>
+      <c r="I101" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J101" s="46" t="inlineStr"/>
+      <c r="K101" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M101" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N101" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O101" s="46" t="n"/>
+      <c r="P101" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q101" s="46" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="49" t="inlineStr">
+        <is>
+          <t>24413021</t>
+        </is>
+      </c>
+      <c r="B102" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="C102" s="49" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="D102" s="49" t="inlineStr"/>
+      <c r="E102" s="50" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F102" s="50" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G102" s="49" t="inlineStr"/>
+      <c r="H102" s="49" t="inlineStr"/>
+      <c r="I102" s="49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J102" s="49" t="inlineStr"/>
+      <c r="K102" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="49" t="inlineStr">
+        <is>
+          <t>SIN_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="M102" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N102" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O102" s="49" t="n"/>
+      <c r="P102" s="51" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q102" s="49" t="inlineStr">
+        <is>
+          <t>Nombre no reconocido en NAME_MAP: 'Vacaciones🏖️'</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="46" t="inlineStr">
+        <is>
+          <t>24426873</t>
+        </is>
+      </c>
+      <c r="B103" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C103" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D103" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E103" s="47" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F103" s="47" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G103" s="46" t="inlineStr"/>
+      <c r="H103" s="46" t="inlineStr"/>
+      <c r="I103" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J103" s="46" t="inlineStr"/>
+      <c r="K103" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M103" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N103" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O103" s="46" t="n"/>
+      <c r="P103" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q103" s="46" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="46" t="inlineStr">
+        <is>
+          <t>24432902</t>
+        </is>
+      </c>
+      <c r="B104" s="46" t="inlineStr">
+        <is>
+          <t>Nela</t>
+        </is>
+      </c>
+      <c r="C104" s="46" t="inlineStr">
+        <is>
+          <t>NELA GONZALEZ SANZ</t>
+        </is>
+      </c>
+      <c r="D104" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E104" s="47" t="n">
+        <v>46377</v>
+      </c>
+      <c r="F104" s="47" t="n">
+        <v>46379</v>
+      </c>
+      <c r="G104" s="46" t="inlineStr"/>
+      <c r="H104" s="46" t="inlineStr"/>
+      <c r="I104" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J104" s="46" t="inlineStr">
+        <is>
+          <t>21 DIC</t>
+        </is>
+      </c>
+      <c r="K104" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M104" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N104" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O104" s="46" t="n"/>
+      <c r="P104" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q104" s="46" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="46" t="inlineStr">
+        <is>
+          <t>24443552</t>
+        </is>
+      </c>
+      <c r="B105" s="46" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="C105" s="46" t="inlineStr">
+        <is>
+          <t>SARA BLANCO  BARRIO</t>
+        </is>
+      </c>
+      <c r="D105" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E105" s="47" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F105" s="47" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G105" s="46" t="inlineStr"/>
+      <c r="H105" s="46" t="inlineStr"/>
+      <c r="I105" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J105" s="46" t="inlineStr"/>
+      <c r="K105" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M105" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N105" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O105" s="46" t="n"/>
+      <c r="P105" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q105" s="46" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="46" t="inlineStr">
+        <is>
+          <t>24466993</t>
+        </is>
+      </c>
+      <c r="B106" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C106" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D106" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E106" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F106" s="47" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G106" s="46" t="inlineStr"/>
+      <c r="H106" s="46" t="inlineStr"/>
+      <c r="I106" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J106" s="46" t="inlineStr">
+        <is>
+          <t>12 OCT</t>
+        </is>
+      </c>
+      <c r="K106" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M106" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N106" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O106" s="46" t="n"/>
+      <c r="P106" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q106" s="46" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="46" t="inlineStr">
+        <is>
+          <t>24467029</t>
+        </is>
+      </c>
+      <c r="B107" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C107" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D107" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E107" s="47" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F107" s="47" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G107" s="46" t="inlineStr"/>
+      <c r="H107" s="46" t="inlineStr"/>
+      <c r="I107" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J107" s="46" t="inlineStr"/>
+      <c r="K107" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M107" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N107" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O107" s="46" t="n"/>
+      <c r="P107" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q107" s="46" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="46" t="inlineStr">
+        <is>
+          <t>24512966</t>
+        </is>
+      </c>
+      <c r="B108" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C108" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D108" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E108" s="47" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F108" s="47" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G108" s="46" t="inlineStr"/>
+      <c r="H108" s="46" t="inlineStr"/>
+      <c r="I108" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J108" s="46" t="inlineStr">
+        <is>
+          <t>19 OCT</t>
+        </is>
+      </c>
+      <c r="K108" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M108" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N108" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O108" s="46" t="n"/>
+      <c r="P108" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q108" s="46" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="46" t="inlineStr">
+        <is>
+          <t>24673609</t>
+        </is>
+      </c>
+      <c r="B109" s="46" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C109" s="46" t="inlineStr">
+        <is>
+          <t>ANA MAZA MORENO</t>
+        </is>
+      </c>
+      <c r="D109" s="46" t="inlineStr">
+        <is>
+          <t>Ausencia</t>
+        </is>
+      </c>
+      <c r="E109" s="47" t="n">
+        <v>46345</v>
+      </c>
+      <c r="F109" s="47" t="n">
+        <v>46345</v>
+      </c>
+      <c r="G109" s="46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H109" s="46" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="I109" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J109" s="46" t="inlineStr">
+        <is>
+          <t>16 NOV</t>
+        </is>
+      </c>
+      <c r="K109" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M109" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N109" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O109" s="46" t="n"/>
+      <c r="P109" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q109" s="46" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="46" t="inlineStr">
+        <is>
+          <t>24674162</t>
+        </is>
+      </c>
+      <c r="B110" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C110" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D110" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E110" s="47" t="n">
+        <v>46365</v>
+      </c>
+      <c r="F110" s="47" t="n">
+        <v>46367</v>
+      </c>
+      <c r="G110" s="46" t="inlineStr"/>
+      <c r="H110" s="46" t="inlineStr"/>
+      <c r="I110" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J110" s="46" t="inlineStr">
+        <is>
+          <t>7 DIC</t>
+        </is>
+      </c>
+      <c r="K110" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M110" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N110" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O110" s="46" t="n"/>
+      <c r="P110" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q110" s="46" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="46" t="inlineStr">
+        <is>
+          <t>24674183</t>
+        </is>
+      </c>
+      <c r="B111" s="46" t="inlineStr">
+        <is>
+          <t>Naiara</t>
+        </is>
+      </c>
+      <c r="C111" s="46" t="inlineStr">
+        <is>
+          <t>NAIARA PLAZAOLA GARCIA</t>
+        </is>
+      </c>
+      <c r="D111" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E111" s="47" t="n">
+        <v>46379</v>
+      </c>
+      <c r="F111" s="47" t="n">
+        <v>46394</v>
+      </c>
+      <c r="G111" s="46" t="inlineStr"/>
+      <c r="H111" s="46" t="inlineStr"/>
+      <c r="I111" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J111" s="46" t="inlineStr">
+        <is>
+          <t>21 DIC, 28 DIC, 4 ENE</t>
+        </is>
+      </c>
+      <c r="K111" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L111" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M111" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N111" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O111" s="46" t="n"/>
+      <c r="P111" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q111" s="46" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="46" t="inlineStr">
+        <is>
+          <t>24677175</t>
+        </is>
+      </c>
+      <c r="B112" s="46" t="inlineStr">
+        <is>
+          <t>Olatz</t>
+        </is>
+      </c>
+      <c r="C112" s="46" t="inlineStr">
+        <is>
+          <t>OLATZ MANDIOLA SOLOGAISTUA</t>
+        </is>
+      </c>
+      <c r="D112" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E112" s="47" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F112" s="47" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G112" s="46" t="inlineStr"/>
+      <c r="H112" s="46" t="inlineStr"/>
+      <c r="I112" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J112" s="46" t="inlineStr">
+        <is>
+          <t>19 OCT</t>
+        </is>
+      </c>
+      <c r="K112" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M112" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N112" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O112" s="46" t="n"/>
+      <c r="P112" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q112" s="46" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="46" t="inlineStr">
+        <is>
+          <t>24693127</t>
+        </is>
+      </c>
+      <c r="B113" s="46" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C113" s="46" t="inlineStr">
+        <is>
+          <t>MAURO BERNAT LARGO</t>
+        </is>
+      </c>
+      <c r="D113" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E113" s="47" t="n">
+        <v>46353</v>
+      </c>
+      <c r="F113" s="47" t="n">
+        <v>46353</v>
+      </c>
+      <c r="G113" s="46" t="inlineStr"/>
+      <c r="H113" s="46" t="inlineStr"/>
+      <c r="I113" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J113" s="46" t="inlineStr">
+        <is>
+          <t>23 NOV</t>
+        </is>
+      </c>
+      <c r="K113" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M113" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N113" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O113" s="46" t="n"/>
+      <c r="P113" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q113" s="46" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="46" t="inlineStr">
+        <is>
+          <t>24707199</t>
+        </is>
+      </c>
+      <c r="B114" s="46" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C114" s="46" t="inlineStr">
+        <is>
+          <t>MARTA MARIA LÓPEZ DELGADO</t>
+        </is>
+      </c>
+      <c r="D114" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E114" s="47" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F114" s="47" t="n">
+        <v>46324</v>
+      </c>
+      <c r="G114" s="46" t="inlineStr"/>
+      <c r="H114" s="46" t="inlineStr"/>
+      <c r="I114" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J114" s="46" t="inlineStr">
+        <is>
+          <t>26 OCT</t>
+        </is>
+      </c>
+      <c r="K114" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M114" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N114" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="O114" s="46" t="n"/>
+      <c r="P114" s="48" t="n">
+        <v>46323.51385416667</v>
+      </c>
+      <c r="Q114" s="46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -25,10 +25,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="DD/MM/YYYY HH:MM"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY HH:MM"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -399,19 +399,31 @@
     <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9138,7 +9150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9268,10 +9280,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E2" s="47" t="n">
+      <c r="E2" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F2" s="47" t="n">
+      <c r="F2" s="52" t="n">
         <v>46029</v>
       </c>
       <c r="G2" s="46" t="inlineStr"/>
@@ -9295,11 +9307,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N2" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N2" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O2" s="46" t="n"/>
-      <c r="P2" s="48" t="n">
+      <c r="P2" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q2" s="46" t="inlineStr"/>
@@ -9325,10 +9337,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E3" s="47" t="n">
+      <c r="E3" s="52" t="n">
         <v>46021</v>
       </c>
-      <c r="F3" s="47" t="n">
+      <c r="F3" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G3" s="46" t="inlineStr"/>
@@ -9352,11 +9364,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N3" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N3" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O3" s="46" t="n"/>
-      <c r="P3" s="48" t="n">
+      <c r="P3" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q3" s="46" t="inlineStr"/>
@@ -9382,10 +9394,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E4" s="47" t="n">
+      <c r="E4" s="52" t="n">
         <v>46024</v>
       </c>
-      <c r="F4" s="47" t="n">
+      <c r="F4" s="52" t="n">
         <v>46024</v>
       </c>
       <c r="G4" s="46" t="inlineStr"/>
@@ -9409,11 +9421,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N4" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N4" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O4" s="46" t="n"/>
-      <c r="P4" s="48" t="n">
+      <c r="P4" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q4" s="46" t="inlineStr"/>
@@ -9439,10 +9451,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G5" s="46" t="inlineStr"/>
@@ -9466,11 +9478,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N5" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N5" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O5" s="46" t="n"/>
-      <c r="P5" s="48" t="n">
+      <c r="P5" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q5" s="46" t="inlineStr"/>
@@ -9496,10 +9508,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="52" t="n">
         <v>46048</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="52" t="n">
         <v>46048</v>
       </c>
       <c r="G6" s="46" t="inlineStr"/>
@@ -9523,11 +9535,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N6" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N6" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O6" s="46" t="n"/>
-      <c r="P6" s="48" t="n">
+      <c r="P6" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q6" s="46" t="inlineStr"/>
@@ -9553,10 +9565,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="52" t="n">
         <v>46251</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="52" t="n">
         <v>46254</v>
       </c>
       <c r="G7" s="46" t="inlineStr"/>
@@ -9580,11 +9592,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N7" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N7" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O7" s="46" t="n"/>
-      <c r="P7" s="48" t="n">
+      <c r="P7" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q7" s="46" t="inlineStr"/>
@@ -9610,10 +9622,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="52" t="n">
         <v>46050</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="52" t="n">
         <v>46050</v>
       </c>
       <c r="G8" s="46" t="inlineStr"/>
@@ -9637,11 +9649,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N8" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N8" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O8" s="46" t="n"/>
-      <c r="P8" s="48" t="n">
+      <c r="P8" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q8" s="46" t="inlineStr"/>
@@ -9667,10 +9679,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="52" t="n">
         <v>46051</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="52" t="n">
         <v>46051</v>
       </c>
       <c r="G9" s="46" t="inlineStr"/>
@@ -9694,11 +9706,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N9" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N9" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O9" s="46" t="n"/>
-      <c r="P9" s="48" t="n">
+      <c r="P9" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q9" s="46" t="inlineStr"/>
@@ -9724,10 +9736,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="52" t="n">
         <v>46052</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="52" t="n">
         <v>46052</v>
       </c>
       <c r="G10" s="46" t="inlineStr"/>
@@ -9751,11 +9763,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N10" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N10" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O10" s="46" t="n"/>
-      <c r="P10" s="48" t="n">
+      <c r="P10" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q10" s="46" t="inlineStr"/>
@@ -9781,10 +9793,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="52" t="n">
         <v>46024</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="52" t="n">
         <v>46024</v>
       </c>
       <c r="G11" s="46" t="inlineStr"/>
@@ -9808,11 +9820,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N11" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N11" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O11" s="46" t="n"/>
-      <c r="P11" s="48" t="n">
+      <c r="P11" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q11" s="46" t="inlineStr"/>
@@ -9838,10 +9850,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G12" s="46" t="inlineStr"/>
@@ -9865,11 +9877,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N12" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N12" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O12" s="46" t="n"/>
-      <c r="P12" s="48" t="n">
+      <c r="P12" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q12" s="46" t="inlineStr"/>
@@ -9895,10 +9907,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="52" t="n">
         <v>46024</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="52" t="n">
         <v>46024</v>
       </c>
       <c r="G13" s="46" t="inlineStr"/>
@@ -9922,11 +9934,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N13" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N13" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O13" s="46" t="n"/>
-      <c r="P13" s="48" t="n">
+      <c r="P13" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q13" s="46" t="inlineStr"/>
@@ -9948,10 +9960,10 @@
         </is>
       </c>
       <c r="D14" s="49" t="inlineStr"/>
-      <c r="E14" s="50" t="n">
+      <c r="E14" s="54" t="n">
         <v>46014</v>
       </c>
-      <c r="F14" s="50" t="n">
+      <c r="F14" s="54" t="n">
         <v>46028</v>
       </c>
       <c r="G14" s="49" t="inlineStr"/>
@@ -9975,11 +9987,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N14" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N14" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O14" s="49" t="n"/>
-      <c r="P14" s="51" t="n">
+      <c r="P14" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q14" s="49" t="inlineStr">
@@ -10009,10 +10021,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="52" t="n">
         <v>46029</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="52" t="n">
         <v>46029</v>
       </c>
       <c r="G15" s="46" t="inlineStr"/>
@@ -10036,11 +10048,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N15" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N15" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O15" s="46" t="n"/>
-      <c r="P15" s="48" t="n">
+      <c r="P15" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q15" s="46" t="inlineStr"/>
@@ -10066,10 +10078,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G16" s="46" t="inlineStr"/>
@@ -10093,11 +10105,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N16" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N16" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O16" s="46" t="n"/>
-      <c r="P16" s="48" t="n">
+      <c r="P16" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q16" s="46" t="inlineStr"/>
@@ -10123,10 +10135,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="52" t="n">
         <v>46024</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="52" t="n">
         <v>46024</v>
       </c>
       <c r="G17" s="46" t="inlineStr"/>
@@ -10150,11 +10162,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N17" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N17" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O17" s="46" t="n"/>
-      <c r="P17" s="48" t="n">
+      <c r="P17" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q17" s="46" t="inlineStr"/>
@@ -10180,10 +10192,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F18" s="47" t="n">
+      <c r="F18" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G18" s="46" t="inlineStr"/>
@@ -10207,11 +10219,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N18" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N18" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O18" s="46" t="n"/>
-      <c r="P18" s="48" t="n">
+      <c r="P18" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q18" s="46" t="inlineStr"/>
@@ -10237,10 +10249,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G19" s="46" t="inlineStr"/>
@@ -10264,11 +10276,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N19" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N19" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O19" s="46" t="n"/>
-      <c r="P19" s="48" t="n">
+      <c r="P19" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q19" s="46" t="inlineStr"/>
@@ -10294,10 +10306,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="52" t="n">
         <v>46024</v>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="F20" s="52" t="n">
         <v>46024</v>
       </c>
       <c r="G20" s="46" t="inlineStr"/>
@@ -10321,11 +10333,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N20" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N20" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O20" s="46" t="n"/>
-      <c r="P20" s="48" t="n">
+      <c r="P20" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q20" s="46" t="inlineStr"/>
@@ -10351,10 +10363,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="52" t="n">
         <v>46037</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="F21" s="52" t="n">
         <v>46041</v>
       </c>
       <c r="G21" s="46" t="inlineStr"/>
@@ -10378,11 +10390,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N21" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N21" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O21" s="46" t="n"/>
-      <c r="P21" s="48" t="n">
+      <c r="P21" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q21" s="46" t="inlineStr"/>
@@ -10408,10 +10420,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="52" t="n">
         <v>46069</v>
       </c>
-      <c r="F22" s="47" t="n">
+      <c r="F22" s="52" t="n">
         <v>46071</v>
       </c>
       <c r="G22" s="46" t="inlineStr"/>
@@ -10435,11 +10447,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N22" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N22" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O22" s="46" t="n"/>
-      <c r="P22" s="48" t="n">
+      <c r="P22" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q22" s="46" t="inlineStr"/>
@@ -10465,10 +10477,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G23" s="46" t="inlineStr"/>
@@ -10492,11 +10504,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N23" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N23" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O23" s="46" t="n"/>
-      <c r="P23" s="48" t="n">
+      <c r="P23" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q23" s="46" t="inlineStr"/>
@@ -10522,10 +10534,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E24" s="47" t="n">
+      <c r="E24" s="52" t="n">
         <v>46024</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="F24" s="52" t="n">
         <v>46024</v>
       </c>
       <c r="G24" s="46" t="inlineStr"/>
@@ -10549,11 +10561,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N24" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N24" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O24" s="46" t="n"/>
-      <c r="P24" s="48" t="n">
+      <c r="P24" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q24" s="46" t="inlineStr"/>
@@ -10579,10 +10591,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="52" t="n">
         <v>46027</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="52" t="n">
         <v>46027</v>
       </c>
       <c r="G25" s="46" t="inlineStr"/>
@@ -10606,11 +10618,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N25" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N25" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O25" s="46" t="n"/>
-      <c r="P25" s="48" t="n">
+      <c r="P25" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q25" s="46" t="inlineStr"/>
@@ -10636,10 +10648,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="52" t="n">
         <v>46034</v>
       </c>
-      <c r="F26" s="47" t="n">
+      <c r="F26" s="52" t="n">
         <v>46035</v>
       </c>
       <c r="G26" s="46" t="inlineStr"/>
@@ -10663,11 +10675,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N26" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N26" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O26" s="46" t="n"/>
-      <c r="P26" s="48" t="n">
+      <c r="P26" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q26" s="46" t="inlineStr"/>
@@ -10693,10 +10705,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="52" t="n">
         <v>46066</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="52" t="n">
         <v>46069</v>
       </c>
       <c r="G27" s="46" t="inlineStr"/>
@@ -10720,11 +10732,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N27" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N27" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O27" s="46" t="n"/>
-      <c r="P27" s="48" t="n">
+      <c r="P27" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q27" s="46" t="inlineStr"/>
@@ -10750,10 +10762,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E28" s="47" t="n">
+      <c r="E28" s="52" t="n">
         <v>46090</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="F28" s="52" t="n">
         <v>46090</v>
       </c>
       <c r="G28" s="46" t="inlineStr"/>
@@ -10777,11 +10789,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N28" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N28" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O28" s="46" t="n"/>
-      <c r="P28" s="48" t="n">
+      <c r="P28" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q28" s="46" t="inlineStr"/>
@@ -10807,10 +10819,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="52" t="n">
         <v>46048</v>
       </c>
-      <c r="F29" s="47" t="n">
+      <c r="F29" s="52" t="n">
         <v>46049</v>
       </c>
       <c r="G29" s="46" t="inlineStr"/>
@@ -10834,11 +10846,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N29" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N29" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O29" s="46" t="n"/>
-      <c r="P29" s="48" t="n">
+      <c r="P29" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q29" s="46" t="inlineStr"/>
@@ -10864,10 +10876,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="52" t="n">
         <v>46041</v>
       </c>
-      <c r="F30" s="47" t="n">
+      <c r="F30" s="52" t="n">
         <v>46041</v>
       </c>
       <c r="G30" s="46" t="inlineStr"/>
@@ -10891,11 +10903,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N30" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N30" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O30" s="46" t="n"/>
-      <c r="P30" s="48" t="n">
+      <c r="P30" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q30" s="46" t="inlineStr"/>
@@ -10921,10 +10933,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E31" s="47" t="n">
+      <c r="E31" s="52" t="n">
         <v>46043</v>
       </c>
-      <c r="F31" s="47" t="n">
+      <c r="F31" s="52" t="n">
         <v>46044</v>
       </c>
       <c r="G31" s="46" t="inlineStr"/>
@@ -10948,11 +10960,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N31" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N31" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O31" s="46" t="n"/>
-      <c r="P31" s="48" t="n">
+      <c r="P31" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q31" s="46" t="inlineStr"/>
@@ -10978,10 +10990,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E32" s="47" t="n">
+      <c r="E32" s="52" t="n">
         <v>46111</v>
       </c>
-      <c r="F32" s="47" t="n">
+      <c r="F32" s="52" t="n">
         <v>46111</v>
       </c>
       <c r="G32" s="46" t="inlineStr"/>
@@ -11005,11 +11017,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N32" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N32" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O32" s="46" t="n"/>
-      <c r="P32" s="48" t="n">
+      <c r="P32" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q32" s="46" t="inlineStr"/>
@@ -11035,10 +11047,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E33" s="52" t="n">
         <v>46112</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="52" t="n">
         <v>46118</v>
       </c>
       <c r="G33" s="46" t="inlineStr"/>
@@ -11062,11 +11074,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N33" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N33" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O33" s="46" t="n"/>
-      <c r="P33" s="48" t="n">
+      <c r="P33" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q33" s="46" t="inlineStr"/>
@@ -11092,10 +11104,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="52" t="n">
         <v>46052</v>
       </c>
-      <c r="F34" s="47" t="n">
+      <c r="F34" s="52" t="n">
         <v>46052</v>
       </c>
       <c r="G34" s="46" t="inlineStr"/>
@@ -11119,11 +11131,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N34" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N34" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O34" s="46" t="n"/>
-      <c r="P34" s="48" t="n">
+      <c r="P34" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q34" s="46" t="inlineStr"/>
@@ -11149,10 +11161,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E35" s="47" t="n">
+      <c r="E35" s="52" t="n">
         <v>46049</v>
       </c>
-      <c r="F35" s="47" t="n">
+      <c r="F35" s="52" t="n">
         <v>46049</v>
       </c>
       <c r="G35" s="46" t="inlineStr"/>
@@ -11176,11 +11188,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N35" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N35" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O35" s="46" t="n"/>
-      <c r="P35" s="48" t="n">
+      <c r="P35" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q35" s="46" t="inlineStr"/>
@@ -11206,10 +11218,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E36" s="47" t="n">
+      <c r="E36" s="52" t="n">
         <v>46097</v>
       </c>
-      <c r="F36" s="47" t="n">
+      <c r="F36" s="52" t="n">
         <v>46097</v>
       </c>
       <c r="G36" s="46" t="inlineStr"/>
@@ -11233,11 +11245,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N36" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N36" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O36" s="46" t="n"/>
-      <c r="P36" s="48" t="n">
+      <c r="P36" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q36" s="46" t="inlineStr"/>
@@ -11263,10 +11275,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E37" s="47" t="n">
+      <c r="E37" s="52" t="n">
         <v>46080</v>
       </c>
-      <c r="F37" s="47" t="n">
+      <c r="F37" s="52" t="n">
         <v>46080</v>
       </c>
       <c r="G37" s="46" t="inlineStr"/>
@@ -11290,11 +11302,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N37" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N37" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O37" s="46" t="n"/>
-      <c r="P37" s="48" t="n">
+      <c r="P37" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q37" s="46" t="inlineStr"/>
@@ -11320,10 +11332,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E38" s="47" t="n">
+      <c r="E38" s="52" t="n">
         <v>46065</v>
       </c>
-      <c r="F38" s="47" t="n">
+      <c r="F38" s="52" t="n">
         <v>46065</v>
       </c>
       <c r="G38" s="46" t="inlineStr"/>
@@ -11347,11 +11359,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N38" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N38" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O38" s="46" t="n"/>
-      <c r="P38" s="48" t="n">
+      <c r="P38" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q38" s="46" t="inlineStr"/>
@@ -11377,10 +11389,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E39" s="47" t="n">
+      <c r="E39" s="52" t="n">
         <v>46085</v>
       </c>
-      <c r="F39" s="47" t="n">
+      <c r="F39" s="52" t="n">
         <v>46087</v>
       </c>
       <c r="G39" s="46" t="inlineStr"/>
@@ -11404,11 +11416,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N39" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N39" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O39" s="46" t="n"/>
-      <c r="P39" s="48" t="n">
+      <c r="P39" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q39" s="46" t="inlineStr"/>
@@ -11434,10 +11446,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E40" s="47" t="n">
+      <c r="E40" s="52" t="n">
         <v>46072</v>
       </c>
-      <c r="F40" s="47" t="n">
+      <c r="F40" s="52" t="n">
         <v>46072</v>
       </c>
       <c r="G40" s="46" t="inlineStr"/>
@@ -11461,11 +11473,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N40" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N40" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O40" s="46" t="n"/>
-      <c r="P40" s="48" t="n">
+      <c r="P40" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q40" s="46" t="inlineStr"/>
@@ -11491,10 +11503,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E41" s="47" t="n">
+      <c r="E41" s="52" t="n">
         <v>46111</v>
       </c>
-      <c r="F41" s="47" t="n">
+      <c r="F41" s="52" t="n">
         <v>46113</v>
       </c>
       <c r="G41" s="46" t="inlineStr"/>
@@ -11518,11 +11530,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N41" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N41" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O41" s="46" t="n"/>
-      <c r="P41" s="48" t="n">
+      <c r="P41" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q41" s="46" t="inlineStr"/>
@@ -11548,10 +11560,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E42" s="47" t="n">
+      <c r="E42" s="52" t="n">
         <v>46108</v>
       </c>
-      <c r="F42" s="47" t="n">
+      <c r="F42" s="52" t="n">
         <v>46108</v>
       </c>
       <c r="G42" s="46" t="inlineStr"/>
@@ -11575,11 +11587,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N42" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N42" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O42" s="46" t="n"/>
-      <c r="P42" s="48" t="n">
+      <c r="P42" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q42" s="46" t="inlineStr"/>
@@ -11605,10 +11617,10 @@
           <t>Mudanza, traslado domicilio habitual</t>
         </is>
       </c>
-      <c r="E43" s="47" t="n">
+      <c r="E43" s="52" t="n">
         <v>46104</v>
       </c>
-      <c r="F43" s="47" t="n">
+      <c r="F43" s="52" t="n">
         <v>46104</v>
       </c>
       <c r="G43" s="46" t="inlineStr"/>
@@ -11632,11 +11644,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N43" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N43" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O43" s="46" t="n"/>
-      <c r="P43" s="48" t="n">
+      <c r="P43" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q43" s="46" t="inlineStr"/>
@@ -11662,10 +11674,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E44" s="47" t="n">
+      <c r="E44" s="52" t="n">
         <v>46105</v>
       </c>
-      <c r="F44" s="47" t="n">
+      <c r="F44" s="52" t="n">
         <v>46111</v>
       </c>
       <c r="G44" s="46" t="inlineStr"/>
@@ -11689,11 +11701,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N44" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N44" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O44" s="46" t="n"/>
-      <c r="P44" s="48" t="n">
+      <c r="P44" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q44" s="46" t="inlineStr"/>
@@ -11719,10 +11731,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E45" s="47" t="n">
+      <c r="E45" s="52" t="n">
         <v>46217</v>
       </c>
-      <c r="F45" s="47" t="n">
+      <c r="F45" s="52" t="n">
         <v>46234</v>
       </c>
       <c r="G45" s="46" t="inlineStr"/>
@@ -11746,11 +11758,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N45" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N45" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O45" s="46" t="n"/>
-      <c r="P45" s="48" t="n">
+      <c r="P45" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q45" s="46" t="inlineStr"/>
@@ -11776,10 +11788,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E46" s="47" t="n">
+      <c r="E46" s="52" t="n">
         <v>46100</v>
       </c>
-      <c r="F46" s="47" t="n">
+      <c r="F46" s="52" t="n">
         <v>46100</v>
       </c>
       <c r="G46" s="46" t="inlineStr"/>
@@ -11803,11 +11815,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N46" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N46" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O46" s="46" t="n"/>
-      <c r="P46" s="48" t="n">
+      <c r="P46" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q46" s="46" t="inlineStr"/>
@@ -11833,10 +11845,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="52" t="n">
         <v>46258</v>
       </c>
-      <c r="F47" s="47" t="n">
+      <c r="F47" s="52" t="n">
         <v>46258</v>
       </c>
       <c r="G47" s="46" t="inlineStr"/>
@@ -11860,11 +11872,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N47" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N47" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O47" s="46" t="n"/>
-      <c r="P47" s="48" t="n">
+      <c r="P47" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q47" s="46" t="inlineStr"/>
@@ -11890,10 +11902,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E48" s="47" t="n">
+      <c r="E48" s="52" t="n">
         <v>46111</v>
       </c>
-      <c r="F48" s="47" t="n">
+      <c r="F48" s="52" t="n">
         <v>46113</v>
       </c>
       <c r="G48" s="46" t="inlineStr"/>
@@ -11917,11 +11929,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N48" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N48" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O48" s="46" t="n"/>
-      <c r="P48" s="48" t="n">
+      <c r="P48" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q48" s="46" t="inlineStr"/>
@@ -11947,10 +11959,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E49" s="47" t="n">
+      <c r="E49" s="52" t="n">
         <v>46117</v>
       </c>
-      <c r="F49" s="47" t="n">
+      <c r="F49" s="52" t="n">
         <v>46118</v>
       </c>
       <c r="G49" s="46" t="inlineStr"/>
@@ -11974,11 +11986,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N49" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N49" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O49" s="46" t="n"/>
-      <c r="P49" s="48" t="n">
+      <c r="P49" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q49" s="46" t="inlineStr"/>
@@ -12000,10 +12012,10 @@
         </is>
       </c>
       <c r="D50" s="49" t="inlineStr"/>
-      <c r="E50" s="50" t="n">
+      <c r="E50" s="54" t="n">
         <v>46231</v>
       </c>
-      <c r="F50" s="50" t="n">
+      <c r="F50" s="54" t="n">
         <v>46231</v>
       </c>
       <c r="G50" s="49" t="inlineStr"/>
@@ -12027,11 +12039,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N50" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N50" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O50" s="49" t="n"/>
-      <c r="P50" s="51" t="n">
+      <c r="P50" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q50" s="49" t="inlineStr">
@@ -12057,10 +12069,10 @@
         </is>
       </c>
       <c r="D51" s="49" t="inlineStr"/>
-      <c r="E51" s="50" t="n">
+      <c r="E51" s="54" t="n">
         <v>46237</v>
       </c>
-      <c r="F51" s="50" t="n">
+      <c r="F51" s="54" t="n">
         <v>46255</v>
       </c>
       <c r="G51" s="49" t="inlineStr"/>
@@ -12084,11 +12096,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N51" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N51" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O51" s="49" t="n"/>
-      <c r="P51" s="51" t="n">
+      <c r="P51" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q51" s="49" t="inlineStr">
@@ -12118,10 +12130,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E52" s="47" t="n">
+      <c r="E52" s="52" t="n">
         <v>46112</v>
       </c>
-      <c r="F52" s="47" t="n">
+      <c r="F52" s="52" t="n">
         <v>46113</v>
       </c>
       <c r="G52" s="46" t="inlineStr"/>
@@ -12145,11 +12157,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N52" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N52" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O52" s="46" t="n"/>
-      <c r="P52" s="48" t="n">
+      <c r="P52" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q52" s="46" t="inlineStr"/>
@@ -12175,10 +12187,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E53" s="47" t="n">
+      <c r="E53" s="52" t="n">
         <v>46136</v>
       </c>
-      <c r="F53" s="47" t="n">
+      <c r="F53" s="52" t="n">
         <v>46136</v>
       </c>
       <c r="G53" s="46" t="inlineStr"/>
@@ -12202,11 +12214,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N53" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N53" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O53" s="46" t="n"/>
-      <c r="P53" s="48" t="n">
+      <c r="P53" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q53" s="46" t="inlineStr"/>
@@ -12228,10 +12240,10 @@
         </is>
       </c>
       <c r="D54" s="49" t="inlineStr"/>
-      <c r="E54" s="50" t="n">
+      <c r="E54" s="54" t="n">
         <v>46142</v>
       </c>
-      <c r="F54" s="50" t="n">
+      <c r="F54" s="54" t="n">
         <v>46142</v>
       </c>
       <c r="G54" s="49" t="inlineStr"/>
@@ -12255,11 +12267,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N54" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N54" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O54" s="49" t="n"/>
-      <c r="P54" s="51" t="n">
+      <c r="P54" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q54" s="49" t="inlineStr">
@@ -12289,10 +12301,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E55" s="47" t="n">
+      <c r="E55" s="52" t="n">
         <v>46156</v>
       </c>
-      <c r="F55" s="47" t="n">
+      <c r="F55" s="52" t="n">
         <v>46160</v>
       </c>
       <c r="G55" s="46" t="inlineStr"/>
@@ -12316,11 +12328,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N55" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N55" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O55" s="46" t="n"/>
-      <c r="P55" s="48" t="n">
+      <c r="P55" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q55" s="46" t="inlineStr"/>
@@ -12346,10 +12358,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E56" s="47" t="n">
+      <c r="E56" s="52" t="n">
         <v>46192</v>
       </c>
-      <c r="F56" s="47" t="n">
+      <c r="F56" s="52" t="n">
         <v>46192</v>
       </c>
       <c r="G56" s="46" t="inlineStr"/>
@@ -12373,11 +12385,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N56" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N56" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O56" s="46" t="n"/>
-      <c r="P56" s="48" t="n">
+      <c r="P56" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q56" s="46" t="inlineStr"/>
@@ -12403,10 +12415,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E57" s="47" t="n">
+      <c r="E57" s="52" t="n">
         <v>46191</v>
       </c>
-      <c r="F57" s="47" t="n">
+      <c r="F57" s="52" t="n">
         <v>46191</v>
       </c>
       <c r="G57" s="46" t="inlineStr"/>
@@ -12430,11 +12442,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N57" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N57" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O57" s="46" t="n"/>
-      <c r="P57" s="48" t="n">
+      <c r="P57" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q57" s="46" t="inlineStr"/>
@@ -12460,10 +12472,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E58" s="47" t="n">
+      <c r="E58" s="52" t="n">
         <v>46154</v>
       </c>
-      <c r="F58" s="47" t="n">
+      <c r="F58" s="52" t="n">
         <v>46154</v>
       </c>
       <c r="G58" s="46" t="inlineStr"/>
@@ -12487,11 +12499,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N58" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N58" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O58" s="46" t="n"/>
-      <c r="P58" s="48" t="n">
+      <c r="P58" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q58" s="46" t="inlineStr"/>
@@ -12517,10 +12529,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E59" s="47" t="n">
+      <c r="E59" s="52" t="n">
         <v>46150</v>
       </c>
-      <c r="F59" s="47" t="n">
+      <c r="F59" s="52" t="n">
         <v>46150</v>
       </c>
       <c r="G59" s="46" t="inlineStr"/>
@@ -12544,11 +12556,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N59" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N59" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O59" s="46" t="n"/>
-      <c r="P59" s="48" t="n">
+      <c r="P59" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q59" s="46" t="inlineStr"/>
@@ -12574,10 +12586,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E60" s="47" t="n">
+      <c r="E60" s="52" t="n">
         <v>46149</v>
       </c>
-      <c r="F60" s="47" t="n">
+      <c r="F60" s="52" t="n">
         <v>46149</v>
       </c>
       <c r="G60" s="46" t="inlineStr">
@@ -12609,11 +12621,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N60" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N60" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O60" s="46" t="n"/>
-      <c r="P60" s="48" t="n">
+      <c r="P60" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q60" s="46" t="inlineStr"/>
@@ -12639,10 +12651,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E61" s="47" t="n">
+      <c r="E61" s="52" t="n">
         <v>46125</v>
       </c>
-      <c r="F61" s="47" t="n">
+      <c r="F61" s="52" t="n">
         <v>46129</v>
       </c>
       <c r="G61" s="46" t="inlineStr"/>
@@ -12666,11 +12678,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N61" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N61" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O61" s="46" t="n"/>
-      <c r="P61" s="48" t="n">
+      <c r="P61" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q61" s="46" t="inlineStr"/>
@@ -12696,10 +12708,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E62" s="50" t="n">
+      <c r="E62" s="54" t="n">
         <v>46223</v>
       </c>
-      <c r="F62" s="50" t="n">
+      <c r="F62" s="54" t="n">
         <v>46237</v>
       </c>
       <c r="G62" s="49" t="inlineStr"/>
@@ -12723,11 +12735,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N62" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N62" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O62" s="49" t="n"/>
-      <c r="P62" s="51" t="n">
+      <c r="P62" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q62" s="49" t="inlineStr">
@@ -12757,10 +12769,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E63" s="50" t="n">
+      <c r="E63" s="54" t="n">
         <v>46238</v>
       </c>
-      <c r="F63" s="50" t="n">
+      <c r="F63" s="54" t="n">
         <v>46244</v>
       </c>
       <c r="G63" s="49" t="inlineStr"/>
@@ -12784,11 +12796,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N63" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N63" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O63" s="49" t="n"/>
-      <c r="P63" s="51" t="n">
+      <c r="P63" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q63" s="49" t="inlineStr">
@@ -12818,10 +12830,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E64" s="47" t="n">
+      <c r="E64" s="52" t="n">
         <v>46209</v>
       </c>
-      <c r="F64" s="47" t="n">
+      <c r="F64" s="52" t="n">
         <v>46213</v>
       </c>
       <c r="G64" s="46" t="inlineStr"/>
@@ -12845,11 +12857,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N64" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N64" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O64" s="46" t="n"/>
-      <c r="P64" s="48" t="n">
+      <c r="P64" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q64" s="46" t="inlineStr"/>
@@ -12875,10 +12887,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E65" s="47" t="n">
+      <c r="E65" s="52" t="n">
         <v>46244</v>
       </c>
-      <c r="F65" s="47" t="n">
+      <c r="F65" s="52" t="n">
         <v>46257</v>
       </c>
       <c r="G65" s="46" t="inlineStr"/>
@@ -12902,11 +12914,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N65" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N65" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O65" s="46" t="n"/>
-      <c r="P65" s="48" t="n">
+      <c r="P65" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q65" s="46" t="inlineStr"/>
@@ -12932,10 +12944,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E66" s="47" t="n">
+      <c r="E66" s="52" t="n">
         <v>46182</v>
       </c>
-      <c r="F66" s="47" t="n">
+      <c r="F66" s="52" t="n">
         <v>46184</v>
       </c>
       <c r="G66" s="46" t="inlineStr"/>
@@ -12959,11 +12971,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N66" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N66" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O66" s="46" t="n"/>
-      <c r="P66" s="48" t="n">
+      <c r="P66" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q66" s="46" t="inlineStr"/>
@@ -12989,10 +13001,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E67" s="47" t="n">
+      <c r="E67" s="52" t="n">
         <v>46206</v>
       </c>
-      <c r="F67" s="47" t="n">
+      <c r="F67" s="52" t="n">
         <v>46206</v>
       </c>
       <c r="G67" s="46" t="inlineStr"/>
@@ -13016,11 +13028,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N67" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N67" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O67" s="46" t="n"/>
-      <c r="P67" s="48" t="n">
+      <c r="P67" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q67" s="46" t="inlineStr"/>
@@ -13046,10 +13058,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E68" s="47" t="n">
+      <c r="E68" s="52" t="n">
         <v>46195</v>
       </c>
-      <c r="F68" s="47" t="n">
+      <c r="F68" s="52" t="n">
         <v>46195</v>
       </c>
       <c r="G68" s="46" t="inlineStr"/>
@@ -13073,11 +13085,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N68" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N68" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O68" s="46" t="n"/>
-      <c r="P68" s="48" t="n">
+      <c r="P68" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q68" s="46" t="inlineStr"/>
@@ -13103,10 +13115,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E69" s="47" t="n">
+      <c r="E69" s="52" t="n">
         <v>46194</v>
       </c>
-      <c r="F69" s="47" t="n">
+      <c r="F69" s="52" t="n">
         <v>46195</v>
       </c>
       <c r="G69" s="46" t="inlineStr"/>
@@ -13130,11 +13142,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N69" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N69" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O69" s="46" t="n"/>
-      <c r="P69" s="48" t="n">
+      <c r="P69" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q69" s="46" t="inlineStr"/>
@@ -13160,10 +13172,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E70" s="50" t="n">
+      <c r="E70" s="54" t="n">
         <v>46192</v>
       </c>
-      <c r="F70" s="50" t="n">
+      <c r="F70" s="54" t="n">
         <v>46192</v>
       </c>
       <c r="G70" s="49" t="inlineStr"/>
@@ -13187,11 +13199,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N70" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N70" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O70" s="49" t="n"/>
-      <c r="P70" s="51" t="n">
+      <c r="P70" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q70" s="49" t="inlineStr">
@@ -13221,10 +13233,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E71" s="47" t="n">
+      <c r="E71" s="52" t="n">
         <v>46199</v>
       </c>
-      <c r="F71" s="47" t="n">
+      <c r="F71" s="52" t="n">
         <v>46199</v>
       </c>
       <c r="G71" s="46" t="inlineStr"/>
@@ -13248,11 +13260,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N71" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N71" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O71" s="46" t="n"/>
-      <c r="P71" s="48" t="n">
+      <c r="P71" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q71" s="46" t="inlineStr"/>
@@ -13278,10 +13290,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E72" s="47" t="n">
+      <c r="E72" s="52" t="n">
         <v>46216</v>
       </c>
-      <c r="F72" s="47" t="n">
+      <c r="F72" s="52" t="n">
         <v>46233</v>
       </c>
       <c r="G72" s="46" t="inlineStr"/>
@@ -13305,11 +13317,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N72" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N72" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O72" s="46" t="n"/>
-      <c r="P72" s="48" t="n">
+      <c r="P72" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q72" s="46" t="inlineStr"/>
@@ -13335,10 +13347,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E73" s="47" t="n">
+      <c r="E73" s="52" t="n">
         <v>46234</v>
       </c>
-      <c r="F73" s="47" t="n">
+      <c r="F73" s="52" t="n">
         <v>46234</v>
       </c>
       <c r="G73" s="46" t="inlineStr"/>
@@ -13362,11 +13374,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N73" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N73" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O73" s="46" t="n"/>
-      <c r="P73" s="48" t="n">
+      <c r="P73" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q73" s="46" t="inlineStr"/>
@@ -13392,10 +13404,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E74" s="47" t="n">
+      <c r="E74" s="52" t="n">
         <v>46237</v>
       </c>
-      <c r="F74" s="47" t="n">
+      <c r="F74" s="52" t="n">
         <v>46241</v>
       </c>
       <c r="G74" s="46" t="inlineStr"/>
@@ -13419,11 +13431,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N74" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N74" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O74" s="46" t="n"/>
-      <c r="P74" s="48" t="n">
+      <c r="P74" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q74" s="46" t="inlineStr"/>
@@ -13449,10 +13461,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E75" s="47" t="n">
+      <c r="E75" s="52" t="n">
         <v>46246</v>
       </c>
-      <c r="F75" s="47" t="n">
+      <c r="F75" s="52" t="n">
         <v>46248</v>
       </c>
       <c r="G75" s="46" t="inlineStr"/>
@@ -13476,11 +13488,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N75" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N75" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O75" s="46" t="n"/>
-      <c r="P75" s="48" t="n">
+      <c r="P75" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q75" s="46" t="inlineStr"/>
@@ -13506,10 +13518,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E76" s="47" t="n">
+      <c r="E76" s="52" t="n">
         <v>46255</v>
       </c>
-      <c r="F76" s="47" t="n">
+      <c r="F76" s="52" t="n">
         <v>46272</v>
       </c>
       <c r="G76" s="46" t="inlineStr"/>
@@ -13533,11 +13545,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N76" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N76" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O76" s="46" t="n"/>
-      <c r="P76" s="48" t="n">
+      <c r="P76" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q76" s="46" t="inlineStr"/>
@@ -13563,10 +13575,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E77" s="47" t="n">
+      <c r="E77" s="52" t="n">
         <v>46238</v>
       </c>
-      <c r="F77" s="47" t="n">
+      <c r="F77" s="52" t="n">
         <v>46251</v>
       </c>
       <c r="G77" s="46" t="inlineStr"/>
@@ -13590,11 +13602,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N77" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N77" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O77" s="46" t="n"/>
-      <c r="P77" s="48" t="n">
+      <c r="P77" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q77" s="46" t="inlineStr"/>
@@ -13620,10 +13632,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E78" s="47" t="n">
+      <c r="E78" s="52" t="n">
         <v>46244</v>
       </c>
-      <c r="F78" s="47" t="n">
+      <c r="F78" s="52" t="n">
         <v>46255</v>
       </c>
       <c r="G78" s="46" t="inlineStr"/>
@@ -13647,11 +13659,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N78" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N78" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O78" s="46" t="n"/>
-      <c r="P78" s="48" t="n">
+      <c r="P78" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q78" s="46" t="inlineStr"/>
@@ -13677,10 +13689,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E79" s="47" t="n">
+      <c r="E79" s="52" t="n">
         <v>46269</v>
       </c>
-      <c r="F79" s="47" t="n">
+      <c r="F79" s="52" t="n">
         <v>46276</v>
       </c>
       <c r="G79" s="46" t="inlineStr"/>
@@ -13704,11 +13716,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N79" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N79" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O79" s="46" t="n"/>
-      <c r="P79" s="48" t="n">
+      <c r="P79" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q79" s="46" t="inlineStr"/>
@@ -13734,10 +13746,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E80" s="47" t="n">
+      <c r="E80" s="52" t="n">
         <v>46238</v>
       </c>
-      <c r="F80" s="47" t="n">
+      <c r="F80" s="52" t="n">
         <v>46240</v>
       </c>
       <c r="G80" s="46" t="inlineStr"/>
@@ -13761,11 +13773,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N80" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N80" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O80" s="46" t="n"/>
-      <c r="P80" s="48" t="n">
+      <c r="P80" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q80" s="46" t="inlineStr"/>
@@ -13791,10 +13803,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E81" s="47" t="n">
+      <c r="E81" s="52" t="n">
         <v>46251</v>
       </c>
-      <c r="F81" s="47" t="n">
+      <c r="F81" s="52" t="n">
         <v>46260</v>
       </c>
       <c r="G81" s="46" t="inlineStr"/>
@@ -13818,11 +13830,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N81" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N81" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O81" s="46" t="n"/>
-      <c r="P81" s="48" t="n">
+      <c r="P81" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q81" s="46" t="inlineStr"/>
@@ -13848,10 +13860,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E82" s="47" t="n">
+      <c r="E82" s="52" t="n">
         <v>46240</v>
       </c>
-      <c r="F82" s="47" t="n">
+      <c r="F82" s="52" t="n">
         <v>46240</v>
       </c>
       <c r="G82" s="46" t="inlineStr"/>
@@ -13875,11 +13887,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N82" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N82" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O82" s="46" t="n"/>
-      <c r="P82" s="48" t="n">
+      <c r="P82" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q82" s="46" t="inlineStr"/>
@@ -13905,10 +13917,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E83" s="47" t="n">
+      <c r="E83" s="52" t="n">
         <v>46241</v>
       </c>
-      <c r="F83" s="47" t="n">
+      <c r="F83" s="52" t="n">
         <v>46241</v>
       </c>
       <c r="G83" s="46" t="inlineStr"/>
@@ -13932,11 +13944,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N83" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N83" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O83" s="46" t="n"/>
-      <c r="P83" s="48" t="n">
+      <c r="P83" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q83" s="46" t="inlineStr"/>
@@ -13962,10 +13974,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E84" s="47" t="n">
+      <c r="E84" s="52" t="n">
         <v>46251</v>
       </c>
-      <c r="F84" s="47" t="n">
+      <c r="F84" s="52" t="n">
         <v>46255</v>
       </c>
       <c r="G84" s="46" t="inlineStr"/>
@@ -13989,11 +14001,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N84" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N84" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O84" s="46" t="n"/>
-      <c r="P84" s="48" t="n">
+      <c r="P84" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q84" s="46" t="inlineStr"/>
@@ -14019,10 +14031,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E85" s="47" t="n">
+      <c r="E85" s="52" t="n">
         <v>46255</v>
       </c>
-      <c r="F85" s="47" t="n">
+      <c r="F85" s="52" t="n">
         <v>46255</v>
       </c>
       <c r="G85" s="46" t="inlineStr"/>
@@ -14046,11 +14058,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N85" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N85" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O85" s="46" t="n"/>
-      <c r="P85" s="48" t="n">
+      <c r="P85" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q85" s="46" t="inlineStr"/>
@@ -14076,10 +14088,10 @@
           <t>Mudanza, traslado domicilio habitual</t>
         </is>
       </c>
-      <c r="E86" s="47" t="n">
+      <c r="E86" s="52" t="n">
         <v>46268</v>
       </c>
-      <c r="F86" s="47" t="n">
+      <c r="F86" s="52" t="n">
         <v>46268</v>
       </c>
       <c r="G86" s="46" t="inlineStr"/>
@@ -14103,11 +14115,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N86" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N86" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O86" s="46" t="n"/>
-      <c r="P86" s="48" t="n">
+      <c r="P86" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q86" s="46" t="inlineStr"/>
@@ -14133,10 +14145,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E87" s="47" t="n">
+      <c r="E87" s="52" t="n">
         <v>46244</v>
       </c>
-      <c r="F87" s="47" t="n">
+      <c r="F87" s="52" t="n">
         <v>46248</v>
       </c>
       <c r="G87" s="46" t="inlineStr"/>
@@ -14160,11 +14172,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N87" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N87" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O87" s="46" t="n"/>
-      <c r="P87" s="48" t="n">
+      <c r="P87" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q87" s="46" t="inlineStr"/>
@@ -14190,10 +14202,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E88" s="47" t="n">
+      <c r="E88" s="52" t="n">
         <v>46251</v>
       </c>
-      <c r="F88" s="47" t="n">
+      <c r="F88" s="52" t="n">
         <v>46255</v>
       </c>
       <c r="G88" s="46" t="inlineStr"/>
@@ -14217,11 +14229,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N88" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N88" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O88" s="46" t="n"/>
-      <c r="P88" s="48" t="n">
+      <c r="P88" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q88" s="46" t="inlineStr"/>
@@ -14247,10 +14259,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E89" s="47" t="n">
+      <c r="E89" s="52" t="n">
         <v>46275</v>
       </c>
-      <c r="F89" s="47" t="n">
+      <c r="F89" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="G89" s="46" t="inlineStr">
@@ -14282,11 +14294,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N89" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N89" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O89" s="46" t="n"/>
-      <c r="P89" s="48" t="n">
+      <c r="P89" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q89" s="46" t="inlineStr"/>
@@ -14312,10 +14324,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E90" s="47" t="n">
+      <c r="E90" s="52" t="n">
         <v>46261</v>
       </c>
-      <c r="F90" s="47" t="n">
+      <c r="F90" s="52" t="n">
         <v>46261</v>
       </c>
       <c r="G90" s="46" t="inlineStr"/>
@@ -14339,11 +14351,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N90" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N90" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O90" s="46" t="n"/>
-      <c r="P90" s="48" t="n">
+      <c r="P90" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q90" s="46" t="inlineStr"/>
@@ -14369,10 +14381,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E91" s="47" t="n">
+      <c r="E91" s="52" t="n">
         <v>46262</v>
       </c>
-      <c r="F91" s="47" t="n">
+      <c r="F91" s="52" t="n">
         <v>46262</v>
       </c>
       <c r="G91" s="46" t="inlineStr"/>
@@ -14396,11 +14408,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N91" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N91" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O91" s="46" t="n"/>
-      <c r="P91" s="48" t="n">
+      <c r="P91" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q91" s="46" t="inlineStr"/>
@@ -14426,10 +14438,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E92" s="47" t="n">
+      <c r="E92" s="52" t="n">
         <v>46272</v>
       </c>
-      <c r="F92" s="47" t="n">
+      <c r="F92" s="52" t="n">
         <v>46276</v>
       </c>
       <c r="G92" s="46" t="inlineStr"/>
@@ -14453,11 +14465,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N92" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N92" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O92" s="46" t="n"/>
-      <c r="P92" s="48" t="n">
+      <c r="P92" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q92" s="46" t="inlineStr"/>
@@ -14483,10 +14495,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E93" s="47" t="n">
+      <c r="E93" s="52" t="n">
         <v>46296</v>
       </c>
-      <c r="F93" s="47" t="n">
+      <c r="F93" s="52" t="n">
         <v>46300</v>
       </c>
       <c r="G93" s="46" t="inlineStr"/>
@@ -14510,11 +14522,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N93" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N93" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O93" s="46" t="n"/>
-      <c r="P93" s="48" t="n">
+      <c r="P93" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q93" s="46" t="inlineStr"/>
@@ -14540,10 +14552,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E94" s="50" t="n">
+      <c r="E94" s="54" t="n">
         <v>46276</v>
       </c>
-      <c r="F94" s="50" t="n">
+      <c r="F94" s="54" t="n">
         <v>46276</v>
       </c>
       <c r="G94" s="49" t="inlineStr"/>
@@ -14567,11 +14579,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N94" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N94" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O94" s="49" t="n"/>
-      <c r="P94" s="51" t="n">
+      <c r="P94" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q94" s="49" t="inlineStr">
@@ -14601,10 +14613,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E95" s="47" t="n">
+      <c r="E95" s="52" t="n">
         <v>46290</v>
       </c>
-      <c r="F95" s="47" t="n">
+      <c r="F95" s="52" t="n">
         <v>46290</v>
       </c>
       <c r="G95" s="46" t="inlineStr"/>
@@ -14628,11 +14640,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N95" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N95" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O95" s="46" t="n"/>
-      <c r="P95" s="48" t="n">
+      <c r="P95" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q95" s="46" t="inlineStr"/>
@@ -14658,10 +14670,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E96" s="47" t="n">
+      <c r="E96" s="52" t="n">
         <v>46310</v>
       </c>
-      <c r="F96" s="47" t="n">
+      <c r="F96" s="52" t="n">
         <v>46316</v>
       </c>
       <c r="G96" s="46" t="inlineStr"/>
@@ -14689,11 +14701,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N96" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N96" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O96" s="46" t="n"/>
-      <c r="P96" s="48" t="n">
+      <c r="P96" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q96" s="46" t="inlineStr"/>
@@ -14719,10 +14731,10 @@
           <t>Mudanza, traslado domicilio habitual</t>
         </is>
       </c>
-      <c r="E97" s="47" t="n">
+      <c r="E97" s="52" t="n">
         <v>46300</v>
       </c>
-      <c r="F97" s="47" t="n">
+      <c r="F97" s="52" t="n">
         <v>46300</v>
       </c>
       <c r="G97" s="46" t="inlineStr"/>
@@ -14746,11 +14758,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N97" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N97" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O97" s="46" t="n"/>
-      <c r="P97" s="48" t="n">
+      <c r="P97" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q97" s="46" t="inlineStr"/>
@@ -14776,10 +14788,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E98" s="47" t="n">
+      <c r="E98" s="52" t="n">
         <v>46336</v>
       </c>
-      <c r="F98" s="47" t="n">
+      <c r="F98" s="52" t="n">
         <v>46336</v>
       </c>
       <c r="G98" s="46" t="inlineStr">
@@ -14815,11 +14827,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N98" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N98" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O98" s="46" t="n"/>
-      <c r="P98" s="48" t="n">
+      <c r="P98" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q98" s="46" t="inlineStr"/>
@@ -14845,10 +14857,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E99" s="47" t="n">
+      <c r="E99" s="52" t="n">
         <v>46304</v>
       </c>
-      <c r="F99" s="47" t="n">
+      <c r="F99" s="52" t="n">
         <v>46304</v>
       </c>
       <c r="G99" s="46" t="inlineStr"/>
@@ -14872,11 +14884,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N99" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N99" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O99" s="46" t="n"/>
-      <c r="P99" s="48" t="n">
+      <c r="P99" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q99" s="46" t="inlineStr"/>
@@ -14902,10 +14914,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E100" s="47" t="n">
+      <c r="E100" s="52" t="n">
         <v>46308</v>
       </c>
-      <c r="F100" s="47" t="n">
+      <c r="F100" s="52" t="n">
         <v>46308</v>
       </c>
       <c r="G100" s="46" t="inlineStr"/>
@@ -14933,11 +14945,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N100" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N100" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O100" s="46" t="n"/>
-      <c r="P100" s="48" t="n">
+      <c r="P100" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q100" s="46" t="inlineStr"/>
@@ -14963,10 +14975,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E101" s="47" t="n">
+      <c r="E101" s="52" t="n">
         <v>46301</v>
       </c>
-      <c r="F101" s="47" t="n">
+      <c r="F101" s="52" t="n">
         <v>46301</v>
       </c>
       <c r="G101" s="46" t="inlineStr"/>
@@ -14990,11 +15002,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N101" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N101" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O101" s="46" t="n"/>
-      <c r="P101" s="48" t="n">
+      <c r="P101" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q101" s="46" t="inlineStr"/>
@@ -15016,10 +15028,10 @@
         </is>
       </c>
       <c r="D102" s="49" t="inlineStr"/>
-      <c r="E102" s="50" t="n">
+      <c r="E102" s="54" t="n">
         <v>46297</v>
       </c>
-      <c r="F102" s="50" t="n">
+      <c r="F102" s="54" t="n">
         <v>46297</v>
       </c>
       <c r="G102" s="49" t="inlineStr"/>
@@ -15043,11 +15055,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N102" s="51" t="n">
-        <v>46323.51385416667</v>
+      <c r="N102" s="55" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O102" s="49" t="n"/>
-      <c r="P102" s="51" t="n">
+      <c r="P102" s="55" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q102" s="49" t="inlineStr">
@@ -15077,10 +15089,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E103" s="47" t="n">
+      <c r="E103" s="52" t="n">
         <v>46300</v>
       </c>
-      <c r="F103" s="47" t="n">
+      <c r="F103" s="52" t="n">
         <v>46300</v>
       </c>
       <c r="G103" s="46" t="inlineStr"/>
@@ -15104,11 +15116,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N103" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N103" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O103" s="46" t="n"/>
-      <c r="P103" s="48" t="n">
+      <c r="P103" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q103" s="46" t="inlineStr"/>
@@ -15134,10 +15146,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E104" s="47" t="n">
+      <c r="E104" s="52" t="n">
         <v>46377</v>
       </c>
-      <c r="F104" s="47" t="n">
+      <c r="F104" s="52" t="n">
         <v>46379</v>
       </c>
       <c r="G104" s="46" t="inlineStr"/>
@@ -15165,11 +15177,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N104" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N104" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O104" s="46" t="n"/>
-      <c r="P104" s="48" t="n">
+      <c r="P104" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q104" s="46" t="inlineStr"/>
@@ -15195,10 +15207,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E105" s="47" t="n">
+      <c r="E105" s="52" t="n">
         <v>46302</v>
       </c>
-      <c r="F105" s="47" t="n">
+      <c r="F105" s="52" t="n">
         <v>46302</v>
       </c>
       <c r="G105" s="46" t="inlineStr"/>
@@ -15222,11 +15234,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N105" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N105" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O105" s="46" t="n"/>
-      <c r="P105" s="48" t="n">
+      <c r="P105" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q105" s="46" t="inlineStr"/>
@@ -15252,10 +15264,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E106" s="47" t="n">
+      <c r="E106" s="52" t="n">
         <v>46308</v>
       </c>
-      <c r="F106" s="47" t="n">
+      <c r="F106" s="52" t="n">
         <v>46308</v>
       </c>
       <c r="G106" s="46" t="inlineStr"/>
@@ -15283,11 +15295,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N106" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N106" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O106" s="46" t="n"/>
-      <c r="P106" s="48" t="n">
+      <c r="P106" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q106" s="46" t="inlineStr"/>
@@ -15313,10 +15325,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E107" s="47" t="n">
+      <c r="E107" s="52" t="n">
         <v>46304</v>
       </c>
-      <c r="F107" s="47" t="n">
+      <c r="F107" s="52" t="n">
         <v>46304</v>
       </c>
       <c r="G107" s="46" t="inlineStr"/>
@@ -15340,11 +15352,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N107" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N107" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O107" s="46" t="n"/>
-      <c r="P107" s="48" t="n">
+      <c r="P107" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q107" s="46" t="inlineStr"/>
@@ -15370,10 +15382,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E108" s="47" t="n">
+      <c r="E108" s="52" t="n">
         <v>46317</v>
       </c>
-      <c r="F108" s="47" t="n">
+      <c r="F108" s="52" t="n">
         <v>46317</v>
       </c>
       <c r="G108" s="46" t="inlineStr"/>
@@ -15401,11 +15413,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N108" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N108" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O108" s="46" t="n"/>
-      <c r="P108" s="48" t="n">
+      <c r="P108" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q108" s="46" t="inlineStr"/>
@@ -15431,10 +15443,10 @@
           <t>Ausencia</t>
         </is>
       </c>
-      <c r="E109" s="47" t="n">
+      <c r="E109" s="52" t="n">
         <v>46345</v>
       </c>
-      <c r="F109" s="47" t="n">
+      <c r="F109" s="52" t="n">
         <v>46345</v>
       </c>
       <c r="G109" s="46" t="inlineStr">
@@ -15470,11 +15482,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N109" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N109" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O109" s="46" t="n"/>
-      <c r="P109" s="48" t="n">
+      <c r="P109" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q109" s="46" t="inlineStr"/>
@@ -15500,10 +15512,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E110" s="47" t="n">
+      <c r="E110" s="52" t="n">
         <v>46365</v>
       </c>
-      <c r="F110" s="47" t="n">
+      <c r="F110" s="52" t="n">
         <v>46367</v>
       </c>
       <c r="G110" s="46" t="inlineStr"/>
@@ -15531,11 +15543,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N110" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N110" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O110" s="46" t="n"/>
-      <c r="P110" s="48" t="n">
+      <c r="P110" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q110" s="46" t="inlineStr"/>
@@ -15561,10 +15573,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E111" s="47" t="n">
+      <c r="E111" s="52" t="n">
         <v>46379</v>
       </c>
-      <c r="F111" s="47" t="n">
+      <c r="F111" s="52" t="n">
         <v>46394</v>
       </c>
       <c r="G111" s="46" t="inlineStr"/>
@@ -15592,11 +15604,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N111" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N111" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O111" s="46" t="n"/>
-      <c r="P111" s="48" t="n">
+      <c r="P111" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q111" s="46" t="inlineStr"/>
@@ -15622,10 +15634,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E112" s="47" t="n">
+      <c r="E112" s="52" t="n">
         <v>46318</v>
       </c>
-      <c r="F112" s="47" t="n">
+      <c r="F112" s="52" t="n">
         <v>46319</v>
       </c>
       <c r="G112" s="46" t="inlineStr"/>
@@ -15653,11 +15665,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N112" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N112" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O112" s="46" t="n"/>
-      <c r="P112" s="48" t="n">
+      <c r="P112" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q112" s="46" t="inlineStr"/>
@@ -15683,10 +15695,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E113" s="47" t="n">
+      <c r="E113" s="52" t="n">
         <v>46353</v>
       </c>
-      <c r="F113" s="47" t="n">
+      <c r="F113" s="52" t="n">
         <v>46353</v>
       </c>
       <c r="G113" s="46" t="inlineStr"/>
@@ -15714,11 +15726,11 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="N113" s="48" t="n">
-        <v>46323.51385416667</v>
+      <c r="N113" s="53" t="n">
+        <v>46324.52037037037</v>
       </c>
       <c r="O113" s="46" t="n"/>
-      <c r="P113" s="48" t="n">
+      <c r="P113" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
       <c r="Q113" s="46" t="inlineStr"/>
@@ -15744,10 +15756,10 @@
           <t>Vacaciones🏖️</t>
         </is>
       </c>
-      <c r="E114" s="47" t="n">
+      <c r="E114" s="52" t="n">
         <v>46324</v>
       </c>
-      <c r="F114" s="47" t="n">
+      <c r="F114" s="52" t="n">
         <v>46324</v>
       </c>
       <c r="G114" s="46" t="inlineStr"/>
@@ -15775,14 +15787,75 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="N114" s="48" t="n">
+      <c r="N114" s="53" t="n">
+        <v>46324.52037037037</v>
+      </c>
+      <c r="O114" s="46" t="n"/>
+      <c r="P114" s="53" t="n">
         <v>46323.51385416667</v>
       </c>
-      <c r="O114" s="46" t="n"/>
-      <c r="P114" s="48" t="n">
-        <v>46323.51385416667</v>
-      </c>
       <c r="Q114" s="46" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="46" t="inlineStr">
+        <is>
+          <t>23652108</t>
+        </is>
+      </c>
+      <c r="B115" s="46" t="inlineStr">
+        <is>
+          <t>Sofía</t>
+        </is>
+      </c>
+      <c r="C115" s="46" t="inlineStr">
+        <is>
+          <t>SOFIA MEDIALDEA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="D115" s="46" t="inlineStr">
+        <is>
+          <t>Vacaciones🏖️</t>
+        </is>
+      </c>
+      <c r="E115" s="52" t="n">
+        <v>46339</v>
+      </c>
+      <c r="F115" s="52" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G115" s="46" t="inlineStr"/>
+      <c r="H115" s="46" t="inlineStr"/>
+      <c r="I115" s="46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J115" s="46" t="inlineStr">
+        <is>
+          <t>9 NOV, 16 NOV, 23 NOV</t>
+        </is>
+      </c>
+      <c r="K115" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L115" s="46" t="inlineStr">
+        <is>
+          <t>CONFIRMADA</t>
+        </is>
+      </c>
+      <c r="M115" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N115" s="53" t="n">
+        <v>46324.52037037037</v>
+      </c>
+      <c r="O115" s="46" t="n"/>
+      <c r="P115" s="53" t="n">
+        <v>46324.52037037037</v>
+      </c>
+      <c r="Q115" s="46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -24,11 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY HH:MM"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -9308,7 +9306,7 @@
         </is>
       </c>
       <c r="N2" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O2" s="46" t="n"/>
       <c r="P2" s="53" t="n">
@@ -9365,7 +9363,7 @@
         </is>
       </c>
       <c r="N3" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O3" s="46" t="n"/>
       <c r="P3" s="53" t="n">
@@ -9422,7 +9420,7 @@
         </is>
       </c>
       <c r="N4" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O4" s="46" t="n"/>
       <c r="P4" s="53" t="n">
@@ -9479,7 +9477,7 @@
         </is>
       </c>
       <c r="N5" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O5" s="46" t="n"/>
       <c r="P5" s="53" t="n">
@@ -9536,7 +9534,7 @@
         </is>
       </c>
       <c r="N6" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O6" s="46" t="n"/>
       <c r="P6" s="53" t="n">
@@ -9593,7 +9591,7 @@
         </is>
       </c>
       <c r="N7" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O7" s="46" t="n"/>
       <c r="P7" s="53" t="n">
@@ -9650,7 +9648,7 @@
         </is>
       </c>
       <c r="N8" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O8" s="46" t="n"/>
       <c r="P8" s="53" t="n">
@@ -9707,7 +9705,7 @@
         </is>
       </c>
       <c r="N9" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O9" s="46" t="n"/>
       <c r="P9" s="53" t="n">
@@ -9764,7 +9762,7 @@
         </is>
       </c>
       <c r="N10" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O10" s="46" t="n"/>
       <c r="P10" s="53" t="n">
@@ -9821,7 +9819,7 @@
         </is>
       </c>
       <c r="N11" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O11" s="46" t="n"/>
       <c r="P11" s="53" t="n">
@@ -9878,7 +9876,7 @@
         </is>
       </c>
       <c r="N12" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O12" s="46" t="n"/>
       <c r="P12" s="53" t="n">
@@ -9935,7 +9933,7 @@
         </is>
       </c>
       <c r="N13" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O13" s="46" t="n"/>
       <c r="P13" s="53" t="n">
@@ -9988,7 +9986,7 @@
         </is>
       </c>
       <c r="N14" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O14" s="49" t="n"/>
       <c r="P14" s="55" t="n">
@@ -10049,7 +10047,7 @@
         </is>
       </c>
       <c r="N15" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O15" s="46" t="n"/>
       <c r="P15" s="53" t="n">
@@ -10106,7 +10104,7 @@
         </is>
       </c>
       <c r="N16" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O16" s="46" t="n"/>
       <c r="P16" s="53" t="n">
@@ -10163,7 +10161,7 @@
         </is>
       </c>
       <c r="N17" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O17" s="46" t="n"/>
       <c r="P17" s="53" t="n">
@@ -10220,7 +10218,7 @@
         </is>
       </c>
       <c r="N18" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O18" s="46" t="n"/>
       <c r="P18" s="53" t="n">
@@ -10277,7 +10275,7 @@
         </is>
       </c>
       <c r="N19" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O19" s="46" t="n"/>
       <c r="P19" s="53" t="n">
@@ -10334,7 +10332,7 @@
         </is>
       </c>
       <c r="N20" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O20" s="46" t="n"/>
       <c r="P20" s="53" t="n">
@@ -10391,7 +10389,7 @@
         </is>
       </c>
       <c r="N21" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O21" s="46" t="n"/>
       <c r="P21" s="53" t="n">
@@ -10448,7 +10446,7 @@
         </is>
       </c>
       <c r="N22" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O22" s="46" t="n"/>
       <c r="P22" s="53" t="n">
@@ -10505,7 +10503,7 @@
         </is>
       </c>
       <c r="N23" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O23" s="46" t="n"/>
       <c r="P23" s="53" t="n">
@@ -10562,7 +10560,7 @@
         </is>
       </c>
       <c r="N24" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O24" s="46" t="n"/>
       <c r="P24" s="53" t="n">
@@ -10619,7 +10617,7 @@
         </is>
       </c>
       <c r="N25" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O25" s="46" t="n"/>
       <c r="P25" s="53" t="n">
@@ -10676,7 +10674,7 @@
         </is>
       </c>
       <c r="N26" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O26" s="46" t="n"/>
       <c r="P26" s="53" t="n">
@@ -10733,7 +10731,7 @@
         </is>
       </c>
       <c r="N27" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O27" s="46" t="n"/>
       <c r="P27" s="53" t="n">
@@ -10790,7 +10788,7 @@
         </is>
       </c>
       <c r="N28" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O28" s="46" t="n"/>
       <c r="P28" s="53" t="n">
@@ -10847,7 +10845,7 @@
         </is>
       </c>
       <c r="N29" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O29" s="46" t="n"/>
       <c r="P29" s="53" t="n">
@@ -10904,7 +10902,7 @@
         </is>
       </c>
       <c r="N30" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O30" s="46" t="n"/>
       <c r="P30" s="53" t="n">
@@ -10961,7 +10959,7 @@
         </is>
       </c>
       <c r="N31" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O31" s="46" t="n"/>
       <c r="P31" s="53" t="n">
@@ -11018,7 +11016,7 @@
         </is>
       </c>
       <c r="N32" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O32" s="46" t="n"/>
       <c r="P32" s="53" t="n">
@@ -11075,7 +11073,7 @@
         </is>
       </c>
       <c r="N33" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O33" s="46" t="n"/>
       <c r="P33" s="53" t="n">
@@ -11132,7 +11130,7 @@
         </is>
       </c>
       <c r="N34" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O34" s="46" t="n"/>
       <c r="P34" s="53" t="n">
@@ -11189,7 +11187,7 @@
         </is>
       </c>
       <c r="N35" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O35" s="46" t="n"/>
       <c r="P35" s="53" t="n">
@@ -11246,7 +11244,7 @@
         </is>
       </c>
       <c r="N36" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O36" s="46" t="n"/>
       <c r="P36" s="53" t="n">
@@ -11303,7 +11301,7 @@
         </is>
       </c>
       <c r="N37" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O37" s="46" t="n"/>
       <c r="P37" s="53" t="n">
@@ -11360,7 +11358,7 @@
         </is>
       </c>
       <c r="N38" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O38" s="46" t="n"/>
       <c r="P38" s="53" t="n">
@@ -11417,7 +11415,7 @@
         </is>
       </c>
       <c r="N39" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O39" s="46" t="n"/>
       <c r="P39" s="53" t="n">
@@ -11474,7 +11472,7 @@
         </is>
       </c>
       <c r="N40" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O40" s="46" t="n"/>
       <c r="P40" s="53" t="n">
@@ -11531,7 +11529,7 @@
         </is>
       </c>
       <c r="N41" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O41" s="46" t="n"/>
       <c r="P41" s="53" t="n">
@@ -11588,7 +11586,7 @@
         </is>
       </c>
       <c r="N42" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O42" s="46" t="n"/>
       <c r="P42" s="53" t="n">
@@ -11645,7 +11643,7 @@
         </is>
       </c>
       <c r="N43" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O43" s="46" t="n"/>
       <c r="P43" s="53" t="n">
@@ -11702,7 +11700,7 @@
         </is>
       </c>
       <c r="N44" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O44" s="46" t="n"/>
       <c r="P44" s="53" t="n">
@@ -11759,7 +11757,7 @@
         </is>
       </c>
       <c r="N45" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O45" s="46" t="n"/>
       <c r="P45" s="53" t="n">
@@ -11816,7 +11814,7 @@
         </is>
       </c>
       <c r="N46" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O46" s="46" t="n"/>
       <c r="P46" s="53" t="n">
@@ -11873,7 +11871,7 @@
         </is>
       </c>
       <c r="N47" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O47" s="46" t="n"/>
       <c r="P47" s="53" t="n">
@@ -11930,7 +11928,7 @@
         </is>
       </c>
       <c r="N48" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O48" s="46" t="n"/>
       <c r="P48" s="53" t="n">
@@ -11987,7 +11985,7 @@
         </is>
       </c>
       <c r="N49" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O49" s="46" t="n"/>
       <c r="P49" s="53" t="n">
@@ -12040,7 +12038,7 @@
         </is>
       </c>
       <c r="N50" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O50" s="49" t="n"/>
       <c r="P50" s="55" t="n">
@@ -12097,7 +12095,7 @@
         </is>
       </c>
       <c r="N51" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O51" s="49" t="n"/>
       <c r="P51" s="55" t="n">
@@ -12158,7 +12156,7 @@
         </is>
       </c>
       <c r="N52" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O52" s="46" t="n"/>
       <c r="P52" s="53" t="n">
@@ -12215,7 +12213,7 @@
         </is>
       </c>
       <c r="N53" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O53" s="46" t="n"/>
       <c r="P53" s="53" t="n">
@@ -12268,7 +12266,7 @@
         </is>
       </c>
       <c r="N54" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O54" s="49" t="n"/>
       <c r="P54" s="55" t="n">
@@ -12329,7 +12327,7 @@
         </is>
       </c>
       <c r="N55" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O55" s="46" t="n"/>
       <c r="P55" s="53" t="n">
@@ -12386,7 +12384,7 @@
         </is>
       </c>
       <c r="N56" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O56" s="46" t="n"/>
       <c r="P56" s="53" t="n">
@@ -12443,7 +12441,7 @@
         </is>
       </c>
       <c r="N57" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O57" s="46" t="n"/>
       <c r="P57" s="53" t="n">
@@ -12500,7 +12498,7 @@
         </is>
       </c>
       <c r="N58" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O58" s="46" t="n"/>
       <c r="P58" s="53" t="n">
@@ -12557,7 +12555,7 @@
         </is>
       </c>
       <c r="N59" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O59" s="46" t="n"/>
       <c r="P59" s="53" t="n">
@@ -12622,7 +12620,7 @@
         </is>
       </c>
       <c r="N60" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O60" s="46" t="n"/>
       <c r="P60" s="53" t="n">
@@ -12679,7 +12677,7 @@
         </is>
       </c>
       <c r="N61" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O61" s="46" t="n"/>
       <c r="P61" s="53" t="n">
@@ -12736,7 +12734,7 @@
         </is>
       </c>
       <c r="N62" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O62" s="49" t="n"/>
       <c r="P62" s="55" t="n">
@@ -12797,7 +12795,7 @@
         </is>
       </c>
       <c r="N63" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O63" s="49" t="n"/>
       <c r="P63" s="55" t="n">
@@ -12858,7 +12856,7 @@
         </is>
       </c>
       <c r="N64" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O64" s="46" t="n"/>
       <c r="P64" s="53" t="n">
@@ -12915,7 +12913,7 @@
         </is>
       </c>
       <c r="N65" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O65" s="46" t="n"/>
       <c r="P65" s="53" t="n">
@@ -12972,7 +12970,7 @@
         </is>
       </c>
       <c r="N66" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O66" s="46" t="n"/>
       <c r="P66" s="53" t="n">
@@ -13029,7 +13027,7 @@
         </is>
       </c>
       <c r="N67" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O67" s="46" t="n"/>
       <c r="P67" s="53" t="n">
@@ -13086,7 +13084,7 @@
         </is>
       </c>
       <c r="N68" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O68" s="46" t="n"/>
       <c r="P68" s="53" t="n">
@@ -13143,7 +13141,7 @@
         </is>
       </c>
       <c r="N69" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O69" s="46" t="n"/>
       <c r="P69" s="53" t="n">
@@ -13200,7 +13198,7 @@
         </is>
       </c>
       <c r="N70" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O70" s="49" t="n"/>
       <c r="P70" s="55" t="n">
@@ -13261,7 +13259,7 @@
         </is>
       </c>
       <c r="N71" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O71" s="46" t="n"/>
       <c r="P71" s="53" t="n">
@@ -13318,7 +13316,7 @@
         </is>
       </c>
       <c r="N72" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O72" s="46" t="n"/>
       <c r="P72" s="53" t="n">
@@ -13375,7 +13373,7 @@
         </is>
       </c>
       <c r="N73" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O73" s="46" t="n"/>
       <c r="P73" s="53" t="n">
@@ -13432,7 +13430,7 @@
         </is>
       </c>
       <c r="N74" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O74" s="46" t="n"/>
       <c r="P74" s="53" t="n">
@@ -13489,7 +13487,7 @@
         </is>
       </c>
       <c r="N75" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O75" s="46" t="n"/>
       <c r="P75" s="53" t="n">
@@ -13546,7 +13544,7 @@
         </is>
       </c>
       <c r="N76" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O76" s="46" t="n"/>
       <c r="P76" s="53" t="n">
@@ -13603,7 +13601,7 @@
         </is>
       </c>
       <c r="N77" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O77" s="46" t="n"/>
       <c r="P77" s="53" t="n">
@@ -13660,7 +13658,7 @@
         </is>
       </c>
       <c r="N78" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O78" s="46" t="n"/>
       <c r="P78" s="53" t="n">
@@ -13717,7 +13715,7 @@
         </is>
       </c>
       <c r="N79" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O79" s="46" t="n"/>
       <c r="P79" s="53" t="n">
@@ -13774,7 +13772,7 @@
         </is>
       </c>
       <c r="N80" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O80" s="46" t="n"/>
       <c r="P80" s="53" t="n">
@@ -13831,7 +13829,7 @@
         </is>
       </c>
       <c r="N81" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O81" s="46" t="n"/>
       <c r="P81" s="53" t="n">
@@ -13888,7 +13886,7 @@
         </is>
       </c>
       <c r="N82" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O82" s="46" t="n"/>
       <c r="P82" s="53" t="n">
@@ -13945,7 +13943,7 @@
         </is>
       </c>
       <c r="N83" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O83" s="46" t="n"/>
       <c r="P83" s="53" t="n">
@@ -14002,7 +14000,7 @@
         </is>
       </c>
       <c r="N84" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O84" s="46" t="n"/>
       <c r="P84" s="53" t="n">
@@ -14059,7 +14057,7 @@
         </is>
       </c>
       <c r="N85" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O85" s="46" t="n"/>
       <c r="P85" s="53" t="n">
@@ -14116,7 +14114,7 @@
         </is>
       </c>
       <c r="N86" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O86" s="46" t="n"/>
       <c r="P86" s="53" t="n">
@@ -14173,7 +14171,7 @@
         </is>
       </c>
       <c r="N87" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O87" s="46" t="n"/>
       <c r="P87" s="53" t="n">
@@ -14230,7 +14228,7 @@
         </is>
       </c>
       <c r="N88" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O88" s="46" t="n"/>
       <c r="P88" s="53" t="n">
@@ -14295,7 +14293,7 @@
         </is>
       </c>
       <c r="N89" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O89" s="46" t="n"/>
       <c r="P89" s="53" t="n">
@@ -14352,7 +14350,7 @@
         </is>
       </c>
       <c r="N90" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O90" s="46" t="n"/>
       <c r="P90" s="53" t="n">
@@ -14409,7 +14407,7 @@
         </is>
       </c>
       <c r="N91" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O91" s="46" t="n"/>
       <c r="P91" s="53" t="n">
@@ -14466,7 +14464,7 @@
         </is>
       </c>
       <c r="N92" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O92" s="46" t="n"/>
       <c r="P92" s="53" t="n">
@@ -14523,7 +14521,7 @@
         </is>
       </c>
       <c r="N93" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O93" s="46" t="n"/>
       <c r="P93" s="53" t="n">
@@ -14580,7 +14578,7 @@
         </is>
       </c>
       <c r="N94" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O94" s="49" t="n"/>
       <c r="P94" s="55" t="n">
@@ -14641,7 +14639,7 @@
         </is>
       </c>
       <c r="N95" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O95" s="46" t="n"/>
       <c r="P95" s="53" t="n">
@@ -14702,7 +14700,7 @@
         </is>
       </c>
       <c r="N96" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O96" s="46" t="n"/>
       <c r="P96" s="53" t="n">
@@ -14759,7 +14757,7 @@
         </is>
       </c>
       <c r="N97" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O97" s="46" t="n"/>
       <c r="P97" s="53" t="n">
@@ -14828,7 +14826,7 @@
         </is>
       </c>
       <c r="N98" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O98" s="46" t="n"/>
       <c r="P98" s="53" t="n">
@@ -14885,7 +14883,7 @@
         </is>
       </c>
       <c r="N99" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O99" s="46" t="n"/>
       <c r="P99" s="53" t="n">
@@ -14946,7 +14944,7 @@
         </is>
       </c>
       <c r="N100" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O100" s="46" t="n"/>
       <c r="P100" s="53" t="n">
@@ -15003,7 +15001,7 @@
         </is>
       </c>
       <c r="N101" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O101" s="46" t="n"/>
       <c r="P101" s="53" t="n">
@@ -15056,7 +15054,7 @@
         </is>
       </c>
       <c r="N102" s="55" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O102" s="49" t="n"/>
       <c r="P102" s="55" t="n">
@@ -15117,7 +15115,7 @@
         </is>
       </c>
       <c r="N103" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O103" s="46" t="n"/>
       <c r="P103" s="53" t="n">
@@ -15178,7 +15176,7 @@
         </is>
       </c>
       <c r="N104" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O104" s="46" t="n"/>
       <c r="P104" s="53" t="n">
@@ -15235,7 +15233,7 @@
         </is>
       </c>
       <c r="N105" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O105" s="46" t="n"/>
       <c r="P105" s="53" t="n">
@@ -15296,7 +15294,7 @@
         </is>
       </c>
       <c r="N106" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O106" s="46" t="n"/>
       <c r="P106" s="53" t="n">
@@ -15353,7 +15351,7 @@
         </is>
       </c>
       <c r="N107" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O107" s="46" t="n"/>
       <c r="P107" s="53" t="n">
@@ -15414,7 +15412,7 @@
         </is>
       </c>
       <c r="N108" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O108" s="46" t="n"/>
       <c r="P108" s="53" t="n">
@@ -15483,7 +15481,7 @@
         </is>
       </c>
       <c r="N109" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O109" s="46" t="n"/>
       <c r="P109" s="53" t="n">
@@ -15544,7 +15542,7 @@
         </is>
       </c>
       <c r="N110" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O110" s="46" t="n"/>
       <c r="P110" s="53" t="n">
@@ -15605,7 +15603,7 @@
         </is>
       </c>
       <c r="N111" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O111" s="46" t="n"/>
       <c r="P111" s="53" t="n">
@@ -15666,7 +15664,7 @@
         </is>
       </c>
       <c r="N112" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O112" s="46" t="n"/>
       <c r="P112" s="53" t="n">
@@ -15727,7 +15725,7 @@
         </is>
       </c>
       <c r="N113" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O113" s="46" t="n"/>
       <c r="P113" s="53" t="n">
@@ -15788,7 +15786,7 @@
         </is>
       </c>
       <c r="N114" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O114" s="46" t="n"/>
       <c r="P114" s="53" t="n">
@@ -15849,7 +15847,7 @@
         </is>
       </c>
       <c r="N115" s="53" t="n">
-        <v>46324.52037037037</v>
+        <v>46325.51431712963</v>
       </c>
       <c r="O115" s="46" t="n"/>
       <c r="P115" s="53" t="n">

--- a/PM_ESTUDIO_MASTER_COMPLETO.xlsx
+++ b/PM_ESTUDIO_MASTER_COMPLETO.xlsx
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="N2" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O2" s="46" t="n"/>
       <c r="P2" s="53" t="n">
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="N3" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O3" s="46" t="n"/>
       <c r="P3" s="53" t="n">
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="N4" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O4" s="46" t="n"/>
       <c r="P4" s="53" t="n">
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="N5" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O5" s="46" t="n"/>
       <c r="P5" s="53" t="n">
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="N6" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O6" s="46" t="n"/>
       <c r="P6" s="53" t="n">
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="N7" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O7" s="46" t="n"/>
       <c r="P7" s="53" t="n">
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="N8" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O8" s="46" t="n"/>
       <c r="P8" s="53" t="n">
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="N9" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O9" s="46" t="n"/>
       <c r="P9" s="53" t="n">
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="N10" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O10" s="46" t="n"/>
       <c r="P10" s="53" t="n">
@@ -9819,7 +9819,7 @@
         </is>
       </c>
       <c r="N11" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O11" s="46" t="n"/>
       <c r="P11" s="53" t="n">
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="N12" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O12" s="46" t="n"/>
       <c r="P12" s="53" t="n">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="N13" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O13" s="46" t="n"/>
       <c r="P13" s="53" t="n">
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="N14" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O14" s="49" t="n"/>
       <c r="P14" s="55" t="n">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="N15" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O15" s="46" t="n"/>
       <c r="P15" s="53" t="n">
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="N16" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O16" s="46" t="n"/>
       <c r="P16" s="53" t="n">
@@ -10161,7 +10161,7 @@
         </is>
       </c>
       <c r="N17" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O17" s="46" t="n"/>
       <c r="P17" s="53" t="n">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="N18" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O18" s="46" t="n"/>
       <c r="P18" s="53" t="n">
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="N19" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O19" s="46" t="n"/>
       <c r="P19" s="53" t="n">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="N20" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O20" s="46" t="n"/>
       <c r="P20" s="53" t="n">
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="N21" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O21" s="46" t="n"/>
       <c r="P21" s="53" t="n">
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="N22" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O22" s="46" t="n"/>
       <c r="P22" s="53" t="n">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="N23" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O23" s="46" t="n"/>
       <c r="P23" s="53" t="n">
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="N24" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O24" s="46" t="n"/>
       <c r="P24" s="53" t="n">
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="N25" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O25" s="46" t="n"/>
       <c r="P25" s="53" t="n">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="N26" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O26" s="46" t="n"/>
       <c r="P26" s="53" t="n">
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="N27" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O27" s="46" t="n"/>
       <c r="P27" s="53" t="n">
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="N28" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O28" s="46" t="n"/>
       <c r="P28" s="53" t="n">
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="N29" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O29" s="46" t="n"/>
       <c r="P29" s="53" t="n">
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="N30" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O30" s="46" t="n"/>
       <c r="P30" s="53" t="n">
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="N31" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O31" s="46" t="n"/>
       <c r="P31" s="53" t="n">
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="N32" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O32" s="46" t="n"/>
       <c r="P32" s="53" t="n">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="N33" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O33" s="46" t="n"/>
       <c r="P33" s="53" t="n">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="N34" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O34" s="46" t="n"/>
       <c r="P34" s="53" t="n">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="N35" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O35" s="46" t="n"/>
       <c r="P35" s="53" t="n">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="N36" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O36" s="46" t="n"/>
       <c r="P36" s="53" t="n">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="N37" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O37" s="46" t="n"/>
       <c r="P37" s="53" t="n">
@@ -11358,7 +11358,7 @@
         </is>
       </c>
       <c r="N38" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O38" s="46" t="n"/>
       <c r="P38" s="53" t="n">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="N39" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O39" s="46" t="n"/>
       <c r="P39" s="53" t="n">
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="N40" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O40" s="46" t="n"/>
       <c r="P40" s="53" t="n">
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="N41" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O41" s="46" t="n"/>
       <c r="P41" s="53" t="n">
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="N42" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O42" s="46" t="n"/>
       <c r="P42" s="53" t="n">
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="N43" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O43" s="46" t="n"/>
       <c r="P43" s="53" t="n">
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="N44" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O44" s="46" t="n"/>
       <c r="P44" s="53" t="n">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="N45" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O45" s="46" t="n"/>
       <c r="P45" s="53" t="n">
@@ -11814,7 +11814,7 @@
         </is>
       </c>
       <c r="N46" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O46" s="46" t="n"/>
       <c r="P46" s="53" t="n">
@@ -11871,7 +11871,7 @@
         </is>
       </c>
       <c r="N47" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O47" s="46" t="n"/>
       <c r="P47" s="53" t="n">
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="N48" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O48" s="46" t="n"/>
       <c r="P48" s="53" t="n">
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="N49" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O49" s="46" t="n"/>
       <c r="P49" s="53" t="n">
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="N50" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O50" s="49" t="n"/>
       <c r="P50" s="55" t="n">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="N51" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O51" s="49" t="n"/>
       <c r="P51" s="55" t="n">
@@ -12156,7 +12156,7 @@
         </is>
       </c>
       <c r="N52" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O52" s="46" t="n"/>
       <c r="P52" s="53" t="n">
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="N53" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O53" s="46" t="n"/>
       <c r="P53" s="53" t="n">
@@ -12266,7 +12266,7 @@
         </is>
       </c>
       <c r="N54" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O54" s="49" t="n"/>
       <c r="P54" s="55" t="n">
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="N55" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O55" s="46" t="n"/>
       <c r="P55" s="53" t="n">
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="N56" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O56" s="46" t="n"/>
       <c r="P56" s="53" t="n">
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="N57" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O57" s="46" t="n"/>
       <c r="P57" s="53" t="n">
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="N58" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O58" s="46" t="n"/>
       <c r="P58" s="53" t="n">
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="N59" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O59" s="46" t="n"/>
       <c r="P59" s="53" t="n">
@@ -12620,7 +12620,7 @@
         </is>
       </c>
       <c r="N60" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O60" s="46" t="n"/>
       <c r="P60" s="53" t="n">
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="N61" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O61" s="46" t="n"/>
       <c r="P61" s="53" t="n">
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="N62" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O62" s="49" t="n"/>
       <c r="P62" s="55" t="n">
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="N63" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O63" s="49" t="n"/>
       <c r="P63" s="55" t="n">
@@ -12856,7 +12856,7 @@
         </is>
       </c>
       <c r="N64" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O64" s="46" t="n"/>
       <c r="P64" s="53" t="n">
@@ -12913,7 +12913,7 @@
         </is>
       </c>
       <c r="N65" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O65" s="46" t="n"/>
       <c r="P65" s="53" t="n">
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="N66" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O66" s="46" t="n"/>
       <c r="P66" s="53" t="n">
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="N67" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O67" s="46" t="n"/>
       <c r="P67" s="53" t="n">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="N68" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O68" s="46" t="n"/>
       <c r="P68" s="53" t="n">
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="N69" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O69" s="46" t="n"/>
       <c r="P69" s="53" t="n">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="N70" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O70" s="49" t="n"/>
       <c r="P70" s="55" t="n">
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="N71" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O71" s="46" t="n"/>
       <c r="P71" s="53" t="n">
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="N72" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O72" s="46" t="n"/>
       <c r="P72" s="53" t="n">
@@ -13373,7 +13373,7 @@
         </is>
       </c>
       <c r="N73" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O73" s="46" t="n"/>
       <c r="P73" s="53" t="n">
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="N74" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O74" s="46" t="n"/>
       <c r="P74" s="53" t="n">
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="N75" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O75" s="46" t="n"/>
       <c r="P75" s="53" t="n">
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="N76" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O76" s="46" t="n"/>
       <c r="P76" s="53" t="n">
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="N77" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O77" s="46" t="n"/>
       <c r="P77" s="53" t="n">
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="N78" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O78" s="46" t="n"/>
       <c r="P78" s="53" t="n">
@@ -13715,7 +13715,7 @@
         </is>
       </c>
       <c r="N79" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O79" s="46" t="n"/>
       <c r="P79" s="53" t="n">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="N80" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O80" s="46" t="n"/>
       <c r="P80" s="53" t="n">
@@ -13829,7 +13829,7 @@
         </is>
       </c>
       <c r="N81" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O81" s="46" t="n"/>
       <c r="P81" s="53" t="n">
@@ -13886,7 +13886,7 @@
         </is>
       </c>
       <c r="N82" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O82" s="46" t="n"/>
       <c r="P82" s="53" t="n">
@@ -13943,7 +13943,7 @@
         </is>
       </c>
       <c r="N83" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O83" s="46" t="n"/>
       <c r="P83" s="53" t="n">
@@ -14000,7 +14000,7 @@
         </is>
       </c>
       <c r="N84" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O84" s="46" t="n"/>
       <c r="P84" s="53" t="n">
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="N85" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O85" s="46" t="n"/>
       <c r="P85" s="53" t="n">
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="N86" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O86" s="46" t="n"/>
       <c r="P86" s="53" t="n">
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="N87" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O87" s="46" t="n"/>
       <c r="P87" s="53" t="n">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="N88" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O88" s="46" t="n"/>
       <c r="P88" s="53" t="n">
@@ -14293,7 +14293,7 @@
         </is>
       </c>
       <c r="N89" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O89" s="46" t="n"/>
       <c r="P89" s="53" t="n">
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="N90" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O90" s="46" t="n"/>
       <c r="P90" s="53" t="n">
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="N91" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O91" s="46" t="n"/>
       <c r="P91" s="53" t="n">
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="N92" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O92" s="46" t="n"/>
       <c r="P92" s="53" t="n">
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="N93" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O93" s="46" t="n"/>
       <c r="P93" s="53" t="n">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="N94" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O94" s="49" t="n"/>
       <c r="P94" s="55" t="n">
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="N95" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O95" s="46" t="n"/>
       <c r="P95" s="53" t="n">
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="N96" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O96" s="46" t="n"/>
       <c r="P96" s="53" t="n">
@@ -14757,7 +14757,7 @@
         </is>
       </c>
       <c r="N97" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O97" s="46" t="n"/>
       <c r="P97" s="53" t="n">
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="N98" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O98" s="46" t="n"/>
       <c r="P98" s="53" t="n">
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="N99" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O99" s="46" t="n"/>
       <c r="P99" s="53" t="n">
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="N100" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O100" s="46" t="n"/>
       <c r="P100" s="53" t="n">
@@ -15001,7 +15001,7 @@
         </is>
       </c>
       <c r="N101" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O101" s="46" t="n"/>
       <c r="P101" s="53" t="n">
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="N102" s="55" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O102" s="49" t="n"/>
       <c r="P102" s="55" t="n">
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="N103" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O103" s="46" t="n"/>
       <c r="P103" s="53" t="n">
@@ -15176,7 +15176,7 @@
         </is>
       </c>
       <c r="N104" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O104" s="46" t="n"/>
       <c r="P104" s="53" t="n">
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="N105" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O105" s="46" t="n"/>
       <c r="P105" s="53" t="n">
@@ -15294,7 +15294,7 @@
         </is>
       </c>
       <c r="N106" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O106" s="46" t="n"/>
       <c r="P106" s="53" t="n">
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="N107" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O107" s="46" t="n"/>
       <c r="P107" s="53" t="n">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="N108" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O108" s="46" t="n"/>
       <c r="P108" s="53" t="n">
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="N109" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O109" s="46" t="n"/>
       <c r="P109" s="53" t="n">
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="N110" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O110" s="46" t="n"/>
       <c r="P110" s="53" t="n">
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="N111" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O111" s="46" t="n"/>
       <c r="P111" s="53" t="n">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="N112" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O112" s="46" t="n"/>
       <c r="P112" s="53" t="n">
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="N113" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O113" s="46" t="n"/>
       <c r="P113" s="53" t="n">
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="N114" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O114" s="46" t="n"/>
       <c r="P114" s="53" t="n">
@@ -15847,7 +15847,7 @@
         </is>
       </c>
       <c r="N115" s="53" t="n">
-        <v>46325.51431712963</v>
+        <v>46326.49396990741</v>
       </c>
       <c r="O115" s="46" t="n"/>
       <c r="P115" s="53" t="n">
